--- a/untitled folder/HSC_Physics_1st_Paper_Chapter_06_Gravitation_and_Gravity.xlsx
+++ b/untitled folder/HSC_Physics_1st_Paper_Chapter_06_Gravitation_and_Gravity.xlsx
@@ -1054,17 +1054,12 @@
           <t>$L$ দৈর্ঘ্য ও $M$ ভরের একটি সুষম সোজা রড অনুভূমিকভাবে রাখা আছে। রডের নিকটবর্তী প্রান্ত থেকে অক্ষীয় রেখা বরাবর $d$ দূরত্বে অবস্থিত $m$ ভরের একটি বিন্দু কণার ওপর রড কর্তৃক প্রযুক্ত মহাকর্ষীয় আকর্ষণ বলের মান নির্ণয় কর।</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>রডের এক প্রান্ত থেকে দূরত্ব $x$ বিবেচনা করি। রডের রৈখিক ভর ঘনত্ব $\lambda = rac{M}{L}$। $dx$ পুরুত্বের একটি ক্ষুদ্রাংশের ভর $dM = \lambda dx = rac{M}{L}dx$। বিন্দু কণা হতে এই অংশের দূরত্ব $x$ (যেখানে $d \le x \le d + L$)। ক্ষুদ্র মহাকর্ষীয় বল $dF = rac{G m dM}{x^2} = rac{G M m}{L}rac{dx}{x^2}$। সমগ্র রডের জন্য সমাকলন করি: $F = rac{G M m}{L} \int_d^{d+L} rac{dx}{x^2} = rac{G M m}{L} \left[ -rac{1}{x} -ight]_d^{d+L} = rac{G M m}{L}\left(rac{1}{d} - rac{1}{d+L}-ight) = rac{G M m}{L}\left(rac{L}{d(d+L)}-ight) = rac{G M m}{d(d + L)}$। লক্ষণীয় যে এটি বিন্দু ভরের সূত্র $d^2$-এর চেয়ে ভিন্ন।</t>
+          <t>রডের এক প্রান্ত থেকে দূরত্ব $x$ বিবেচনা করি। রডের রৈখিক ভর ঘনত্ব $\lambda = \frac{M}{L}$। $dx$ পুরুত্বের একটি ক্ষুদ্রাংশের ভর $dM = \lambda dx = \frac{M}{L}dx$। বিন্দু কণা হতে এই অংশের দূরত্ব $x$ (যেখানে $d \le x \le d + L$)। ক্ষুদ্র মহাকর্ষীয় বল $dF = \frac{G m dM}{x^2} = \frac{G M m}{L}\frac{dx}{x^2}$। সমগ্র রডের জন্য সমাকলন করি: $F = \frac{G M m}{L} \int_d^{d+L} \frac{dx}{x^2} = \frac{G M m}{L} \left[ -\frac{1}{x} +ight]_d^{d+L} = \frac{G M m}{L}\left(\frac{1}{d} - \frac{1}{d+L}+ight) = \frac{G M m}{L}\left(\frac{L}{d(d+L)}+ight) = \frac{G M m}{d(d + L)}$। লক্ষণীয় যে এটি বিন্দু ভরের সূত্র $d^2$-এর চেয়ে ভিন্ন।</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -1107,15 +1102,10 @@
           <t>$L$ দৈর্ঘ্য ও $M$ ভরের একটি সুষম রডের মধ্যবিন্দু থেকে লম্ব দূরত্ব $r$-এ অবস্থিত $m$ ভরের একটি বিন্দু কণার ওপর রড কর্তৃক প্রযুক্ত লব্ধি মহাকর্ষীয় বল কত?</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>রডের মধ্যবিন্দুকে মূলবিন্দু ধরলে রডটি $-L/2 \le x \le L/2$ বরাবর অবস্থিত। কণাটি $(0, r)$ বিন্দুতে অবস্থিত। ক্ষুদ্রাংশ $dx$-এর দূরত্ব $\sqrt{x^2 + r^2}$ এবং কোণ $\cos	heta = rac{r}{\sqrt{x^2+r^2}}$। প্রতিসাম্যের কারণে অনুভূমিক উপাংশসমূহ বাতিল হয়ে যায়। উল্লম্ব লব্ধি বল $F = \int dF_y = \int_{-L/2}^{L/2} rac{G m (M/L)dx}{x^2 + r^2}rac{r}{\sqrt{x^2 + r^2}} = rac{G M m r}{L} \int_{-L/2}^{L/2} rac{dx}{(x^2 + r^2)^{3/2}}$। ত্রিকোণমিতিক প্রতিস্থাপন $x = r	an	heta$ করলে সমাকলনের মান দাঁড়ায় $\left[ rac{x}{r^2 \sqrt{x^2 + r^2}} -ight]_{-L/2}^{L/2} = rac{L}{r^2 \sqrt{(L/2)^2 + r^2}}$। অতএব লব্ধি বল $F = rac{G M m}{r\sqrt{r^2 + L^2/4}} = rac{2G M m}{r\sqrt{4r^2 + L^2}}$। অসীম দৈর্ঘ্যের রডের জন্য ($L 	o \infty$) এটি $F = rac{2G\lambda m}{r}$ হয়।</t>
+          <t>রডের মধ্যবিন্দুকে মূলবিন্দু ধরলে রডটি $-L/2 \le x \le L/2$ বরাবর অবস্থিত। কণাটি $(0, r)$ বিন্দুতে অবস্থিত। ক্ষুদ্রাংশ $dx$-এর দূরত্ব $\sqrt{x^2 + r^2}$ এবং কোণ $\cos\theta = \frac{r}{\sqrt{x^2+r^2}}$। প্রতিসাম্যের কারণে অনুভূমিক উপাংশসমূহ বাতিল হয়ে যায়। উল্লম্ব লব্ধি বল $F = \int dF_y = \int_{-L/2}^{L/2} \frac{G m (M/L)dx}{x^2 + r^2}\frac{r}{\sqrt{x^2 + r^2}} = \frac{G M m r}{L} \int_{-L/2}^{L/2} \frac{dx}{(x^2 + r^2)^{3/2}}$। ত্রিকোণমিতিক প্রতিস্থাপন $x = r\tan\theta$ করলে সমাকলনের মান দাঁড়ায় $\left[ \frac{x}{r^2 \sqrt{x^2 + r^2}} +ight]_{-L/2}^{L/2} = \frac{L}{r^2 \sqrt{(L/2)^2 + r^2}}$। অতএব লব্ধি বল $F = \frac{G M m}{r\sqrt{r^2 + L^2/4}} = \frac{2G M m}{r\sqrt{4r^2 + L^2}}$। অসীম দৈর্ঘ্যের রডের জন্য ($L \to \infty$) এটি $F = \frac{2G\lambda m}{r}$ হয়।</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -1158,14 +1148,9 @@
           <t>$R$ ব্যাসার্ধ ও $M$ ভরের একটি সুষম বৃত্তাকার রিংয়ের অক্ষের ওপর কেন্দ্র থেকে $x$ দূরত্বে মহাকর্ষীয় ক্ষেত্র প্রাবল্য $E(x)$ নির্ণয় কর এবং কেন্দ্র থেকে কত দূরত্বে এই প্রাবল্যের মান সর্বোচ্চ হবে?</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>রিংয়ের পরিধির প্রতিটি বিন্দুর দূরত্ব কণা থেকে ধ্রুব এবং তা $\sqrt{R^2 + x^2}$। প্রতিসাম্যের কারণে অক্ষের লম্ব উপাংশসমূহ শূন্য হয়। অক্ষীয় উপাংশ $E(x) = \int rac{G dm}{R^2 + x^2}\cos	heta = rac{G M}{R^2 + x^2}rac{x}{\sqrt{R^2 + x^2}} = rac{G M x}{(R^2 + x^2)^{3/2}}$ কেন্দ্রের অভিমুখী। সর্বোচ্চ মানের শর্ত $rac{dE}{dx} = 0 \implies rac{(R^2 + x^2)^{3/2}(1) - xrac{3}{2}(R^2 + x^2)^{1/2}(2x)}{(R^2 + x^2)^3} = 0 \implies (R^2 + x^2) - 3x^2 = 0 \implies 2x^2 = R^2 \implies x = \pm rac{R}{\sqrt{2}}$। সর্বোচ্চ প্রাবল্য $E_{\max} = rac{2G M}{3\sqrt{3}R^2}$।</t>
+          <t>রিংয়ের পরিধির প্রতিটি বিন্দুর দূরত্ব কণা থেকে ধ্রুব এবং তা $\sqrt{R^2 + x^2}$। প্রতিসাম্যের কারণে অক্ষের লম্ব উপাংশসমূহ শূন্য হয়। অক্ষীয় উপাংশ $E(x) = \int \frac{G dm}{R^2 + x^2}\cos\theta = \frac{G M}{R^2 + x^2}\frac{x}{\sqrt{R^2 + x^2}} = \frac{G M x}{(R^2 + x^2)^{3/2}}$ কেন্দ্রের অভিমুখী। সর্বোচ্চ মানের শর্ত $\frac{dE}{dx} = 0 \implies \frac{(R^2 + x^2)^{3/2}(1) - xrac{3}{2}(R^2 + x^2)^{1/2}(2x)}{(R^2 + x^2)^3} = 0 \implies (R^2 + x^2) - 3x^2 = 0 \implies 2x^2 = R^2 \implies x = \pm \frac{R}{\sqrt{2}}$। সর্বোচ্চ প্রাবল্য $E_{\max} = \frac{2G M}{3\sqrt{3}R^2}$।</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -1208,17 +1193,12 @@
           <t>$R$ ব্যাসার্ধ এবং সুষম ক্ষেত্র ঘনত্ব $\sigma$ বিশিষ্ট একটি পাতলা বৃত্তাকার চাকতির অক্ষ বরাবর কেন্দ্র থেকে $x$ দূরত্বে মহাকর্ষীয় ক্ষেত্র প্রাবল্য নির্ণয় কর এবং অসীম পাতের সীমাস্থ মান আলোচনা কর।</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>চাকতিটিকে $r$ ব্যাসার্ধ ও $dr$ পুরুত্বের সমকেন্দ্রিক রিংসমূহে বিভক্ত করি। রিংয়ের ভর $dM = \sigma 2\pi r dr$। রিংয়ের জন্য প্রাবল্য $dE = rac{G (dM) x}{(r^2 + x^2)^{3/2}} = 2\pi G \sigma x rac{r dr}{(r^2 + x^2)^{3/2}}$। সমগ্র চাকতির জন্য সমাকলন করি: $E = 2\pi G \sigma x \int_0^R rac{r dr}{(r^2 + x^2)^{3/2}} = 2\pi G \sigma x \left[ -rac{1}{\sqrt{r^2 + x^2}} -ight]_0^R = 2\pi G \sigma x \left(rac{1}{x} - rac{1}{\sqrt{R^2 + x^2}}-ight) = 2\pi G \sigma \left(1 - rac{x}{\sqrt{R^2 + x^2}}-ight)$। অসীম চাকতির ক্ষেত্রে ($R 	o \infty$) প্রাবল্য ধ্রুব থাকে: $E = 2\pi G \sigma$ (দূরত্বের ওপর স্বাধীন)।</t>
+          <t>চাকতিটিকে $r$ ব্যাসার্ধ ও $dr$ পুরুত্বের সমকেন্দ্রিক রিংসমূহে বিভক্ত করি। রিংয়ের ভর $dM = \sigma 2\pi r dr$। রিংয়ের জন্য প্রাবল্য $dE = \frac{G (dM) x}{(r^2 + x^2)^{3/2}} = 2\pi G \sigma x \frac{r dr}{(r^2 + x^2)^{3/2}}$। সমগ্র চাকতির জন্য সমাকলন করি: $E = 2\pi G \sigma x \int_0^R \frac{r dr}{(r^2 + x^2)^{3/2}} = 2\pi G \sigma x \left[ -\frac{1}{\sqrt{r^2 + x^2}} +ight]_0^R = 2\pi G \sigma x \left(\frac{1}{x} - \frac{1}{\sqrt{R^2 + x^2}}+ight) = 2\pi G \sigma \left(1 - \frac{x}{\sqrt{R^2 + x^2}}+ight)$। অসীম চাকতির ক্ষেত্রে ($R \to \infty$) প্রাবল্য ধ্রুব থাকে: $E = 2\pi G \sigma$ (দূরত্বের ওপর স্বাধীন)।</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1262,20 +1242,15 @@
 ho$ সুষম ঘনত্বের একটি নিরেট গোলকের ভেতর $R/2$ ব্যাসের একটি গোলকীয় গহ্বর তৈরি করা হলো যার কেন্দ্র মূল কেন্দ্র থেকে $ec{d}$ ভেক্টরে অবস্থিত। প্রমাণ কর যে গহ্বরের অভ্যন্তরে যে কোনো বিন্দুতে মহাকর্ষীয় ক্ষেত্র প্রাবল্য সম্পূর্ণ সুষম (Uniform) এবং এর মান ও দিক নির্ণয় কর।</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>উপরিফাতন নীতি অনুসারে: গহ্বরযুক্ত গোলকের ক্ষেত্র = সম্পূর্ণ গোলকের ক্ষেত্র ($ec{E}_1$) + গহ্বরের আয়তনের সমান ঋণাত্মক ঘনত্বের গোলকের ক্ষেত্র ($ec{E}_2$)। গাউসের সূত্রানুসারে সম্পূর্ণ গোলকের অভ্যন্তরে কেন্দ্র থেকে $ec{r}$ অবস্থানে প্রাবল্য $ec{E}_1 = -rac{4}{3}\pi G -ho ec{r}$। গহ্বরের কেন্দ্রের সাপেক্ষে অবস্থান $ec{r}' = ec{r} - ec{d}$ হলে ঋণাত্মক গোলকের প্রাবল্য $ec{E}_2 = +rac{4}{3}\pi G -ho ec{r}' = rac{4}{3}\pi G -ho (ec{r} - ec{d})$। অতএব গহ্বরের অভ্যন্তরে মোট প্রাবল্য $ec{E} = ec{E}_1 + ec{E}_2 = -rac{4}{3}\pi G -ho ec{r} + rac{4}{3}\pi G -ho ec{r} - rac{4}{3}\pi G -ho ec{d} = -rac{4}{3}\pi G +          <t>উপরিফাতন নীতি অনুসারে: গহ্বরযুক্ত গোলকের ক্ষেত্র = সম্পূর্ণ গোলকের ক্ষেত্র ($ec{E}_1$) + গহ্বরের আয়তনের সমান ঋণাত্মক ঘনত্বের গোলকের ক্ষেত্র ($ec{E}_2$)। গাউসের সূত্রানুসারে সম্পূর্ণ গোলকের অভ্যন্তরে কেন্দ্র থেকে $ec{r}$ অবস্থানে প্রাবল্য $ec{E}_1 = -\frac{4}{3}\pi G +ho ec{r}$। গহ্বরের কেন্দ্রের সাপেক্ষে অবস্থান $ec{r}' = ec{r} - ec{d}$ হলে ঋণাত্মক গোলকের প্রাবল্য $ec{E}_2 = +\frac{4}{3}\pi G +ho ec{r}' = \frac{4}{3}\pi G +ho (ec{r} - ec{d})$। অতএব গহ্বরের অভ্যন্তরে মোট প্রাবল্য $ec{E} = ec{E}_1 + ec{E}_2 = -\frac{4}{3}\pi G +ho ec{r} + \frac{4}{3}\pi G +ho ec{r} - \frac{4}{3}\pi G +ho ec{d} = -\frac{4}{3}\pi G  ho ec{d}$। যেহেতু এটি অবস্থানের ওপর নির্ভর করে না, সেহেতু গহ্বরের ভেতরে মহাকর্ষীয় ক্ষেত্র সম্পূর্ণ সুষম এবং এর দিক মূল কেন্দ্র থেকে গহ্বরের কেন্দ্রের দিকে।</t>
         </is>
       </c>
@@ -1319,18 +1294,13 @@
           <t>$R$ ব্যাসার্ধ এবং সুষম পৃষ্ঠ ঘনত্ব $\sigma$ বিশিষ্ট একটি পাতলা ফাঁপা গোলকের অর্ধেক কেটে একটি উন্মুক্ত অর্ধগোলক তৈরি করা হলো। অর্ধগোলকের ভূমির কেন্দ্রবিন্দুতে মহাকর্ষীয় ক্ষেত্র প্রাবল্য কত?</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>অর্ধগোলকের কেন্দ্রে প্রতিসাম্যের কারণে লব্ধি প্রাবল্য অক্ষের দিকে ক্রিয়া করে। অর্ধগোলকের ওপর $	heta$ কোণে $d	heta$ কৌণিক প্রস্থের একটি রিং বিবেচনা করি যার ব্যাসার্ধ $r = R\sin	heta$ এবং ক্ষেত্রফল $dA = 2\pi R\sin	heta (R d	heta) = 2\pi R^2 \sin	heta d	heta$। রিংয়ের প্রতিটি বিন্দুর দূরত্ব কেন্দ্র থেকে $R$। কেন্দ্রে রিংয়ের মহাকর্ষীয় প্রাবল্য $dE = rac{G \sigma dA}{R^2}\cos	heta = rac{G \sigma (2\pi R^2 \sin	heta d	heta)}{R^2}\cos	heta = 2\pi G \sigma \sin	heta\cos	heta d	heta = \pi G \sigma \sin(2	heta)d	heta$। সমগ্র অর্ধগোলকের জন্য সমাকলন করি ($0 \le 	heta \le \pi/2$): $E = \pi G \sigma \int_0^{\pi/2}\sin(2	heta)d	heta = \pi G \sigma \left[ -rac{\cos(2	heta)}{2} -ight]_0^{\pi/2} = \pi G \sigma \left(rac{1}{2} - \left(-rac{1}{2}+          <t>অর্ধগোলকের কেন্দ্রে প্রতিসাম্যের কারণে লব্ধি প্রাবল্য অক্ষের দিকে ক্রিয়া করে। অর্ধগোলকের ওপর $\theta$ কোণে $d\theta$ কৌণিক প্রস্থের একটি রিং বিবেচনা করি যার ব্যাসার্ধ $r = R\sin\theta$ এবং ক্ষেত্রফল $dA = 2\pi R\sin\theta (R d\theta) = 2\pi R^2 \sin\theta d\theta$। রিংয়ের প্রতিটি বিন্দুর দূরত্ব কেন্দ্র থেকে $R$। কেন্দ্রে রিংয়ের মহাকর্ষীয় প্রাবল্য $dE = \frac{G \sigma dA}{R^2}\cos\theta = \frac{G \sigma (2\pi R^2 \sin\theta d\theta)}{R^2}\cos\theta = 2\pi G \sigma \sin\theta\cos\theta d\theta = \pi G \sigma \sin(2\theta)d\theta$। সমগ্র অর্ধগোলকের জন্য সমাকলন করি ($0 \le \theta \le \pi/2$): $E = \pi G \sigma \int_0^{\pi/2}\sin(2\theta)d\theta = \pi G \sigma \left[ -\frac{\cos(2\theta)}{2} +ight]_0^{\pi/2} = \pi G \sigma \left(\frac{1}{2} - \left(-\frac{1}{2} ight)-ight) = \pi G \sigma$। যেহেতু অর্ধগোলকের মোট ভর $M = 2\pi R^2 \sigma \implies \sigma = rac{M}{2\pi R^2}$, সেহেতু $E = \pi G \left(rac{M}{2\pi R^2}-ight) = rac{G M}{2R^2}$।</t>
+ight) = \pi G \sigma$। যেহেতু অর্ধগোলকের মোট ভর $M = 2\pi R^2 \sigma \implies \sigma = \frac{M}{2\pi R^2}$, সেহেতু $E = \pi G \left(\frac{M}{2\pi R^2}+ight) = \frac{G M}{2R^2}$।</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1370,17 +1340,12 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>ক্যাভেন্ডিশের পরীক্ষায় $L$ দৈর্ঘ্যের একটি হালকা দণ্ডের দুই প্রান্তে দুটি ছোট সীসার গোলক (প্রতিটির ভর $m$) আটকানো। তাদের কাছে দুটি ভারী গোলক (প্রতিটির ভর $M$) $d$ দূরত্বে আনলে তারের টরশন কোণ $	heta$ হয়। তারের টরশন ধ্রুবক $C$ হলে মহাকর্ষীয় ধ্রুবক $G$-এর সূত্র প্রতিপাদন কর।</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>None</t>
+          <t>ক্যাভেন্ডিশের পরীক্ষায় $L$ দৈর্ঘ্যের একটি হালকা দণ্ডের দুই প্রান্তে দুটি ছোট সীসার গোলক (প্রতিটির ভর $m$) আটকানো। তাদের কাছে দুটি ভারী গোলক (প্রতিটির ভর $M$) $d$ দূরত্বে আনলে তারের টরশন কোণ $\theta$ হয়। তারের টরশন ধ্রুবক $C$ হলে মহাকর্ষীয় ধ্রুবক $G$-এর সূত্র প্রতিপাদন কর।</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>প্রতিটি ছোট গোলকের ওপর ভারী গোলক কর্তৃক মহাকর্ষীয় বল $F = rac{GMm}{d^2}$। দণ্ডের কেন্দ্র সাপেক্ষে এই দুটি সমান ও বিপরীতমুখী বলের যুগল বা টর্ক $	au_{	ext{grav}} = F L = rac{GMm L}{d^2}$। এই টর্ক তারের স্থিতিস্থাপক প্রত্যয়নী টর্ক $	au_{	ext{restoring}} = C 	heta$-এর সাথে ভারসাম্য রক্ষা করে। সাম্যাবস্থায়: $rac{GMm L}{d^2} = C 	heta \implies G = rac{C 	heta d^2}{M m L}$। দণ্ডের দোলন পর্যায়কাল $T = 2\pi\sqrt{rac{I}{C}}$ (যেখানে $I = 2m(L/2)^2 = rac{1}{2}mL^2$) থেকে $C = rac{4\pi^2 I}{T^2}$ নির্ণয় করে $G$-এর অত্যন্ত সূক্ষ্ম মান পরিমাপ করা হয়।</t>
+          <t>প্রতিটি ছোট গোলকের ওপর ভারী গোলক কর্তৃক মহাকর্ষীয় বল $F = \frac{GMm}{d^2}$। দণ্ডের কেন্দ্র সাপেক্ষে এই দুটি সমান ও বিপরীতমুখী বলের যুগল বা টর্ক $\tau_{\text{grav}} = F L = \frac{GMm L}{d^2}$। এই টর্ক তারের স্থিতিস্থাপক প্রত্যয়নী টর্ক $\tau_{\text{restoring}} = C \theta$-এর সাথে ভারসাম্য রক্ষা করে। সাম্যাবস্থায়: $\frac{GMm L}{d^2} = C \theta \implies G = \frac{C \theta d^2}{M m L}$। দণ্ডের দোলন পর্যায়কাল $T = 2\pi\sqrt{\frac{I}{C}}$ (যেখানে $I = 2m(L/2)^2 = \frac{1}{2}mL^2$) থেকে $C = \frac{4\pi^2 I}{T^2}$ নির্ণয় করে $G$-এর অত্যন্ত সূক্ষ্ম মান পরিমাপ করা হয়।</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1423,15 +1388,10 @@
           <t>$m$ ভরের তিনটি সমান কণা মহাকর্ষীয় আকর্ষণের অধীনে পরস্পরের সাথে $a$ বাহুবিশিষ্ট সমবাহু ত্রিভুজ গঠন করে একটি সাধারণ কেন্দ্রের চারদিকে সমদ্রুতিতে ঘুরছে। কণাগুলোর সাধারণ কৌণিক বেগ $\omega$ এবং পর্যায়কাল $T$ নির্ণয় কর।</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>যেকোনো একটি কণার ওপর অপর দুটি কণা কর্তৃক আকর্ষণ বলের মান $F_0 = rac{Gm^2}{a^2}$। তাদের মধ্যবর্তী কোণ $60^\circ$। লব্ধি বল ত্রিভুজের ভরকেন্দ্রের অভিমুখী এবং এর মান $F_{	ext{net}} = \sqrt{F_0^2 + F_0^2 + 2F_0^2\cos 60^\circ} = \sqrt{3}F_0 = rac{\sqrt{3}Gm^2}{a^2}$। ভরকেন্দ্র থেকে প্রতিটি শীর্ষবিন্দুর দূরত্ব $R = rac{a}{\sqrt{3}}$। কণাটির কেন্দ্রমুখী বলের সাথে সমতা করি: $F_{	ext{net}} = m\omega^2 R \implies rac{\sqrt{3}Gm^2}{a^2} = m\omega^2 \left(rac{a}{\sqrt{3}}-ight) \implies \omega^2 = rac{3Gm}{a^3} \implies \omega = \sqrt{rac{3Gm}{a^3}}$। পর্যায়কাল $T = rac{2\pi}{\omega} = 2\pi\sqrt{rac{a^3}{3Gm}}$।</t>
+          <t>যেকোনো একটি কণার ওপর অপর দুটি কণা কর্তৃক আকর্ষণ বলের মান $F_0 = \frac{Gm^2}{a^2}$। তাদের মধ্যবর্তী কোণ $60^\circ$। লব্ধি বল ত্রিভুজের ভরকেন্দ্রের অভিমুখী এবং এর মান $F_{\text{net}} = \sqrt{F_0^2 + F_0^2 + 2F_0^2\cos 60^\circ} = \sqrt{3}F_0 = \frac{\sqrt{3}Gm^2}{a^2}$। ভরকেন্দ্র থেকে প্রতিটি শীর্ষবিন্দুর দূরত্ব $R = \frac{a}{\sqrt{3}}$। কণাটির কেন্দ্রমুখী বলের সাথে সমতা করি: $F_{\text{net}} = m\omega^2 R \implies \frac{\sqrt{3}Gm^2}{a^2} = m\omega^2 \left(\frac{a}{\sqrt{3}}+ight) \implies \omega^2 = \frac{3Gm}{a^3} \implies \omega = \sqrt{\frac{3Gm}{a^3}}$। পর্যায়কাল $T = \frac{2\pi}{\omega} = 2\pi\sqrt{\frac{a^3}{3Gm}}$।</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1474,18 +1434,13 @@
           <t>$m$ ভরের চারটি সমান কণা একটি $a$ বাহুবিশিষ্ট বর্গক্ষেত্রের চার শীর্ষে অবস্থান করে নিজেদের পারস্পরিক মহাকর্ষীয় টানে বর্গাকার আকৃতি বজায় রেখে ঘুরছে। প্রতিটি কণার রৈখিক গতিবেগ $v$ নির্ণয় কর।</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>একটি কণার ওপর অপর তিনটি কণার আকর্ষণ বল: সন্নিহিত দুই কণার বল $F_1 = rac{Gm^2}{a^2}$ (পরস্পর সমকোণে), যাদের লব্ধি $\sqrt{2}F_1 = \sqrt{2}rac{Gm^2}{a^2}$ কেন্দ্রের দিকে। কর্ণের বিপরীত কণার দূরত্ব $\sqrt{2}a$, ফলে এর বল $F_2 = rac{Gm^2}{(\sqrt{2}a)^2} = rac{Gm^2}{2a^2}$ কেন্দ্রের দিকে। মোট অন্তর্মুখী বল $F_{	ext{net}} = rac{Gm^2}{a^2}\left(\sqrt{2} + rac{1}{2}-ight) = rac{Gm^2}{a^2}\left(rac{2\sqrt{2}+1}{2}-ight)$। কেন্দ্র থেকে শীর্ষের দূরত্ব $R = rac{a}{\sqrt{2}}$। কেন্দ্রমুখী বলের সমীকরণ: $rac{m v^2}{R} = F_{	ext{net}} \implies rac{m v^2}{a/\sqrt{2}} = rac{Gm^2}{a^2}rac{2\sqrt{2}+1}{2} \implies v^2 = rac{Gm}{a}\left(1 + rac{1}{2\sqrt{2}}-ight) = rac{Gm}{a}\left(rac{4+\sqrt{2}}{4}-ight)$। অতএব $v = \sqrt{rac{Gm}{a}\left(rac{4+\sqrt{2}}{4}+          <t>একটি কণার ওপর অপর তিনটি কণার আকর্ষণ বল: সন্নিহিত দুই কণার বল $F_1 = \frac{Gm^2}{a^2}$ (পরস্পর সমকোণে), যাদের লব্ধি $\sqrt{2}F_1 = \sqrt{2}\frac{Gm^2}{a^2}$ কেন্দ্রের দিকে। কর্ণের বিপরীত কণার দূরত্ব $\sqrt{2}a$, ফলে এর বল $F_2 = \frac{Gm^2}{(\sqrt{2}a)^2} = \frac{Gm^2}{2a^2}$ কেন্দ্রের দিকে। মোট অন্তর্মুখী বল $F_{\text{net}} = \frac{Gm^2}{a^2}\left(\sqrt{2} + \frac{1}{2}+ight) = \frac{Gm^2}{a^2}\left(\frac{2\sqrt{2}+1}{2}+ight)$। কেন্দ্র থেকে শীর্ষের দূরত্ব $R = \frac{a}{\sqrt{2}}$। কেন্দ্রমুখী বলের সমীকরণ: $\frac{m v^2}{R} = F_{\text{net}} \implies \frac{m v^2}{a/\sqrt{2}} = \frac{Gm^2}{a^2}\frac{2\sqrt{2}+1}{2} \implies v^2 = \frac{Gm}{a}\left(1 + \frac{1}{2\sqrt{2}}+ight) = \frac{Gm}{a}\left(\frac{4+\sqrt{2}}{4}+ight)$। অতএব $v = \sqrt{\frac{Gm}{a}\left(\frac{4+\sqrt{2}}{4} ight)}$।</t>
         </is>
       </c>
@@ -1529,22 +1484,17 @@
           <t>$R$ ব্যাসার্ধ ও $M$ ভরের একটি সুষম অসংকোচনীয় তরল গোলকের স্ব-মহাকর্ষের কারণে তার কেন্দ্রে সৃষ্ট হাইড্রোস্ট্যাটিক চাপ $P_c$ নির্ণয় কর।</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>হাইড্রোস্ট্যাটিক ভারসাম্যের সমীকরণ: $rac{dP}{dr} = --ho g(r)$। সুষম ঘনত্বের ক্ষেত্রে কেন্দ্র থেকে $r$ দূরত্বের ভেতর আবদ্ধ ভর $M(r) = rac{M}{R^3}r^3$। ফলে ক্ষেত্র প্রাবল্য $g(r) = rac{G M(r)}{r^2} = rac{GM}{R^3}r$। সমাকলন করি পৃষ্ঠ ($P(R)=0$) থেকে কেন্দ্র ($P(0)=P_c$) পর্যন্ত: $\int_{P_c}^0 dP = -\int_0^R -ho \left(rac{GM}{R^3}r-ight)dr \implies -P_c = -rac{G M -ho}{R^3}\left[rac{r^2}{2}-ight]_0^R = -rac{G M +          <t>হাইড্রোস্ট্যাটিক ভারসাম্যের সমীকরণ: $\frac{dP}{dr} = -+ho g(r)$। সুষম ঘনত্বের ক্ষেত্রে কেন্দ্র থেকে $r$ দূরত্বের ভেতর আবদ্ধ ভর $M(r) = \frac{M}{R^3}r^3$। ফলে ক্ষেত্র প্রাবল্য $g(r) = \frac{G M(r)}{r^2} = \frac{GM}{R^3}r$। সমাকলন করি পৃষ্ঠ ($P(R)=0$) থেকে কেন্দ্র ($P(0)=P_c$) পর্যন্ত: $\int_{P_c}^0 dP = -\int_0^R +ho \left(\frac{GM}{R^3}r+ight)dr \implies -P_c = -\frac{G M +ho}{R^3}\left[\frac{r^2}{2}+ight]_0^R = -\frac{G M  ho}{2R}$। ঘনত্ব $-ho = rac{3M}{4\pi R^3}$ বসিয়ে পাই: $P_c = rac{GM}{2R}\left(rac{3M}{4\pi R^3}-ight) = rac{3GM^2}{8\pi R^4}$।</t>
+ho = \frac{3M}{4\pi R^3}$ বসিয়ে পাই: $P_c = \frac{GM}{2R}\left(\frac{3M}{4\pi R^3}+ight) = \frac{3GM^2}{8\pi R^4}$।</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1584,20 +1534,15 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>মহাকর্ষীয় ক্ষেত্রের জন্য গাউসের ফ্লাক্স উপপাদ্য $\oint ec{g}\cdot dec{A} = -4\pi G M_{	ext{enc}}$ বিবৃত কর এবং এর ব্যবকলনীয় রূপ (পয়সনের সমীকরণ $
+          <t>মহাকর্ষীয় ক্ষেত্রের জন্য গাউসের ফ্লাক্স উপপাদ্য $\oint ec{g}\cdot dec{A} = -4\pi G M_{\text{enc}}$ বিবৃত কর এবং এর ব্যবকলনীয় রূপ (পয়সনের সমীকরণ $
 abla^2 V = 4\pi G  ho$) প্রতিপাদন কর।</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>কোনো আবদ্ধ তল $S$-এর মধ্য দিয়ে অতিক্রান্ত মোট মহাকর্ষীয় ফ্লাক্স হলো তলের অভ্যন্তরে আবদ্ধ মোট ভরের $-4\pi G$ গুণ: $\Phi_g = \oint_S ec{g}\cdot dec{A} = -4\pi G M_{	ext{enc}}$। ডাইভারজেন্স উপপাদ্য প্রয়োগ করে: $\oint_S ec{g}\cdot dec{A} = \iiint_V (ec{
-abla}\cdotec{g})dV$। আবার আবদ্ধ ভর $M_{	ext{enc}} = \iiint_V +          <t>কোনো আবদ্ধ তল $S$-এর মধ্য দিয়ে অতিক্রান্ত মোট মহাকর্ষীয় ফ্লাক্স হলো তলের অভ্যন্তরে আবদ্ধ মোট ভরের $-4\pi G$ গুণ: $\Phi_g = \oint_S ec{g}\cdot dec{A} = -4\pi G M_{\text{enc}}$। ডাইভারজেন্স উপপাদ্য প্রয়োগ করে: $\oint_S ec{g}\cdot dec{A} = \iiint_V (ec{
+abla}\cdotec{g})dV$। আবার আবদ্ধ ভর $M_{\text{enc}} = \iiint_V  ho dV$। ফলে $\iiint_V (ec{
 abla}\cdotec{g} + 4\pi G  ho)dV = 0$। যেকোনো আয়তনের জন্য এটি সত্য হওয়ায় ব্যবকলনীয় রূপ $ec{
@@ -1652,14 +1597,9 @@
           <t>নিউটনের শেল উপপাদ্য ব্যবহার করে প্রমাণ কর যে সুষম ঘনত্বের একটি পাতলা ফাঁপা গোলকের অভ্যন্তরীণ যেকোনো বিন্দুতে মহাকর্ষীয় ক্ষেত্র প্রাবল্য ঠিক শূন্য এবং গোলকের বাইরের যে কোনো বিন্দুতে সম্পূর্ণ ভর কেন্দ্রে পুঞ্জীভূত বিন্দুর মতো আচরণ করে।</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>ধরা যাক $R$ ব্যাসার্ধ ও $M$ ভরের একটি পাতলা গোলকীয় খোলস। (১) অভ্যন্তরীণ বিন্দুর জন্য ($r &lt; R$): $r$ ব্যাসার্ধের একটি সমকেন্দ্রিক গাউসীয় গোলক কল্পনা করি। এই তলের অভ্যন্তরে কোনো ভর নেই, ফলে $M_{	ext{enc}} = 0$। গাউসের সূত্রানুসারে $g(4\pi r^2) = -4\pi G (0) \implies g_{	ext{inside}} = 0$। ফলে ফাঁপা গোলকের ভেতরে কোনো মহাকর্ষ বল থাকে না। (২) বহিস্থ বিন্দুর জন্য ($r &gt; R$): $r$ ব্যাসার্ধের গাউসীয় তল সম্পূর্ণ খোলসটিকে আবদ্ধ করে, ফলে $M_{	ext{enc}} = M$। গাউসের সূত্র: $g(4\pi r^2) = -4\pi G M \implies g_{	ext{outside}} = -rac{GM}{r^2}\hat{r}$, যা সম্পূর্ণ ভর কেন্দ্রে রাখা একটি বিন্দু ভরের ক্ষেত্রের হুবহু সমান।</t>
+          <t>ধরা যাক $R$ ব্যাসার্ধ ও $M$ ভরের একটি পাতলা গোলকীয় খোলস। (১) অভ্যন্তরীণ বিন্দুর জন্য ($r &lt; R$): $r$ ব্যাসার্ধের একটি সমকেন্দ্রিক গাউসীয় গোলক কল্পনা করি। এই তলের অভ্যন্তরে কোনো ভর নেই, ফলে $M_{\text{enc}} = 0$। গাউসের সূত্রানুসারে $g(4\pi r^2) = -4\pi G (0) \implies g_{\text{inside}} = 0$। ফলে ফাঁপা গোলকের ভেতরে কোনো মহাকর্ষ বল থাকে না। (২) বহিস্থ বিন্দুর জন্য ($r &gt; R$): $r$ ব্যাসার্ধের গাউসীয় তল সম্পূর্ণ খোলসটিকে আবদ্ধ করে, ফলে $M_{\text{enc}} = M$। গাউসের সূত্র: $g(4\pi r^2) = -4\pi G M \implies g_{\text{outside}} = -\frac{GM}{r^2}\hat{r}$, যা সম্পূর্ণ ভর কেন্দ্রে রাখা একটি বিন্দু ভরের ক্ষেত্রের হুবহু সমান।</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1702,15 +1642,10 @@
           <t>পৃথিবীর ভেতর দিয়ে কেন্দ্রগামী নয় এমন যেকোনো দুটি বিন্দুর মাঝে একটি সোজা ঘর্ষণহীন সুড়ঙ্গ খনন করা হলো। সুড়ঙ্গের এক প্রান্তে একটি বস্তুকে ছেড়ে দিলে তার গতির সমীকরণ গঠন কর এবং প্রমাণ কর যে সুড়ঙ্গটি কেন্দ্র দিয়ে যাক বা না যাক, তার পর্যায়কাল সর্বদা ধ্রুব থাকে।</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>পৃথিবীর কেন্দ্রকে মূলবিন্দু ধরি এবং সুড়ঙ্গের মধ্যবিন্দু থেকে কেন্দ্র পর্যন্ত লম্ব দূরত্ব $d$। সুড়ঙ্গ বরাবর স্থানাঙ্ক $x$ হলে কেন্দ্র থেকে কণার দূরত্ব $r = \sqrt{x^2 + d^2}$। পৃথিবীর ভেতরে মহাকর্ষীয় বল সর্বদা কেন্দ্রের দিকে এবং এর মান $F = rac{GMm}{R^3}r$। সুড়ঙ্গ বরাবর বলের উপাংশ $F_x = -F\cos	heta = -\left(rac{GMm}{R^3}r-ight)rac{x}{r} = -rac{GMm}{R^3}x$। নিউটনের দ্বিতীয় সূত্র: $m\ddot{x} = -rac{GMm}{R^3}x \implies \ddot{x} + rac{GM}{R^3}x = 0$। এটি একটি নিখুঁত সরল ছন্দিত স্পন্দন যার কৌণিক কম্পাঙ্ক $\omega = \sqrt{rac{GM}{R^3}} = \sqrt{rac{g}{R}}$ ধ্রুবক। পর্যায়কাল $T = 2\pi\sqrt{rac{R}{g}} pprox 84.6	ext{ মিনিট}$। এটি কেন্দ্র থেকে সুড়ঙ্গের দূরত্ব $d$-এর ওপর সম্পূর্ণ স্বাধীন।</t>
+          <t>পৃথিবীর কেন্দ্রকে মূলবিন্দু ধরি এবং সুড়ঙ্গের মধ্যবিন্দু থেকে কেন্দ্র পর্যন্ত লম্ব দূরত্ব $d$। সুড়ঙ্গ বরাবর স্থানাঙ্ক $x$ হলে কেন্দ্র থেকে কণার দূরত্ব $r = \sqrt{x^2 + d^2}$। পৃথিবীর ভেতরে মহাকর্ষীয় বল সর্বদা কেন্দ্রের দিকে এবং এর মান $F = \frac{GMm}{R^3}r$। সুড়ঙ্গ বরাবর বলের উপাংশ $F_x = -F\cos\theta = -\left(\frac{GMm}{R^3}r+ight)\frac{x}{r} = -\frac{GMm}{R^3}x$। নিউটনের দ্বিতীয় সূত্র: $m\ddot{x} = -\frac{GMm}{R^3}x \implies \ddot{x} + \frac{GM}{R^3}x = 0$। এটি একটি নিখুঁত সরল ছন্দিত স্পন্দন যার কৌণিক কম্পাঙ্ক $\omega = \sqrt{\frac{GM}{R^3}} = \sqrt{\frac{g}{R}}$ ধ্রুবক। পর্যায়কাল $T = 2\pi\sqrt{\frac{R}{g}} pprox 84.6\text{ মিনিট}$। এটি কেন্দ্র থেকে সুড়ঙ্গের দূরত্ব $d$-এর ওপর সম্পূর্ণ স্বাধীন।</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1752,25 +1687,20 @@
         <is>
           <t>একটি গ্রহের ঘনত্ব ব্যাসার্ধের সাথে পরিবর্তিত হয়: $ ho(r) = -ho_0 \left(1 - rac{r}{R}+ho_0 \left(1 - \frac{r}{R} ight)$ (যেখানে $0 \le r \le R$)। কেন্দ্র থেকে দূরত্বের অপেক্ষক হিসেবে অভিকর্ষজ ত্বরণ $g(r)$ নির্ণয় কর এবং কোন গভীরতায় ত্বরণ সর্বাধিক হবে?</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
           <t>কেন্দ্র থেকে $r$ দূরত্বের গোলকের ভেতরে আবদ্ধ ভর: $M(r) = \int_0^r  ho(r') 4\pi r'^2 dr' = 4\pi-ho_0 \int_0^r \left(r'^2 - rac{r'^3}{R}+ho_0 \int_0^r \left(r'^2 - \frac{r'^3}{R} ight)dr' = 4\pi-ho_0 \left[rac{r^3}{3} - rac{r^4}{4R}-ight]$। মহাকর্ষীয় ক্ষেত্র প্রাবল্য $g(r) = rac{G M(r)}{r^2} = 4\pi G -ho_0 \left(rac{r}{3} - rac{r^2}{4R}-ight)$। ত্বরণ সর্বাধিক হওয়ার শর্ত $rac{dg}{dr} = 0 \implies rac{1}{3} - rac{2r}{4R} = 0 \implies rac{r}{2R} = rac{1}{3} \implies r = rac{2}{3}R$। অর্থাৎ কেন্দ্র থেকে $rac{2}{3}R$ দূরত্বে (বা পৃষ্ঠ থেকে $R/3$ গভীরতায়) ত্বরণ সর্বাধিক হবে।</t>
+ho_0 \left[\frac{r^3}{3} - \frac{r^4}{4R}+ight]$। মহাকর্ষীয় ক্ষেত্র প্রাবল্য $g(r) = \frac{G M(r)}{r^2} = 4\pi G +ho_0 \left(\frac{r}{3} - \frac{r^2}{4R}+ight)$। ত্বরণ সর্বাধিক হওয়ার শর্ত $\frac{dg}{dr} = 0 \implies \frac{1}{3} - \frac{2r}{4R} = 0 \implies \frac{r}{2R} = \frac{1}{3} \implies r = \frac{2}{3}R$। অর্থাৎ কেন্দ্র থেকে $\frac{2}{3}R$ দূরত্বে (বা পৃষ্ঠ থেকে $R/3$ গভীরতায়) ত্বরণ সর্বাধিক হবে।</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1814,17 +1744,12 @@
 ho$। গাউসের মহাকর্ষীয় উপপাদ্য প্রয়োগ করে সিলিন্ডারের অভ্যন্তরে ($r &lt; R$) এবং বাইরে ($r &gt; R$) মহাকর্ষীয় প্রাবল্য নির্ণয় কর।</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>$L$ দৈর্ঘ্যের সমকেন্দ্রিক সিলিন্ডারীয় গাউসীয় তল বিবেচনা করি। বৃত্তাকার প্রান্তদ্বয়ে ফ্লাক্স শূন্য। পার্শ্বতলের ক্ষেত্রফল $2\pi r L$। (১) বাইরে ($r &gt; R$): আবদ্ধ ভর $M_{	ext{enc}} = +          <t>$L$ দৈর্ঘ্যের সমকেন্দ্রিক সিলিন্ডারীয় গাউসীয় তল বিবেচনা করি। বৃত্তাকার প্রান্তদ্বয়ে ফ্লাক্স শূন্য। পার্শ্বতলের ক্ষেত্রফল $2\pi r L$। (১) বাইরে ($r &gt; R$): আবদ্ধ ভর $M_{\text{enc}} =  ho \pi R^2 L$। গাউসের সূত্র: $g(2\pi r L) = -4\pi G (-ho \pi R^2 L) \implies g(r) = -rac{2G(-ho \pi R^2)}{r} = -rac{2G\lambda}{r}$ (দূরত্বের ব্যস্তানুপাতিক)। (২) ভেতরে ($r &lt; R$): আবদ্ধ ভর $M_{	ext{enc}} = +ho \pi R^2 L) \implies g(r) = -\frac{2G(+ho \pi R^2)}{r} = -\frac{2G\lambda}{r}$ (দূরত্বের ব্যস্তানুপাতিক)। (২) ভেতরে ($r &lt; R$): আবদ্ধ ভর $M_{\text{enc}} =  ho \pi r^2 L$। গাউসের সূত্র: $g(2\pi r L) = -4\pi G ( ho \pi r^2 L) \implies g(r) = -2\pi G  ho r$ (দূরত্বের সমানুপাতিক)।</t>
@@ -1870,15 +1795,10 @@
           <t>$R$ ব্যাসার্ধের একটি সুষম নিরেট গোলকের ভেতর দুটি সমান ব্যাসার্ধের ($R/4$) গোলকীয় গহ্বর তৈরি করা হলো যাদের কেন্দ্র যথাক্রমে $(R/2, 0, 0)$ এবং $(-R/2, 0, 0)$ বিন্দুতে অবস্থিত। $(0, 2R, 0)$ বিন্দুতে রাখা $m$ ভরের কণার ওপর লব্ধি মহাকর্ষীয় বল কত?</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>উপরিফাতন নীতি অনুসারে: লব্ধি বল = সম্পূর্ণ গোলকের বল ($F_0$) - প্রথম গহ্বরের বল ($F_1$) - দ্বিতীয় গহ্বরের বল ($F_2$)। সম্পূর্ণ গোলকের ভর $M$, কেন্দ্র $(0,0,0)$ থেকে কণার দূরত্ব $2R$, ফলে $F_0 = rac{GMm}{(2R)^2} = rac{GMm}{4R^2}$ (-$y$ দিকে)। প্রতিটি গহ্বরের আয়তন মূল গোলকের $(1/4)^3 = 1/64$ গুণ, ফলে প্রতিটি গহ্বরের ভর $M/64$। গহ্বরদ্বয়ের অবস্থান $(\pm R/2, 0)$ থেকে কণার দূরত্বের বর্গ $d^2 = (R/2)^2 + (2R)^2 = rac{R^2}{4} + 4R^2 = rac{17}{4}R^2$। প্রতিসাম্যের কারণে $x$-উপাংশদ্বয় বাতিল হয়। $y$-বরাবর প্রতিটি গহ্বরের উপাংশ $F_{1y} = rac{G(M/64)m}{17R^2/4}rac{2R}{\sqrt{17}/2 R} = rac{GMm}{R^2}rac{16}{64 	imes 17\sqrt{17}} = rac{GMm}{R^2}rac{1}{68\sqrt{17}}$। দুটি গহ্বরের জন্য লব্ধি বল $F_y = rac{GMm}{4R^2} - 2\left(rac{GMm}{68\sqrt{17}R^2}-ight) = rac{GMm}{R^2}\left(rac{1}{4} - rac{1}{34\sqrt{17}}+          <t>উপরিফাতন নীতি অনুসারে: লব্ধি বল = সম্পূর্ণ গোলকের বল ($F_0$) - প্রথম গহ্বরের বল ($F_1$) - দ্বিতীয় গহ্বরের বল ($F_2$)। সম্পূর্ণ গোলকের ভর $M$, কেন্দ্র $(0,0,0)$ থেকে কণার দূরত্ব $2R$, ফলে $F_0 = \frac{GMm}{(2R)^2} = \frac{GMm}{4R^2}$ (-$y$ দিকে)। প্রতিটি গহ্বরের আয়তন মূল গোলকের $(1/4)^3 = 1/64$ গুণ, ফলে প্রতিটি গহ্বরের ভর $M/64$। গহ্বরদ্বয়ের অবস্থান $(\pm R/2, 0)$ থেকে কণার দূরত্বের বর্গ $d^2 = (R/2)^2 + (2R)^2 = \frac{R^2}{4} + 4R^2 = \frac{17}{4}R^2$। প্রতিসাম্যের কারণে $x$-উপাংশদ্বয় বাতিল হয়। $y$-বরাবর প্রতিটি গহ্বরের উপাংশ $F_{1y} = \frac{G(M/64)m}{17R^2/4}\frac{2R}{\sqrt{17}/2 R} = \frac{GMm}{R^2}\frac{16}{64 \times 17\sqrt{17}} = \frac{GMm}{R^2}\frac{1}{68\sqrt{17}}$। দুটি গহ্বরের জন্য লব্ধি বল $F_y = \frac{GMm}{4R^2} - 2\left(\frac{GMm}{68\sqrt{17}R^2}+ight) = \frac{GMm}{R^2}\left(\frac{1}{4} - \frac{1}{34\sqrt{17}} ight)$।</t>
         </is>
       </c>
@@ -1919,18 +1839,13 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>আইনস্টাইনের চতুর্ধ্রুবক সূত্র (Einstein's Quadrupole Formula) অনুসারে দুটি পরিক্রমণশীল নক্ষত্র দ্বারা মহাকর্ষীয় তরঙ্গের মাধ্যমে বিকিরিত ক্ষমতা $P = rac{32 G}{5 c^5} \mu^2 r^4 \omega^6$। কেন মহাকর্ষীয় দ্বিমেরু (Dipole) বিকিরণ অসম্ভব?</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>None</t>
+          <t>আইনস্টাইনের চতুর্ধ্রুবক সূত্র (Einstein's Quadrupole Formula) অনুসারে দুটি পরিক্রমণশীল নক্ষত্র দ্বারা মহাকর্ষীয় তরঙ্গের মাধ্যমে বিকিরিত ক্ষমতা $P = \frac{32 G}{5 c^5} \mu^2 r^4 \omega^6$। কেন মহাকর্ষীয় দ্বিমেরু (Dipole) বিকিরণ অসম্ভব?</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
           <t>তড়িৎচৌম্বকীয় তরঙ্গে আধান-ভর অনুপাতের পার্থক্যের কারণে বৈদ্যুতিক দ্বিমেরু বিকিরণ সম্ভব হয় ($\ddot{ec{d}} 
-eq 0$)। কিন্তু মহাকর্ষে ভরই মহাকর্ষীয় আধানের ভূমিকা পালন করে, ফলে সমতা নীতির (Equivalence Principle) কারণে ভরকেন্দ্রের দ্বিতীয় অন্তরক ভরবেগ সংরক্ষণের সাথে আবদ্ধ: $ec{d}_{	ext{grav}} = \sum m_i ec{r}_i = M ec{r}_{	ext{cm}}$। ভরবেগ সংরক্ষিত থাকায় $\ddot{ec{d}}_{	ext{grav}} = rac{dec{P}}{dt} = 0$ (বাহ্যিক বল শূন্য)। ফলে মহাকর্ষীয় দ্বিমেরু বিকিরণ কঠোরভাবে শূন্য। সর্বনিম্ন ক্রমের মহাকর্ষীয় বিকিরণ শুরু হয় ভর চতুর্ধ্রুবক (Mass Quadrupole) ভ্রামকের তৃতীয় অন্তরকের বর্গের মাধ্যমে।</t>
+eq 0$)। কিন্তু মহাকর্ষে ভরই মহাকর্ষীয় আধানের ভূমিকা পালন করে, ফলে সমতা নীতির (Equivalence Principle) কারণে ভরকেন্দ্রের দ্বিতীয় অন্তরক ভরবেগ সংরক্ষণের সাথে আবদ্ধ: $ec{d}_{\text{grav}} = \sum m_i ec{r}_i = M ec{r}_{\text{cm}}$। ভরবেগ সংরক্ষিত থাকায় $\ddot{ec{d}}_{\text{grav}} = \frac{dec{P}}{dt} = 0$ (বাহ্যিক বল শূন্য)। ফলে মহাকর্ষীয় দ্বিমেরু বিকিরণ কঠোরভাবে শূন্য। সর্বনিম্ন ক্রমের মহাকর্ষীয় বিকিরণ শুরু হয় ভর চতুর্ধ্রুবক (Mass Quadrupole) ভ্রামকের তৃতীয় অন্তরকের বর্গের মাধ্যমে।</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1974,11 +1889,6 @@
 ho^{1 + 1/n}$। হাইড্রোস্ট্যাটিক ভারসাম্য ও পয়সনের সমীকরণ সমন্বয় করে লেন-এমডেন (Lane-Emden) সমীকরণের সার্বজনীন রূপ ব্যাখ্যা কর।</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I19" t="inlineStr">
         <is>
           <t>হাইড্রোস্ট্যাটিক সমীকরণ $\frac{1}{\rho}\frac{dP}{dr} = -\frac{d\Phi}{dr}$ এবং গোলকীয় স্থানাঙ্কে পয়সনের সমীকরণ $\frac{1}{r^2}\frac{d}{dr}\left(r^2 \frac{d\Phi}{dr}\right) = 4\pi G \rho$। দুটিকে সমন্বয় করলে পাওয়া যায় $\frac{1}{r^2}\frac{d}{dr}\left(\frac{r^2}{\rho}\frac{dP}{dr}\right) = -4\pi G \rho$। ঘনত্বকে মাত্রাহীন চলকে রূপান্তর করে $\rho = \rho_c \theta^n$ এবং ব্যাসার্ধকে $r = \alpha \xi$ ধরলে লেন-এমডেন সমীকরণ দাঁড়ায়: $\frac{1}{\xi^2}\frac{d}{d\xi}\left(\xi^2 \frac{d\theta}{d\xi}\right) = -\theta^n$। $n=0$ (সুষম অসংকোচনীয় গোলক), $n=1$ এবং $n=5$-এর জন্য এর সঠিক বিশ্লেষণাত্মক সমাধান রয়েছে, যা নক্ষত্রের অভ্যন্তরীণ কাঠামো নির্ধারণের ভিত্তি।</t>
@@ -2024,11 +1934,6 @@
           <t>একটি সুষম নিরেট গোলকের পৃষ্ঠ থেকে কেন্দ্র পর্যন্ত একটি সরু সুড়ঙ্গ কাটা হলো যার ব্যাস নগণ্য। সুড়ঙ্গের ঠিক মাঝবিন্দুতে একটি ক্ষুদ্র কণা ছেড়ে দিলে কণার ওপর পার্শ্বদেয়ালের কোনো অভিলম্ব প্রতিক্রিয়া বল সৃষ্টি হবে কি?</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I20" t="inlineStr">
         <is>
           <t>সুষম গোলকের ভেতরের যেকোনো বিন্দুতে মহাকর্ষীয় বল নিখুঁতভাবে গোলকের কেন্দ্রের অভিমুখী ($ec{F} = -k ec{r}$)। যেহেতু সুড়ঙ্গটি কেন্দ্রগামী সরলরেখা বরাবর কাটা হয়েছে, সেহেতু মহাকর্ষীয় আকর্ষণ বলের সম্পূর্ণ দিকটি সুড়ঙ্গের অক্ষ বরাবর নিবদ্ধ থাকে। সুড়ঙ্গের অক্ষের লম্ব বরাবর কোনো মহাকর্ষীয় বলের উপাংশ নেই। ফলে কণাটি চলার সময় সুড়ঙ্গের কোনো পার্শ্বদেয়ালকে স্পর্শ বা চাপ প্রয়োগ করে না, অর্থাৎ পার্শ্বদেয়ালের অভিলম্ব প্রতিক্রিয়া বল নিখুঁতভাবে শূন্য থাকে।</t>
@@ -2074,14 +1979,9 @@
           <t>একটি অসীম সমতল পাতের ক্ষেত্র ঘনত্ব $\sigma$। গাউসের মহাকর্ষীয় উপপাদ্য প্রয়োগ করে পাত থেকে $z$ উচ্চতায় মহাকর্ষীয় ক্ষেত্র প্রাবল্য $g$ নির্ণয় কর।</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>পাতকে ছেদকারী $A$ প্রস্থচ্ছেদের একটি পিলবক্স (Pillbox) গাউসীয় তল বিবেচনা করি যা উভয় পাশে $z$ দূরত্ব পর্যন্ত বিস্তৃত। পিলবক্সের অভ্যন্তরে আবদ্ধ মোট ভর $M_{	ext{enc}} = \sigma A$। উভয় প্রান্ততলের ক্ষেত্রফল $2A$ এবং ফ্লাক্স অন্তর্মুখী। গাউসের সূত্র: $2 g A = 4\pi G (\sigma A) \implies g = 2\pi G \sigma$। লক্ষণীয় যে অভিকর্ষজ ক্ষেত্র প্রাবল্য $g$ পাত থেকে দূরত্বের ওপর সম্পূর্ণ নিরপেক্ষ এবং একটি সার্বজনীন ধ্রুবক।</t>
+          <t>পাতকে ছেদকারী $A$ প্রস্থচ্ছেদের একটি পিলবক্স (Pillbox) গাউসীয় তল বিবেচনা করি যা উভয় পাশে $z$ দূরত্ব পর্যন্ত বিস্তৃত। পিলবক্সের অভ্যন্তরে আবদ্ধ মোট ভর $M_{\text{enc}} = \sigma A$। উভয় প্রান্ততলের ক্ষেত্রফল $2A$ এবং ফ্লাক্স অন্তর্মুখী। গাউসের সূত্র: $2 g A = 4\pi G (\sigma A) \implies g = 2\pi G \sigma$। লক্ষণীয় যে অভিকর্ষজ ক্ষেত্র প্রাবল্য $g$ পাত থেকে দূরত্বের ওপর সম্পূর্ণ নিরপেক্ষ এবং একটি সার্বজনীন ধ্রুবক।</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -2122,7 +2022,7 @@
       <c r="G22" t="inlineStr">
         <is>
           <t>##GEO:ellipse[size:medium]##
-ভূপৃষ্ঠ থেকে একটি ক্ষুদ্র উচ্চতা $h$ ($h \ll R$) এবং সমান ক্ষুদ্র গভীরতা $d = h$-তে অভিকর্ষজ ত্বরণের পরিবর্তন ঘটে। উভয় ক্ষেত্রে $g$-এর হ্রাসের অনুপাত $rac{\Delta g_h}{\Delta g_d}$ কত?</t>
+ভূপৃষ্ঠ থেকে একটি ক্ষুদ্র উচ্চতা $h$ ($h \ll R$) এবং সমান ক্ষুদ্র গভীরতা $d = h$-তে অভিকর্ষজ ত্বরণের পরিবর্তন ঘটে। উভয় ক্ষেত্রে $g$-এর হ্রাসের অনুপাত $\frac{\Delta g_h}{\Delta g_d}$ কত?</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2132,10 +2032,10 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>ভূপৃষ্ঠে ত্বরণ $g = rac{GM}{R^2}$। (১) উচ্চতায় $h \ll R$ হলে দ্বিপদী বিস্তারে $g_h = g\left(1 + rac{h}{R}-ight)^{-2} pprox g\left(1 - rac{2h}{R}-ight)$। ত্বরণের হ্রাস $\Delta g_h = g - g_h = rac{2h}{R}g$। (২) গভীরতায় $d$ হলে সুষম ঘনত্বের গোলকের জন্য $g_d = g\left(1 - rac{d}{R}-ight)$। ত্বরণের হ্রাস $\Delta g_d = g - g_d = rac{d}{R}g$। যদি $d = h$ হয়, তবে $\Delta g_h = 2\Delta g_d$। অতএব তাদের হ্রাসের অনুপাত $rac{\Delta g_h}{\Delta g_d} = rac{2h/R}{h/R} = 2:1$। অর্থাৎ সমউচ্চতায় অভিকর্ষজ ত্বরণ সমগভীরতার দ্বিগুণ হারে হ্রাস পায়।</t>
+          <t>ভূপৃষ্ঠে ত্বরণ $g = \frac{GM}{R^2}$। (১) উচ্চতায় $h \ll R$ হলে দ্বিপদী বিস্তারে $g_h = g\left(1 + \frac{h}{R}+ight)^{-2} pprox g\left(1 - \frac{2h}{R}+ight)$। ত্বরণের হ্রাস $\Delta g_h = g - g_h = \frac{2h}{R}g$। (২) গভীরতায় $d$ হলে সুষম ঘনত্বের গোলকের জন্য $g_d = g\left(1 - \frac{d}{R}+ight)$। ত্বরণের হ্রাস $\Delta g_d = g - g_d = \frac{d}{R}g$। যদি $d = h$ হয়, তবে $\Delta g_h = 2\Delta g_d$। অতএব তাদের হ্রাসের অনুপাত $\frac{\Delta g_h}{\Delta g_d} = \frac{2h/R}{h/R} = 2:1$। অর্থাৎ সমউচ্চতায় অভিকর্ষজ ত্বরণ সমগভীরতার দ্বিগুণ হারে হ্রাস পায়।</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -2178,11 +2078,6 @@
           <t>ভূপৃষ্ঠে অভিকর্ষজ ত্বরণ $g$ হলে ঠিক কত উচ্চতায় অভিকর্ষজ ত্বরণের মান ভূপৃষ্ঠের মানের এক-চতুর্থাংশ ($g/4$) হবে? এই ক্ষেত্রে আসন্ন সূত্র কেন প্রযোজ্য নয়?</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I23" t="inlineStr">
         <is>
           <t>উচ্চতায় অভিকর্ষজ ত্বরণের নির্ভুল সূত্র $g_h = \frac{GM}{(R + h)^2} = g\frac{R^2}{(R + h)^2}$। শর্তানুসারে $g_h = \frac{g}{4} \implies \frac{R^2}{(R + h)^2} = \frac{1}{4} \implies \frac{R}{R + h} = \frac{1}{2} \implies R + h = 2R \implies h = R$। অর্থাৎ পৃথিবীর ব্যাসার্ধের সমান উচ্চতায় (প্রায় ৬৪০০ কিমি) অভিকর্ষজ ত্বরণ এক-চতুর্থাংশ হয়। আসন্ন সূত্র $g_h \approx g(1 - 2h/R)$ কেবল $h \ll R$ এর জন্য প্রযোজ্য; এখানে $h = R$ বসালে $g_h = -g$ আসে যা অবাস্তব ও অর্থহীন।</t>
@@ -2225,17 +2120,12 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>পৃথিবীর ব্যাসার্ধ $R = 6400	ext{ km}$ এবং $g = 9.8	ext{ m/s}^2$। পৃথিবীর নিজস্ব আহ্নিক ঘূর্ণনের কৌণিক বেগ $\omega$ বর্তমান মানের কত গুণ বৃদ্ধি পেলে বিষুবরেখায় অবস্থিত কোনো বস্তুর আপাত ওজন সম্পূর্ণ শূন্য (ওজনহীন) হবে?</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>None</t>
+          <t>পৃথিবীর ব্যাসার্ধ $R = 6400\text{ km}$ এবং $g = 9.8\text{ m/s}^2$। পৃথিবীর নিজস্ব আহ্নিক ঘূর্ণনের কৌণিক বেগ $\omega$ বর্তমান মানের কত গুণ বৃদ্ধি পেলে বিষুবরেখায় অবস্থিত কোনো বস্তুর আপাত ওজন সম্পূর্ণ শূন্য (ওজনহীন) হবে?</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>বিষুবরেখায় ($\lambda = 0^\circ$) বস্তুর কার্যকর অভিকর্ষজ ত্বরণ $g' = g - \omega^2 R$। ওজনহীনতার শর্ত $g' = 0 \implies \omega^2 R = g \implies \omega = \sqrt{rac{g}{R}}$। মান বসিয়ে পাই: $\omega = \sqrt{rac{9.8}{6.4 	imes 10^6}} = \sqrt{1.531 	imes 10^{-6}} pprox 1.237 	imes 10^{-3}	ext{ rad/s}$। পৃথিবীর বর্তমান আহ্নিক কৌণিক বেগ $\omega_0 = rac{2\pi}{86400} pprox 7.27 	imes 10^{-5}	ext{ rad/s}$। অনুপাত: $rac{\omega}{\omega_0} = rac{1.237 	imes 10^{-3}}{7.27 	imes 10^{-5}} pprox 17$। অর্থাৎ পৃথিবী বর্তমানের চেয়ে প্রায় ১৭ গুণ দ্রুত ঘুরলে বিষুবরেখায় ওজন শূন্য হবে এবং দিন হবে মাত্র ১.৪ ঘণ্টার।</t>
+          <t>বিষুবরেখায় ($\lambda = 0^\circ$) বস্তুর কার্যকর অভিকর্ষজ ত্বরণ $g' = g - \omega^2 R$। ওজনহীনতার শর্ত $g' = 0 \implies \omega^2 R = g \implies \omega = \sqrt{\frac{g}{R}}$। মান বসিয়ে পাই: $\omega = \sqrt{\frac{9.8}{6.4 \times 10^6}} = \sqrt{1.531 \times 10^{-6}} pprox 1.237 \times 10^{-3}\text{ rad/s}$। পৃথিবীর বর্তমান আহ্নিক কৌণিক বেগ $\omega_0 = \frac{2\pi}{86400} pprox 7.27 \times 10^{-5}\text{ rad/s}$। অনুপাত: $\frac{\omega}{\omega_0} = \frac{1.237 \times 10^{-3}}{7.27 \times 10^{-5}} pprox 17$। অর্থাৎ পৃথিবী বর্তমানের চেয়ে প্রায় ১৭ গুণ দ্রুত ঘুরলে বিষুবরেখায় ওজন শূন্য হবে এবং দিন হবে মাত্র ১.৪ ঘণ্টার।</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -2278,14 +2168,9 @@
           <t>$\lambda$ অক্ষাংশে পৃথিবীর ঘূর্ণনের কারণে আপাত অভিকর্ষজ বলের ক্রিয়া রেখা পৃথিবীর জ্যামিতিক কেন্দ্র থেকে সামান্য বিচ্যুত হয়। এই বিচ্যুতি কোণ $\delta$ (Angle of Deflection) নির্ণয় কর।</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>অক্ষাংশ $\lambda$-তে কণার ওপর দুটি বল ক্রিয়া করে: প্রকৃত মহাকর্ষীয় বল $mg$ (পৃথিবীর কেন্দ্রের দিকে) এবং কেন্দ্রাতিগ অপকেন্দ্র বল $F_c = m\omega^2 R\cos\lambda$ (ঘূর্ণন অক্ষের লম্বভাবে বাইরের দিকে)। এই দুটি বলের মধ্যবর্তী কোণ $180^\circ - \lambda$। আপাত অভিকর্ষ বল $ec{g}'$ প্রকৃত উল্লম্বের সাথে কোণ উৎপন্ন করে $	an\delta pprox rac{\omega^2 R\cos\lambda\sin\lambda}{g - \omega^2 R\cos^2\lambda} pprox rac{\omega^2 R}{2g}\sin(2\lambda)$। বিচ্যুতি কোণ সর্বাধিক হয় $\lambda = 45^\circ$-তে এবং এর মান $\delta_{\max} pprox rac{\omega^2 R}{2g} pprox rac{1}{580}	ext{ rad} pprox 0.1^\circ$ বা প্রায় ৬ আর্ক-মিনিট।</t>
+          <t>অক্ষাংশ $\lambda$-তে কণার ওপর দুটি বল ক্রিয়া করে: প্রকৃত মহাকর্ষীয় বল $mg$ (পৃথিবীর কেন্দ্রের দিকে) এবং কেন্দ্রাতিগ অপকেন্দ্র বল $F_c = m\omega^2 R\cos\lambda$ (ঘূর্ণন অক্ষের লম্বভাবে বাইরের দিকে)। এই দুটি বলের মধ্যবর্তী কোণ $180^\circ - \lambda$। আপাত অভিকর্ষ বল $ec{g}'$ প্রকৃত উল্লম্বের সাথে কোণ উৎপন্ন করে $\tan\delta pprox \frac{\omega^2 R\cos\lambda\sin\lambda}{g - \omega^2 R\cos^2\lambda} pprox \frac{\omega^2 R}{2g}\sin(2\lambda)$। বিচ্যুতি কোণ সর্বাধিক হয় $\lambda = 45^\circ$-তে এবং এর মান $\delta_{\max} pprox \frac{\omega^2 R}{2g} pprox \frac{1}{580}\text{ rad} pprox 0.1^\circ$ বা প্রায় ৬ আর্ক-মিনিট।</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2325,17 +2210,12 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>ক্লেরটের উপপাদ্য অনুসারে একটি ঘূর্ণায়মান উপবৃত্তাকার গ্রহের অক্ষাংশভিত্তিক অভিকর্ষজ ত্বরণ $g(\lambda) = g_e [1 + eta \sin^2\lambda]$ দ্বারা প্রকাশিত। মেরুতে ও বিষুবরেখায় ত্বরণের পার্থক্যের কারণসমূহ কী কী?</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>None</t>
+          <t>ক্লেরটের উপপাদ্য অনুসারে একটি ঘূর্ণায়মান উপবৃত্তাকার গ্রহের অক্ষাংশভিত্তিক অভিকর্ষজ ত্বরণ $g(\lambda) = g_e [1 + \beta \sin^2\lambda]$ দ্বারা প্রকাশিত। মেরুতে ও বিষুবরেখায় ত্বরণের পার্থক্যের কারণসমূহ কী কী?</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>মেরু ও বিষুবরেখার ত্বরণের পার্থক্যের দুটি প্রধান কারণ: (১) কেন্দ্রাতিগ বল (Centrifugal effect): বিষুবরেখায় অপকেন্দ্র ত্বরণ সর্বোচ্চ ($\omega^2 R$) এবং মেরুতে তা শূন্য। (২) পৃথিবীর উপবৃত্তাকার স্ফীতি (Oblateness): পৃথিবীর বিষুবীয় ব্যাসার্ধ মেরু ব্যাসার্ধ অপেক্ষা প্রায় ২১ কিমি বেশি। ফলে মেরু অঞ্চল পৃথিবীর কেন্দ্রের অধিক নিকটবর্তী হওয়ায় সেখানে প্রকৃত মহাকর্ষ আকর্ষণ বেশি। ক্লেরটের উপপাদ্য দেখায় যে $eta = rac{5}{2}m - f$, যেখানে $m = rac{\omega^2 a}{g_e}$ হলো কেন্দ্রাতিগ অনুপাত এবং $f = rac{a-b}{a}$ হলো পৃথিবীর চ্যাপ্টাতা (Flattening factor)।</t>
+          <t>মেরু ও বিষুবরেখার ত্বরণের পার্থক্যের দুটি প্রধান কারণ: (১) কেন্দ্রাতিগ বল (Centrifugal effect): বিষুবরেখায় অপকেন্দ্র ত্বরণ সর্বোচ্চ ($\omega^2 R$) এবং মেরুতে তা শূন্য। (২) পৃথিবীর উপবৃত্তাকার স্ফীতি (Oblateness): পৃথিবীর বিষুবীয় ব্যাসার্ধ মেরু ব্যাসার্ধ অপেক্ষা প্রায় ২১ কিমি বেশি। ফলে মেরু অঞ্চল পৃথিবীর কেন্দ্রের অধিক নিকটবর্তী হওয়ায় সেখানে প্রকৃত মহাকর্ষ আকর্ষণ বেশি। ক্লেরটের উপপাদ্য দেখায় যে $\beta = \frac{5}{2}m - f$, যেখানে $m = \frac{\omega^2 a}{g_e}$ হলো কেন্দ্রাতিগ অনুপাত এবং $f = \frac{a-b}{a}$ হলো পৃথিবীর চ্যাপ্টাতা (Flattening factor)।</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2378,17 +2258,12 @@
           <t>ভূপৃষ্ঠে সঠিক সময় দেওয়া একটি সেকেন্ড দোলককে (ক) $h$ উচ্চতার পাহাড়ের চূড়ায় এবং (খ) $d$ গভীরতার একটি খনিতে নিয়ে যাওয়া হলো। প্রতিদিন ঘড়িটি যথাক্রমে কত সময় ধীরে চলবে (Time Lost per Day)?</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>সেকেন্ড দোলকের পর্যায়কাল $T = 2\pi\sqrt{rac{L}{g}} \propto g^{-1/2}$। ব্যবকলনে পর্যায়কালের আপেক্ষিক পরিবর্তন $rac{\Delta T}{T} = -rac{1}{2}rac{\Delta g}{g}$। একদিনে মোট সময় $T_0 = 86400	ext{ s}$। একদিনে সময় হারানোর পরিমাণ $\Delta t = T_0 rac{\Delta T}{T} = rac{1}{2}\left(rac{\Delta g}{g}-ight) 86400	ext{ s}$। (ক) পাহাড়ের চূড়ায় $rac{\Delta g}{g} = rac{2h}{R}$, ফলে দৈনিক সময় হারায় $\Delta t_h = rac{1}{2}\left(rac{2h}{R}-ight) 86400 = rac{h}{R} 	imes 86400	ext{ s}$। (খ) খনিগর্ভে $rac{\Delta g}{g} = rac{d}{R}$, ফলে দৈনিক সময় হারায় $\Delta t_d = rac{1}{2}\left(rac{d}{R}-ight) 86400 = rac{d}{2R} 	imes 86400	ext{ s}$।</t>
+          <t>সেকেন্ড দোলকের পর্যায়কাল $T = 2\pi\sqrt{\frac{L}{g}} \propto g^{-1/2}$। ব্যবকলনে পর্যায়কালের আপেক্ষিক পরিবর্তন $\frac{\Delta T}{T} = -\frac{1}{2}\frac{\Delta g}{g}$। একদিনে মোট সময় $T_0 = 86400\text{ s}$। একদিনে সময় হারানোর পরিমাণ $\Delta t = T_0 \frac{\Delta T}{T} = \frac{1}{2}\left(\frac{\Delta g}{g}+ight) 86400\text{ s}$। (ক) পাহাড়ের চূড়ায় $\frac{\Delta g}{g} = \frac{2h}{R}$, ফলে দৈনিক সময় হারায় $\Delta t_h = \frac{1}{2}\left(\frac{2h}{R}+ight) 86400 = \frac{h}{R} \times 86400\text{ s}$। (খ) খনিগর্ভে $\frac{\Delta g}{g} = \frac{d}{R}$, ফলে দৈনিক সময় হারায় $\Delta t_d = \frac{1}{2}\left(\frac{d}{R}+ight) 86400 = \frac{d}{2R} \times 86400\text{ s}$।</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2431,20 +2306,15 @@
           <t>একটি কাল্পনিক গ্রহের গড় ঘনত্ব পৃথিবীর সমান কিন্তু তার ব্যাসার্ধ পৃথিবীর ব্যাসার্ধের দ্বিগুণ ($R' = 2R$) হলে, ওই গ্রহের পৃষ্ঠে অভিকর্ষজ ত্বরণ $g'$ এবং মুক্তিবেগ $v'_e$ পৃথিবীর মানের কত গুণ হবে?</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>গ্রহের ভর $M = rac{4}{3}\pi R^3 -ho$। অভিকর্ষজ ত্বরণ $g = rac{GM}{R^2} = rac{G(rac{4}{3}\pi R^3 -ho)}{R^2} = rac{4}{3}\pi G +          <t>গ্রহের ভর $M = \frac{4}{3}\pi R^3 +ho$। অভিকর্ষজ ত্বরণ $g = \frac{GM}{R^2} = \frac{G(\frac{4}{3}\pi R^3 +ho)}{R^2} = \frac{4}{3}\pi G  ho R$। যেহেতু ঘনত্ব $-ho$ অপরিবর্তিত, সেহেতু $g \propto R$। ব্যাসার্ধ দ্বিগুণ হলে $g' = 2g$। মুক্তিবেগ $v_e = \sqrt{rac{2GM}{R}} = \sqrt{2gR} = \sqrt{2\left(rac{4}{3}\pi G +ho$ অপরিবর্তিত, সেহেতু $g \propto R$। ব্যাসার্ধ দ্বিগুণ হলে $g' = 2g$। মুক্তিবেগ $v_e = \sqrt{\frac{2GM}{R}} = \sqrt{2gR} = \sqrt{2\left(\frac{4}{3}\pi G  ho R-ight)R} = R\sqrt{rac{8}{3}\pi G +ight)R} = R\sqrt{\frac{8}{3}\pi G  ho}$। সুতরাং $v_e \propto R$। ব্যাসার্ধ দ্বিগুণ হলে মুক্তিবেগও দ্বিগুণ হবে: $v'_e = 2v_e$।</t>
         </is>
       </c>
@@ -2488,14 +2358,9 @@
           <t>পৃথিবীর ভর $M$ অপরিবর্তিত রেখে কোনো কারণে তার ব্যাসার্ধ সংকুচিত হয়ে বর্তমানের অর্ধেক ($R' = R/2$) হয়ে গেলে ভূপৃষ্ঠে অভিকর্ষজ ত্বরণ এবং দিনের দৈর্ঘ্যের কী পরিবর্তন ঘটবে?</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>(১) অভিকর্ষজ ত্বরণ $g = rac{GM}{R^2}$। ভর স্থির রেখে ব্যাসার্ধ অর্ধেক হলে $g' = rac{GM}{(R/2)^2} = 4rac{GM}{R^2} = 4g$ (চারগুণ বৃদ্ধি পাবে)। (২) কৌণিক ভরবেগ সংরক্ষণশীলতা: কোনো বাহ্যিক টর্ক না থাকায় $I_1 \omega_1 = I_2 \omega_2$। জড়তার ভ্রামক $I = rac{2}{5}M R^2 \propto R^2$। ব্যাসার্ধ অর্ধেক হলে জড়তার ভ্রামক $I_2 = rac{1}{4}I_1$। ফলে কৌণিক বেগ $\omega_2 = 4\omega_1$। দিনের দৈর্ঘ্য $T = rac{2\pi}{\omega}$ হওয়ায় নতুন দিন হবে $T' = rac{T_1}{4} = rac{24	ext{ hours}}{4} = 6	ext{ hours}$।</t>
+          <t>(১) অভিকর্ষজ ত্বরণ $g = \frac{GM}{R^2}$। ভর স্থির রেখে ব্যাসার্ধ অর্ধেক হলে $g' = \frac{GM}{(R/2)^2} = 4\frac{GM}{R^2} = 4g$ (চারগুণ বৃদ্ধি পাবে)। (২) কৌণিক ভরবেগ সংরক্ষণশীলতা: কোনো বাহ্যিক টর্ক না থাকায় $I_1 \omega_1 = I_2 \omega_2$। জড়তার ভ্রামক $I = \frac{2}{5}M R^2 \propto R^2$। ব্যাসার্ধ অর্ধেক হলে জড়তার ভ্রামক $I_2 = \frac{1}{4}I_1$। ফলে কৌণিক বেগ $\omega_2 = 4\omega_1$। দিনের দৈর্ঘ্য $T = \frac{2\pi}{\omega}$ হওয়ায় নতুন দিন হবে $T' = \frac{T_1}{4} = \frac{24\text{ hours}}{4} = 6\text{ hours}$।</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2539,15 +2404,10 @@
 ho$। মালভূমির ওপর অভিকর্ষজ ত্বরণ পরিমাপ করার সময় মুক্ত বায়ুর সংশোধন (Free-air correction) এবং বোমার প্লেট সংশোধনের (Bouguer plate correction) সম্মিলিত রূপ কী?</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>উচ্চতার কারণে মুক্ত বায়ুর সংশোধন ত্বরণ কমায়: $\Delta g_{	ext{FA}} = -rac{2g}{R}h$। কিন্তু মালভূমির নিচের শিলাস্তর একটি অসীম পাতের মতো আচরণ করে অতিরিক্ত মহাকর্ষ বল যোগ করে: $\Delta g_{	ext{plate}} = +2\pi G -ho h$। অতএব মালভূমির ওপর নিট তাত্ত্বিক ত্বরণ $g_{	ext{calc}} = g_0 - rac{2g}{R}h + 2\pi G +          <t>উচ্চতার কারণে মুক্ত বায়ুর সংশোধন ত্বরণ কমায়: $\Delta g_{\text{FA}} = -\frac{2g}{R}h$। কিন্তু মালভূমির নিচের শিলাস্তর একটি অসীম পাতের মতো আচরণ করে অতিরিক্ত মহাকর্ষ বল যোগ করে: $\Delta g_{\text{plate}} = +2\pi G +ho h$। অতএব মালভূমির ওপর নিট তাত্ত্বিক ত্বরণ $g_{\text{calc}} = g_0 - \frac{2g}{R}h + 2\pi G  ho h$। প্রকৃত পরিমাপকৃত ত্বরণ এবং এই তাত্ত্বিক মানের পার্থক্যকে বোমার অসঙ্গতি (Bouguer Anomaly) বলা হয়, যা ভূগর্ভস্থ আইসোস্ট্যাটিক ভারসাম্য ও খনিজ অনুসন্ধানে ব্যবহৃত হয়।</t>
         </is>
       </c>
@@ -2588,17 +2448,12 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>সাধারণ আপেক্ষিকতার সমতা নীতি (Equivalence Principle) অনুসারে অভিকর্ষজ ত্বরণ $g$ এবং একটি সমান ত্বরান্বিত রকেটের ত্বরণ $a$-এর মধ্যে কোনো স্থানীয় পরীক্ষা দ্বারা পার্থক্য করা যায় না। তবে একটি অসম মহাকর্ষীয় ক্ষেত্রে টাইডাল গ্রেডিয়েন্ট $rac{\partial g}{\partial z}$ কীভাবে সমতা নীতির স্থানীয় সীমাবদ্ধতা চিহ্নিত করে?</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>None</t>
+          <t>সাধারণ আপেক্ষিকতার সমতা নীতি (Equivalence Principle) অনুসারে অভিকর্ষজ ত্বরণ $g$ এবং একটি সমান ত্বরান্বিত রকেটের ত্বরণ $a$-এর মধ্যে কোনো স্থানীয় পরীক্ষা দ্বারা পার্থক্য করা যায় না। তবে একটি অসম মহাকর্ষীয় ক্ষেত্রে টাইডাল গ্রেডিয়েন্ট $\frac{\partial g}{\partial z}$ কীভাবে সমতা নীতির স্থানীয় সীমাবদ্ধতা চিহ্নিত করে?</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>আইনস্টাইনের দুর্বল সমতা নীতি কেবল অসীম ক্ষুদ্র স্থানে (Local frame) প্রযোজ্য। বাস্তব মহাকর্ষ ক্ষেত্রে বল দূরত্বের সাথে পরিবর্তিত হয় ($rac{\partial g_z}{\partial z} = rac{2GM}{r^3} 
+          <t>আইনস্টাইনের দুর্বল সমতা নীতি কেবল অসীম ক্ষুদ্র স্থানে (Local frame) প্রযোজ্য। বাস্তব মহাকর্ষ ক্ষেত্রে বল দূরত্বের সাথে পরিবর্তিত হয় ($\frac{\partial g_z}{\partial z} = \frac{2GM}{r^3} 
 eq 0$)। একটি বৃহৎ মহাকাশযানে দুটি বিচ্ছিন্ন কণা পাশাপাশি রাখলে তারা পরস্পরের কাছে এগিয়ে আসে (পারস্পরিক অভিসারী ত্বরণ) এবং উল্লম্বভাবে রাখা দুটি কণা দূরে সরে যায় (টাইডাল স্ট্রেচিং)। একটি নিখুঁতভাবে ত্বরান্বিত রকেটে সকল বিন্দুতে ত্বরণ সম্পূর্ণ সমান্তরাল ও সমান থাকে। এই টাইডাল গ্রেডিয়েন্ট পরীক্ষা করে স্থানীয় কাঠামোর আকার বড় হলে মহাকর্ষ ক্ষেত্র ও কৃত্রিম ত্বরণের মধ্যে পার্থক্য স্পষ্ট করা যায়।</t>
         </is>
       </c>
@@ -2639,21 +2494,16 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>$R$ ব্যাসার্ধ এবং $M$ ভরের একটি সুষম নিরেট গোলককে অসীম দূরত্ব থেকে ক্ষুদ্র ক্ষুদ্র ভর কণা এনে শূন্য থেকে ধাপে ধাপে গঠন করতে মহাকর্ষ বলের বিরুদ্ধে মোট কত কাজ করতে হয় (গোলকের মহাকর্ষীয় স্ব-শক্তি $U_{	ext{self}}$)?</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>None</t>
+          <t>$R$ ব্যাসার্ধ এবং $M$ ভরের একটি সুষম নিরেট গোলককে অসীম দূরত্ব থেকে ক্ষুদ্র ক্ষুদ্র ভর কণা এনে শূন্য থেকে ধাপে ধাপে গঠন করতে মহাকর্ষ বলের বিরুদ্ধে মোট কত কাজ করতে হয় (গোলকের মহাকর্ষীয় স্ব-শক্তি $U_{\text{self}}$)?</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>ধরা যাক কোনো মুহূর্তে $r$ ব্যাসার্ধের গোলক গঠিত হয়েছে যার ভর $m(r) = rac{M}{R^3}r^3$। এই গোলকের পৃষ্ঠে মহাকর্ষীয় বিভব $V(r) = -rac{G m(r)}{r} = -rac{G M r^2}{R^3}$। অসীম থেকে $dr$ পুরুত্বের একটি নতুন শেল (ভর $dm = 4\pi r^2 -ho dr = rac{3M}{R^3}r^2 dr$) এনে এর ওপর স্থাপন করতে মহাকর্ষীয় বিভব শক্তির পরিবর্তন $dU = V(r)dm = -\left(rac{G M r^2}{R^3}-ight)\left(rac{3M}{R^3}r^2 dr-ight) = -rac{3GM^2}{R^6}r^4 dr$। সম্পূর্ণ গোলক গঠনের জন্য সমাকলন করি ($0 \le r \le R$): $U_{	ext{self}} = -rac{3GM^2}{R^6} \int_0^R r^4 dr = -rac{3GM^2}{R^6}\left[rac{R^5}{5}-ight] = -rac{3}{5}rac{GM^2}{R}$। এটি গোলকের মহাকর্ষীয় বাইন্ডিং শক্তি নির্দেশ করে।</t>
+          <t>ধরা যাক কোনো মুহূর্তে $r$ ব্যাসার্ধের গোলক গঠিত হয়েছে যার ভর $m(r) = \frac{M}{R^3}r^3$। এই গোলকের পৃষ্ঠে মহাকর্ষীয় বিভব $V(r) = -\frac{G m(r)}{r} = -\frac{G M r^2}{R^3}$। অসীম থেকে $dr$ পুরুত্বের একটি নতুন শেল (ভর $dm = 4\pi r^2 +ho dr = \frac{3M}{R^3}r^2 dr$) এনে এর ওপর স্থাপন করতে মহাকর্ষীয় বিভব শক্তির পরিবর্তন $dU = V(r)dm = -\left(\frac{G M r^2}{R^3}+ight)\left(\frac{3M}{R^3}r^2 dr+ight) = -\frac{3GM^2}{R^6}r^4 dr$। সম্পূর্ণ গোলক গঠনের জন্য সমাকলন করি ($0 \le r \le R$): $U_{\text{self}} = -\frac{3GM^2}{R^6} \int_0^R r^4 dr = -\frac{3GM^2}{R^6}\left[\frac{R^5}{5}+ight] = -\frac{3}{5}\frac{GM^2}{R}$। এটি গোলকের মহাকর্ষীয় বাইন্ডিং শক্তি নির্দেশ করে।</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2693,17 +2543,12 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>$R$ ব্যাসার্ধ এবং $M$ ভরের একটি পাতলা সুষম গোলকীয় খোলসের মহাকর্ষীয় স্ব-শক্তি $U_{	ext{shell}}$ কত এবং নিরেট গোলকের সাথে এর পার্থক্যের কারণ কী?</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>None</t>
+          <t>$R$ ব্যাসার্ধ এবং $M$ ভরের একটি পাতলা সুষম গোলকীয় খোলসের মহাকর্ষীয় স্ব-শক্তি $U_{\text{shell}}$ কত এবং নিরেট গোলকের সাথে এর পার্থক্যের কারণ কী?</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>খোলসটির সমস্ত ভর $M$ কেন্দ্র থেকে সমদূরত্ব $R$-এ অবস্থিত। খোলসটি অসীম থেকে গঠন করার সময় যেকোনো মুহূর্তে খোলসের ভর $m$ হলে পৃষ্ঠের বিভব $V = -rac{Gm}{R}$। অতিরিক্ত $dm$ ভর আনতে স্থিতিশক্তির পরিবর্তন $dU = -rac{Gm}{R}dm$। সমাকলন করি: $U_{	ext{shell}} = -rac{G}{R}\int_0^M m dm = -rac{GM^2}{2R}$। নিরেট গোলকের ক্ষেত্রে ছিল $-rac{3}{5}rac{GM^2}{R}$। নিরেট গোলকে ভর কেন্দ্রের আরও গভীরে সংকুচিত থাকায় তার বন্ধন শক্তি বেশি হয় ($3/5 &gt; 1/2$)।</t>
+          <t>খোলসটির সমস্ত ভর $M$ কেন্দ্র থেকে সমদূরত্ব $R$-এ অবস্থিত। খোলসটি অসীম থেকে গঠন করার সময় যেকোনো মুহূর্তে খোলসের ভর $m$ হলে পৃষ্ঠের বিভব $V = -\frac{Gm}{R}$। অতিরিক্ত $dm$ ভর আনতে স্থিতিশক্তির পরিবর্তন $dU = -\frac{Gm}{R}dm$। সমাকলন করি: $U_{\text{shell}} = -\frac{G}{R}\int_0^M m dm = -\frac{GM^2}{2R}$। নিরেট গোলকের ক্ষেত্রে ছিল $-\frac{3}{5}\frac{GM^2}{R}$। নিরেট গোলকে ভর কেন্দ্রের আরও গভীরে সংকুচিত থাকায় তার বন্ধন শক্তি বেশি হয় ($3/5 &gt; 1/2$)।</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2743,19 +2588,14 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>একটি স্থানের মহাকর্ষীয় বিভব $V(x,y,z) = 4x^2 y - 3y z + 2z^2$ (যেখানে $V$ জুলে/কেজি এবং স্থানাঙ্ক মিটারে)। $(1, -1, 2)	ext{ m}$ বিন্দুতে মহাকর্ষীয় ক্ষেত্র প্রাবল্য ভেক্টর $ec{E}$ এবং এর মান নির্ণয় কর।</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>None</t>
+          <t>একটি স্থানের মহাকর্ষীয় বিভব $V(x,y,z) = 4x^2 y - 3y z + 2z^2$ (যেখানে $V$ জুলে/কেজি এবং স্থানাঙ্ক মিটারে)। $(1, -1, 2)\text{ m}$ বিন্দুতে মহাকর্ষীয় ক্ষেত্র প্রাবল্য ভেক্টর $ec{E}$ এবং এর মান নির্ণয় কর।</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
           <t>মহাকর্ষীয় ক্ষেত্র প্রাবল্য বিভবের ঋণাত্মক গ্রেডিয়েন্ট: $ec{E} = -ec{
-abla}V = -\left(rac{\partial V}{\partial x}\hat{i} + rac{\partial V}{\partial y}\hat{j} + rac{\partial V}{\partial z}\hat{k}-ight)$। আংশিক ব্যবকলন: $rac{\partial V}{\partial x} = 8xy$, $rac{\partial V}{\partial y} = 4x^2 - 3z$, $rac{\partial V}{\partial z} = -3y + 4z$। বিন্দু $(1, -1, 2)$-তে মান বসিয়ে পাই: $rac{\partial V}{\partial x} = 8(1)(-1) = -8$, $rac{\partial V}{\partial y} = 4(1)^2 - 3(2) = 4 - 6 = -2$, $rac{\partial V}{\partial z} = -3(-1) + 4(2) = 3 + 8 = 11$। অতএব প্রাবল্য ভেক্টর $ec{E} = -(-8\hat{i} - 2\hat{j} + 11\hat{k}) = 8\hat{i} + 2\hat{j} - 11\hat{k}	ext{ N/kg}$। প্রাবল্যের মান $|ec{E}| = \sqrt{8^2 + 2^2 + (-11)^2} = \sqrt{64 + 4 + 121} = \sqrt{189} pprox 13.75	ext{ N/kg}$।</t>
+abla}V = -\left(\frac{\partial V}{\partial x}\hat{i} + \frac{\partial V}{\partial y}\hat{j} + \frac{\partial V}{\partial z}\hat{k}+ight)$। আংশিক ব্যবকলন: $\frac{\partial V}{\partial x} = 8xy$, $\frac{\partial V}{\partial y} = 4x^2 - 3z$, $\frac{\partial V}{\partial z} = -3y + 4z$। বিন্দু $(1, -1, 2)$-তে মান বসিয়ে পাই: $\frac{\partial V}{\partial x} = 8(1)(-1) = -8$, $\frac{\partial V}{\partial y} = 4(1)^2 - 3(2) = 4 - 6 = -2$, $\frac{\partial V}{\partial z} = -3(-1) + 4(2) = 3 + 8 = 11$। অতএব প্রাবল্য ভেক্টর $ec{E} = -(-8\hat{i} - 2\hat{j} + 11\hat{k}) = 8\hat{i} + 2\hat{j} - 11\hat{k}\text{ N/kg}$। প্রাবল্যের মান $|ec{E}| = \sqrt{8^2 + 2^2 + (-11)^2} = \sqrt{64 + 4 + 121} = \sqrt{189} pprox 13.75\text{ N/kg}$।</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -2798,16 +2638,11 @@
           <t>$R$ ব্যাসার্ধ ও $M$ ভরের একটি সুষম নিরেট গোলকের অভ্যন্তরে ($r &lt; R$) এবং বাইরে ($r &gt; R$) বিভব অপেক্ষকের সমীকরণ গঠন কর এবং $r = R$ বিন্দুতে বিভব ও প্রাবল্যের অবিচ্ছিন্নতা (Continuity) প্রমাণ কর।</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>(১) বাইরে ($r \ge R$): প্রাবল্য $E = -rac{GM}{r^2}$। বিভব $V_{	ext{out}}(r) = -\int_\infty^r \left(-rac{GM}{r'^2}-ight)dr' = -rac{GM}{r}$। (২) ভেতরে ($r \le R$): প্রাবল্য $E = -rac{GM}{R^3}r$। বিভব $V_{	ext{in}}(r) = V(R) - \int_R^r \left(-rac{GM}{R^3}r'-ight)dr' = -rac{GM}{R} + rac{GM}{2R^3}(r^2 - R^2) = -rac{GM}{2R^3}(3R^2 - r^2)$। অবিচ্ছিন্নতা পরীক্ষা: $r 	o R^+$ হলে $V_{	ext{out}}(R) = -rac{GM}{R}$। $r 	o R^-$ হলে $V_{	ext{in}}(R) = -rac{GM}{2R^3}(3R^2 - R^2) = -rac{GM}{R}$। উভয় সীমা সমান হওয়ায় বিভব সম্পূর্ণরূপে অবিচ্ছিন্ন। একইভাবে প্রাবল্য $E(R) = rac{GM}{R^2}$ উভয় পাশে সমান হওয়ায় প্রাবল্যও অবিচ্ছিন্ন।</t>
+          <t>(১) বাইরে ($r \ge R$): প্রাবল্য $E = -\frac{GM}{r^2}$। বিভব $V_{\text{out}}(r) = -\int_\infty^r \left(-\frac{GM}{r'^2}+ight)dr' = -\frac{GM}{r}$। (২) ভেতরে ($r \le R$): প্রাবল্য $E = -\frac{GM}{R^3}r$। বিভব $V_{\text{in}}(r) = V(R) - \int_R^r \left(-\frac{GM}{R^3}r'+ight)dr' = -\frac{GM}{R} + \frac{GM}{2R^3}(r^2 - R^2) = -\frac{GM}{2R^3}(3R^2 - r^2)$। অবিচ্ছিন্নতা পরীক্ষা: $r \to R^+$ হলে $V_{\text{out}}(R) = -\frac{GM}{R}$। $r \to R^-$ হলে $V_{\text{in}}(R) = -\frac{GM}{2R^3}(3R^2 - R^2) = -\frac{GM}{R}$। উভয় সীমা সমান হওয়ায় বিভব সম্পূর্ণরূপে অবিচ্ছিন্ন। একইভাবে প্রাবল্য $E(R) = \frac{GM}{R^2}$ উভয় পাশে সমান হওয়ায় প্রাবল্যও অবিচ্ছিন্ন।</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -2850,14 +2685,9 @@
           <t>$R$ ব্যাসার্ধ ও $M$ ভরের একটি সুষম রিংয়ের কেন্দ্র থেকে অসীম দূরত্বে অক্ষের ওপর স্থির থাকা $m$ ভরের একটি কণা মহাকর্ষীয় আকর্ষণে রিংয়ের দিকে মুক্তভাবে ধাবিত হলো। কণাটি যখন রিংয়ের কেন্দ্র অতিক্রম করবে, তখন তার গতিবেগ কত হবে?</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>অসীমে কণার বিভব শক্তি শূন্য এবং আদি গতিশক্তি শূন্য, ফলে মোট শক্তি $E = 0$। রিংয়ের কেন্দ্রে অক্ষের ওপর প্রতিটি কণার দূরত্ব $R$। রিংয়ের কেন্দ্রে মহাকর্ষীয় বিভব $V(0) = -rac{GM}{R}$। কেন্দ্রে কণার বিভব শক্তি $U = mV(0) = -rac{GMm}{R}$। শক্তির সংরক্ষণশীলতা অনুসারে: $E = K + U = 0 \implies rac{1}{2}m v^2 - rac{GMm}{R} = 0 \implies rac{1}{2}m v^2 = rac{GMm}{R} \implies v = \sqrt{rac{2GM}{R}}$।</t>
+          <t>অসীমে কণার বিভব শক্তি শূন্য এবং আদি গতিশক্তি শূন্য, ফলে মোট শক্তি $E = 0$। রিংয়ের কেন্দ্রে অক্ষের ওপর প্রতিটি কণার দূরত্ব $R$। রিংয়ের কেন্দ্রে মহাকর্ষীয় বিভব $V(0) = -\frac{GM}{R}$। কেন্দ্রে কণার বিভব শক্তি $U = mV(0) = -\frac{GMm}{R}$। শক্তির সংরক্ষণশীলতা অনুসারে: $E = K + U = 0 \implies \frac{1}{2}m v^2 - \frac{GMm}{R} = 0 \implies \frac{1}{2}m v^2 = \frac{GMm}{R} \implies v = \sqrt{\frac{2GM}{R}}$।</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2900,15 +2730,10 @@
           <t>পরস্পর থেকে $2d$ দূরত্বে রাখা দুটি সমান ভর $M$-এর সংযোগকারী সরলরেখার মধ্যবিন্দুতে মহাকর্ষীয় ক্ষেত্র প্রাবল্য এবং মহাকর্ষীয় বিভব কত?</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>সংযোগকারী সরলরেখার মধ্যবিন্দুতে উভয় ভরের দূরত্ব সমান ($d$)। (১) ক্ষেত্র প্রাবল্য একটি ভেক্টর রাশি: প্রথম ভরের আকর্ষণ বল বামদিকে $E_1 = rac{GM}{d^2}$ এবং দ্বিতীয় ভরের আকর্ষণ বল ডানদিকে $E_2 = rac{GM}{d^2}$। লব্ধি প্রাবল্য $ec{E} = E_2 - E_1 = 0$। (২) বিভব একটি স্কেলার রাশি: মধ্যবিন্দুতে মোট বিভব সাধারণ বীজগণিতীয় যোগফল: $V = V_1 + V_2 = -rac{GM}{d} + \left(-rac{GM}{d}-ight) = -rac{2GM}{d}$। এটি নির্দেশ করে যে প্রাবল্য শূন্য হলেও বিভব কখনই শূন্য হয় না।</t>
+          <t>সংযোগকারী সরলরেখার মধ্যবিন্দুতে উভয় ভরের দূরত্ব সমান ($d$)। (১) ক্ষেত্র প্রাবল্য একটি ভেক্টর রাশি: প্রথম ভরের আকর্ষণ বল বামদিকে $E_1 = \frac{GM}{d^2}$ এবং দ্বিতীয় ভরের আকর্ষণ বল ডানদিকে $E_2 = \frac{GM}{d^2}$। লব্ধি প্রাবল্য $ec{E} = E_2 - E_1 = 0$। (২) বিভব একটি স্কেলার রাশি: মধ্যবিন্দুতে মোট বিভব সাধারণ বীজগণিতীয় যোগফল: $V = V_1 + V_2 = -\frac{GM}{d} + \left(-\frac{GM}{d}+ight) = -\frac{2GM}{d}$। এটি নির্দেশ করে যে প্রাবল্য শূন্য হলেও বিভব কখনই শূন্য হয় না।</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2951,14 +2776,9 @@
           <t>$M_1$ ও $M_2$ দুটি ভর পরস্পরের থেকে $L$ দূরত্বে অবস্থিত। তাদের সংযোগ রেখায় কোন বিন্দুতে মহাকর্ষীয় প্রাবল্য শূন্য হবে এবং ওই বিন্দুতে বিভব একটি স্থানীয় সর্বোচ্চ মান প্রদর্শন করে কেন?</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>ধরা যাক $M_1$ থেকে $x$ দূরত্বে প্রাবল্য শূন্য। প্রাবল্য শূন্যের শর্ত: $rac{G M_1}{x^2} = rac{G M_2}{(L - x)^2} \implies rac{\sqrt{M_1}}{x} = rac{\sqrt{M_2}}{L - x} \implies x = rac{\sqrt{M_1}}{\sqrt{M_1} + \sqrt{M_2}}L$। যেহেতু প্রাবল্য বিভবের ঋণাত্মক ঢাল ($E = -rac{dV}{dx}$), সেহেতু $E = 0$ অর্থ $rac{dV}{dx} = 0$। দ্বিতীয় অন্তরক $rac{d^2 V}{dx^2} = -rac{dE}{dx}$। $x$-এর উভয় পাশে বল ভরগুলোর দিকে টানে, ফলে সংযোগ রেখা বরাবর এই বিন্দুতে বিভব ঋণাত্মক মানের দিক থেকে সবচেয়ে কম ঋণাত্মক অর্থাৎ স্থানীয় সর্বোচ্চ (Local Maximum) মান ধারণ করে। ফলে এটি একটি অস্থিতিশীল স্যাডল পয়েন্ট।</t>
+          <t>ধরা যাক $M_1$ থেকে $x$ দূরত্বে প্রাবল্য শূন্য। প্রাবল্য শূন্যের শর্ত: $\frac{G M_1}{x^2} = \frac{G M_2}{(L - x)^2} \implies \frac{\sqrt{M_1}}{x} = \frac{\sqrt{M_2}}{L - x} \implies x = \frac{\sqrt{M_1}}{\sqrt{M_1} + \sqrt{M_2}}L$। যেহেতু প্রাবল্য বিভবের ঋণাত্মক ঢাল ($E = -\frac{dV}{dx}$), সেহেতু $E = 0$ অর্থ $\frac{dV}{dx} = 0$। দ্বিতীয় অন্তরক $\frac{d^2 V}{dx^2} = -\frac{dE}{dx}$। $x$-এর উভয় পাশে বল ভরগুলোর দিকে টানে, ফলে সংযোগ রেখা বরাবর এই বিন্দুতে বিভব ঋণাত্মক মানের দিক থেকে সবচেয়ে কম ঋণাত্মক অর্থাৎ স্থানীয় সর্বোচ্চ (Local Maximum) মান ধারণ করে। ফলে এটি একটি অস্থিতিশীল স্যাডল পয়েন্ট।</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -3001,15 +2821,10 @@
           <t>$R$ ব্যাসার্ধ এবং সুষম ক্ষেত্র ঘনত্ব $\sigma$ বিশিষ্ট একটি পাতলা বৃত্তাকার চাকতির কেন্দ্রে মহাকর্ষীয় বিভব কত? মোট ভর $M$ দিয়ে প্রকাশ কর।</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>চাকতিটিকে $r$ ব্যাসার্ধের সমকেন্দ্রিক রিংয়ে ভাগ করি। রিংয়ের ভর $dm = \sigma 2\pi r dr$। কেন্দ্রের সাপেক্ষে রিংয়ের প্রতিটি বিন্দুর দূরত্ব $r$। কেন্দ্রে রিংয়ের বিভব $dV = -rac{G dm}{r} = -rac{G (\sigma 2\pi r dr)}{r} = -2\pi G \sigma dr$। সমগ্র চাকতির জন্য সমাকলন করি ($0 \le r \le R$): $V = -2\pi G \sigma \int_0^R dr = -2\pi G \sigma R$। মোট ভর $M = \sigma \pi R^2 \implies \sigma = rac{M}{\pi R^2}$। মান বসিয়ে পাই: $V = -2\pi G \left(rac{M}{\pi R^2}-ight)R = -rac{2GM}{R}$।</t>
+          <t>চাকতিটিকে $r$ ব্যাসার্ধের সমকেন্দ্রিক রিংয়ে ভাগ করি। রিংয়ের ভর $dm = \sigma 2\pi r dr$। কেন্দ্রের সাপেক্ষে রিংয়ের প্রতিটি বিন্দুর দূরত্ব $r$। কেন্দ্রে রিংয়ের বিভব $dV = -\frac{G dm}{r} = -\frac{G (\sigma 2\pi r dr)}{r} = -2\pi G \sigma dr$। সমগ্র চাকতির জন্য সমাকলন করি ($0 \le r \le R$): $V = -2\pi G \sigma \int_0^R dr = -2\pi G \sigma R$। মোট ভর $M = \sigma \pi R^2 \implies \sigma = \frac{M}{\pi R^2}$। মান বসিয়ে পাই: $V = -2\pi G \left(\frac{M}{\pi R^2}+ight)R = -\frac{2GM}{R}$।</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -3049,17 +2864,12 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>একটি সাধারণ ভর বিন্যাসের মাল্টিপোল বিস্তারে (Multipole Expansion) দূরবর্তী অঞ্চলে মহাকর্ষীয় বিভব $V(r) = -rac{GM}{r} - rac{G}{r^3}\sum Q_{ij}n_i n_j + \dots$। কেন $1/r^2$ যুক্ত ডাইপোল পদটি সর্বদা শূন্যে পরিণত হয়?</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>None</t>
+          <t>একটি সাধারণ ভর বিন্যাসের মাল্টিপোল বিস্তারে (Multipole Expansion) দূরবর্তী অঞ্চলে মহাকর্ষীয় বিভব $V(r) = -\frac{GM}{r} - \frac{G}{r^3}\sum Q_{ij}n_i n_j + \dots$। কেন $1/r^2$ যুক্ত ডাইপোল পদটি সর্বদা শূন্যে পরিণত হয়?</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>মহাকর্ষীয় বিভবের মাল্টিপোল বিস্তারে ডাইপোল পদটি হলো $V_{	ext{dipole}} = -rac{G ec{p}\cdot\hat{r}}{r^2}$, যেখানে মহাকর্ষীয় ডাইপোল ভ্রামক $ec{p} = \sum m_i ec{r}_i$। যেহেতু ভর সর্বদাই ধনাত্মক, আমরা সর্বদা রেফারেন্স ফ্রেমের মূলবিন্দুকে সংস্থার ভরকেন্দ্রে ($ec{r}_{	ext{cm}} = rac{\sum m_i ec{r}_i}{M} = ec{0}$) স্থাপন করতে পারি। ভরকেন্দ্র ফ্রেমে $ec{p} = \sum m_i ec{r}_i = 0$। ফলে ডাইপোল পদটি সম্পূর্ণরূপে অপসারিত হয় এবং উচ্চতর সংশোধন সরাসরি চতুর্ধ্রুবক (Quadrupole, $1/r^3$) দিয়ে শুরু হয়।</t>
+          <t>মহাকর্ষীয় বিভবের মাল্টিপোল বিস্তারে ডাইপোল পদটি হলো $V_{\text{dipole}} = -\frac{G ec{p}\cdot\hat{r}}{r^2}$, যেখানে মহাকর্ষীয় ডাইপোল ভ্রামক $ec{p} = \sum m_i ec{r}_i$। যেহেতু ভর সর্বদাই ধনাত্মক, আমরা সর্বদা রেফারেন্স ফ্রেমের মূলবিন্দুকে সংস্থার ভরকেন্দ্রে ($ec{r}_{\text{cm}} = \frac{\sum m_i ec{r}_i}{M} = ec{0}$) স্থাপন করতে পারি। ভরকেন্দ্র ফ্রেমে $ec{p} = \sum m_i ec{r}_i = 0$। ফলে ডাইপোল পদটি সম্পূর্ণরূপে অপসারিত হয় এবং উচ্চতর সংশোধন সরাসরি চতুর্ধ্রুবক (Quadrupole, $1/r^3$) দিয়ে শুরু হয়।</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -3099,20 +2909,15 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>একটি কণার মহাকর্ষীয় বিভব শক্তি $U(x) = -rac{A}{\sqrt{x^2 + a^2}}$ ($A, a &gt; 0$)। সাম্যাবস্থানের সাপেক্ষে ক্ষুদ্র দোলনের কৌণিক কম্পাঙ্ক $\omega$ নির্ণয় কর।</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>None</t>
+          <t>একটি কণার মহাকর্ষীয় বিভব শক্তি $U(x) = -\frac{A}{\sqrt{x^2 + a^2}}$ ($A, a &gt; 0$)। সাম্যাবস্থানের সাপেক্ষে ক্ষুদ্র দোলনের কৌণিক কম্পাঙ্ক $\omega$ নির্ণয় কর।</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>বিভব শক্তির প্রথম অন্তরক: $rac{dU}{dx} = -A\left(-rac{1}{2}-ight)(x^2 + a^2)^{-3/2}(2x) = rac{Ax}{(x^2 + a^2)^{3/2}}$। সাম্যাবস্থার শর্ত $rac{dU}{dx} = 0 \implies x_0 = 0$। দ্বিতীয় অন্তরক: $rac{d^2 U}{dx^2} = A\left[rac{(x^2 + a^2)^{3/2}(1) - xrac{3}{2}(x^2 + a^2)^{1/2}(2x)}{(x^2 + a^2)^3}-ight]$। $x=0$ বিন্দুতে মান: $\left.rac{d^2 U}{dx^2}-ight|_0 = rac{A(a^3)}{a^6} = rac{A}{a^3} &gt; 0$ (স্থিতিশীল সাম্যাবস্থা)। কার্যকর স্প্রিং ধ্রুবক $k_{	ext{eff}} = rac{A}{a^3}$। অতএব $m$ ভরের কণার ক্ষুদ্র দোলনের কৌণিক কম্পাঙ্ক $\omega = \sqrt{rac{k_{	ext{eff}}}{m}} = \sqrt{rac{A}{m a^3}}$।</t>
+          <t>বিভব শক্তির প্রথম অন্তরক: $\frac{dU}{dx} = -A\left(-\frac{1}{2}+ight)(x^2 + a^2)^{-3/2}(2x) = \frac{Ax}{(x^2 + a^2)^{3/2}}$। সাম্যাবস্থার শর্ত $\frac{dU}{dx} = 0 \implies x_0 = 0$। দ্বিতীয় অন্তরক: $\frac{d^2 U}{dx^2} = A\left[\frac{(x^2 + a^2)^{3/2}(1) - xrac{3}{2}(x^2 + a^2)^{1/2}(2x)}{(x^2 + a^2)^3}+ight]$। $x=0$ বিন্দুতে মান: $\left.\frac{d^2 U}{dx^2}+ight|_0 = \frac{A(a^3)}{a^6} = \frac{A}{a^3} &gt; 0$ (স্থিতিশীল সাম্যাবস্থা)। কার্যকর স্প্রিং ধ্রুবক $k_{\text{eff}} = \frac{A}{a^3}$। অতএব $m$ ভরের কণার ক্ষুদ্র দোলনের কৌণিক কম্পাঙ্ক $\omega = \sqrt{\frac{k_{\text{eff}}}{m}} = \sqrt{\frac{A}{m a^3}}$।</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -3155,11 +2960,6 @@
           <t>ভূপৃষ্ঠ থেকে একটি বস্তুকে অনুভূমিকের সাথে $\theta$ কোণে মুক্তিবেগ $v_e = \sqrt{2gR}$ দ্রুতিতে নিক্ষেপ করা হলো (বায়ুমণ্ডলীয় ঘর্ষণ ও বাধা নগণ্য)। বস্তুটি কি মহাকর্ষীয় ক্ষেত্র অতিক্রম করে অসীমে পৌঁছাতে পারবে? প্রক্ষেপণ কোণ $\theta$-এর ওপর এটি কীভাবে নির্ভর করে?</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I42" t="inlineStr">
         <is>
           <t>মুক্তিবেগ একটি শক্তি-ভিত্তিক স্কেলার রাশি। মহাকর্ষীয় বিভব ক্ষেত্রে কণার মোট যান্ত্রিক শক্তি $E = K + U = \frac{1}{2}m v^2 - \frac{GMm}{R}$। মুক্তিবেগের শর্ত হলো কণার মোট যান্ত্রিক শক্তি ন্যূনতম শূন্য হতে হবে ($E \ge 0$)। দ্রুতি $v = v_e = \sqrt{\frac{2GM}{R}}$ হলে নিক্ষেপের কোণ $\theta$ যাই হোক না কেন, গতিশক্তি $K = \frac{GMm}{R}$ হয়, ফলে মোট শক্তি $E = 0$। যেহেতু কোনো বাহ্যিক বাধা নেই এবং মোট শক্তি শূন্য, সেহেতু বস্তুটি যে কোনো অভিমুখে নিক্ষিপ্ত হলেও (যদি না তা সরাসরি মাটির ভেতরে আঘাত করে) একটি উন্মুক্ত পরাবৃত্তীয় (Parabolic, $e=1$) গতিপথে অসীমে মুক্ত হয়ে যাবে। অতএব মুক্তিবেগ প্রক্ষেপণ কোণ $\theta$-এর ওপর সম্পূর্ণরূপে নিরপেক্ষ।</t>
@@ -3205,11 +3005,6 @@
           <t>চাঁদের ভর পৃথিবীর ভরের ১/৮১ অংশ এবং ব্যাসার্ধ পৃথিবীর ব্যাসার্ধের ১/৪ অংশ। চাঁদের পৃষ্ঠে মুক্তিবেগ $v_{e, \text{moon}}$ পৃথিবীর মুক্তিবেগের ($v_e \approx 11.2\text{ km/s}$) কত ভগ্নাংশ এবং এটি কেন চাঁদে বায়ুমণ্ডলের অনুপস্থিতি ব্যাখ্যা করে?</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I43" t="inlineStr">
         <is>
           <t>মুক্তিবেগের সূত্র $v_e = \sqrt{\frac{2GM}{R}}$। চাঁদের ক্ষেত্রে: $v_{e, \text{moon}} = \sqrt{\frac{2G(M_E/81)}{R_E/4}} = \sqrt{\frac{4}{81}}\sqrt{\frac{2GM_E}{R_E}} = \frac{2}{9}v_e = \frac{2}{9}(11.2\text{ km/s}) \approx 2.49\text{ km/s}$ (প্রায় ২.৪ কিমি/সে)। ম্যাক্সওয়েলের গতিতত্ত্ব অনুসারে সাধারণ গ্যাস অণুসমূহের (যেমন হাইড্রোজেন, হিলিয়াম, নাইট্রোজেন ও অক্সিজেন) মূল-গড়-বর্গ দ্রুতি $v_{\text{rms}} = \sqrt{\frac{3k_B T}{m}}$ চাঁদের দিনের বেলার তাপমাত্রায় (প্রায় ৪০০ K) চাঁদের এই অতি ক্ষুদ্র মুক্তিবেগের (২.৪ কিমি/সে) সমকক্ষ বা বেশি হয়ে যায়। ফলে গ্যাসীয় অণুগুলো সময়ের সাথে সাথে মহাকর্ষ কাটিয়ে মহাশূন্যে হারিয়ে গেছে, যার ফলে চাঁদে কোনো স্থায়ী বায়ুমণ্ডল নেই।</t>
@@ -3255,11 +3050,6 @@
           <t>সিয়োলকোভস্কির রকেট সমীকরণ $v = u_{\text{rel}}\ln(M_0/M_f)$ অনুসারে একক স্তরের রাসায়নিক রকেটের নির্গমন বেগ $u_{\text{rel}} \approx 3.5\text{ km/s}$ হলে মুক্তিবেগ ($11.2\text{ km/s}$) অর্জনের জন্য প্রয়োজনীয় ভর অনুপাত কত এবং কেন বহু-স্তরীয় রকেট ব্যবহার বাধ্যতামূলক?</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I44" t="inlineStr">
         <is>
           <t>একক স্তরের জন্য: $11.2 = 3.5\ln\left(\frac{M_0}{M_f}\right) \implies \ln\left(\frac{M_0}{M_f}\right) = \frac{11.2}{3.5} = 3.2 \implies \frac{M_0}{M_f} = e^{3.2} \approx 24.5$। অর্থাৎ রকেটের কাঠামোগত ভর ও পেলোড মোট আদি ভরের মাত্র $1/24.5 \approx 4.08\%$ হতে হবে, যা ধাতব ট্যাঙ্ক ও ইঞ্জিনের ভরের তুলনায় বাস্তবায়ন অসম্ভব। বহু-স্তরীয় (Multistage) রকেটে খালি ট্যাঙ্ক ও পোড়া ইঞ্জিন ধাপে ধাপে খসিয়ে ফেলে অবশিষ্ট ভরের ওপর পরবর্তী ধাপের থ্রাস্ট প্রয়োগ করা হয়, যার ফলে কার্যকর নির্গমন বেগ ও চূড়ান্ত বেগ বহুগুণ বৃদ্ধি পেয়ে কার্যকর পেলোড মহাকাশে পাঠানো সম্ভব হয়।</t>
@@ -3305,11 +3095,6 @@
           <t>পৃথিবীর পৃষ্ঠ থেকে একটি নভোযানকে এমন দ্রুতিতে ছুঁড়তে হবে যেন তা সূর্য ও পৃথিবী উভয়ের মহাকর্ষ কাটিয়ে সৌরজগৎ ত্যাগ করতে পারে (তৃতীয় মহাজাগতিক বেগ $v_3$)। পৃথিবীর কক্ষপথীয় বেগ $V_0 \approx 29.8\text{ km/s}$ বিবেচনা করে এর মান নির্ণয় কর।</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I45" t="inlineStr">
         <is>
           <t>সূর্যের দূরত্বে সৌরজগৎ ত্যাগের প্রয়োজনীয় সূর্য-কেন্দ্রিক বেগ $v_{\infty} = \sqrt{2}V_0 \approx \sqrt{2}(29.8) \approx 42.1\text{ km/s}$। পৃথিবী নিজেই সূর্যের চারদিকে $V_0 = 29.8\text{ km/s}$ বেগে ঘুরছে। পৃথিবীর গতির দিকে নভোযান ছুঁড়লে পৃথিবীর সাপেক্ষে প্রয়োজনীয় ইনফিনিটি দ্রুতি $v_\infty' = \sqrt{2}V_0 - V_0 = (\sqrt{2}-1)V_0 \approx 0.414 \times 29.8 \approx 12.34\text{ km/s}$। এখন ভূপৃষ্ঠ থেকে এই অতিরিক্ত বেগ অর্জনের জন্য শক্তির সমীকরণ: $\frac{1}{2}m v_3^2 - \frac{GM_E m}{R_E} = \frac{1}{2}m v_\infty'^2 \implies v_3 = \sqrt{v_e^2 + v_\infty'^2} = \sqrt{(11.2)^2 + (12.34)^2} = \sqrt{125.44 + 152.28} = \sqrt{277.72} \approx 16.66\text{ km/s}$। এটি তৃতীয় মহাজাগতিক বেগ নামে পরিচিত।</t>
@@ -3355,11 +3140,6 @@
           <t>পৃথিবীর কেন্দ্র পর্যন্ত খননকৃত একটি সোজা সুড়ঙ্গের তলদেশে (পৃথিবীর কেন্দ্রে) রাখা একটি বস্তুর মুক্তিবেগ ভূপৃষ্ঠের মুক্তিবেগের ($v_e$) কত গুণ হবে?</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I46" t="inlineStr">
         <is>
           <t>পৃথিবীর কেন্দ্রে মহাকর্ষীয় বিভব $V(0) = -\frac{3GM}{2R} = -\frac{3}{2}V_{\text{surface}}$। কেন্দ্রে বিভব শক্তি $U(0) = -\frac{3GMm}{2R}$। অসীমে পৌঁছানোর জন্য মোট শক্তি ন্যূনতম শূন্য হতে হবে: $\frac{1}{2}m v_c^2 + U(0) = 0 \implies \frac{1}{2}m v_c^2 = \frac{3GMm}{2R} \implies v_c^2 = \frac{3GM}{R} = \frac{3}{2}\left(\frac{2GM}{R}\right) = \frac{3}{2}v_e^2 \implies v_c = \sqrt{\frac{3}{2}}v_e \approx 1.225 v_e$। অর্থাৎ কেন্দ্র থেকে মুক্তিবেগ ভূপৃষ্ঠের চেয়ে ২২.৫% বেশি এবং এর মান প্রায় ১৩.৭২ কিমি/সে।</t>
@@ -3405,11 +3185,6 @@
           <t>একটি রকেটকে সরাসরি খাড়া না ছুঁড়ে গ্র্যাভিটি টার্ন (Gravity Turn) ম্যানুভারের মাধ্যমে একটি নির্দিষ্ট বক্র গতিপথে উৎক্ষেপণ করা হয় কেন? শক্তি অপচয়ের দৃষ্টিকোণ থেকে ব্যাখ্যা কর।</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I47" t="inlineStr">
         <is>
           <t>খাড়া উড্ডয়নে সার্বক্ষণিক মহাকর্ষীয় টান (Gravity Drag, $\int g dt$) ইঞ্জিনের থ্রাস্টের সরাসরি বিপরীতে কাজ করে বিপুল জ্বালানি অপচয় ঘটায়। গ্র্যাভিটি টার্নে রকেটটি প্রাথমিক উলম্ব উড্ডয়নের পর সামান্য হেলে পড়ে, ফলে মহাকর্ষ নিজেই কোনো অতিরিক্ত স্টিয়ারিং জ্বালানি খরচ ছাড়াই রকেটের গতিপথকে প্রাকৃতিক পরাবৃত্তীয় ট্র্যাজেক্টরি বরাবর অনুভূমিক কক্ষপথের দিকে বাঁকিয়ে দেয়। এতে মহাকর্ষীয় ড্র্যাগ ন্যূনতম হয় এবং রকেটের গতিশক্তি সরাসরি অনুভূমিক কক্ষপথীয় বেগ ($v_0 \approx 7.9\text{ km/s}$) অর্জনে ব্যবহৃত হয়।</t>
@@ -3455,11 +3230,6 @@
           <t>সূর্যের ভর $M_\odot$, ভাস্বর দীপ্তি $L_\odot$। সূর্যের চারপাশে ঘূর্ণায়মান $r$ ব্যাসার্ধ ও $\rho$ ঘনত্বের একটি ক্ষুদ্র গোলাকার ধূলিকণার ওপর মহাকর্ষীয় আকর্ষণ বল এবং সৌর বিকিরণ চাপ বল সমান হওয়ার জন্য কণার ক্রান্তিক ব্যাসার্ধ $r_{\text{crit}}$ নির্ণয় কর।</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I48" t="inlineStr">
         <is>
           <t>সূর্য থেকে $R$ দূরত্বে মহাকর্ষীয় আকর্ষণ বল $F_g = \frac{G M_\odot m}{R^2} = \frac{G M_\odot (\frac{4}{3}\pi r^3 \rho)}{R^2}$। সৌর বিকিরণ ফ্লাক্স $S = \frac{L_\odot}{4\pi R^2}$। কণার প্রস্থচ্ছেদের ক্ষেত্রফল $A = \pi r^2$। ফোটনের ভরবেগ থেকে বিকিরণ বল $F_{\text{rad}} = \frac{S A}{c} = \frac{L_\odot \pi r^2}{4\pi R^2 c} = \frac{L_\odot r^2}{4 R^2 c}$। ভারসাম্য শর্ত $F_g = F_{\text{rad}} \implies \frac{4}{3}\pi G M_\odot \rho r^3 = \frac{L_\odot r^2}{4c} \implies r_{\text{crit}} = \frac{3 L_\odot}{16\pi G M_\odot \rho c}$। যদি ধূলিকণার ব্যাসার্ধ এর চেয়ে ছোট হয় ($r &lt; r_{\text{crit}}$), তবে বিকিরণ চাপ মহাকর্ষকে ছাপিয়ে কণাটিকে সৌরজগতের বাইরে উড়িয়ে নিয়ে যায়।</t>
@@ -3505,11 +3275,6 @@
           <t>পৃথিবীপৃষ্ঠ থেকে $h = R$ উচ্চতার একটি বিন্দু হতে স্থির অবস্থা থেকে একটি কণা পৃথিবীর মহাকর্ষের টানে মুক্তভাবে পড়লে মাটিতে আঘাত করতে কত সময় লাগবে?</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I49" t="inlineStr">
         <is>
           <t>কেন্দ্র থেকে আদি দূরত্ব $r_0 = 2R$ এবং ভূপৃষ্ঠে দূরত্ব $R$। পরিবর্তনশীল মহাকর্ষীয় ত্বরণে শক্তির সমীকরণ: $\frac{1}{2}m\left(\frac{dr}{dt}\right)^2 - \frac{GMm}{r} = -\frac{GMm}{r_0} \implies \frac{dr}{dt} = -\sqrt{2GM\left(\frac{1}{r} - \frac{1}{r_0}\right)}$। সমাকলন করি $r = r_0\cos^2\theta$ প্রতিস্থাপন করে। সমাকলন মান দাঁড়ায়: $t = \sqrt{\frac{r_0^3}{2GM}}\left[ \frac{\pi}{2} - \sin^{-1}\left(\sqrt{\frac{R}{r_0}}\right) + \sqrt{\frac{R}{r_0}\left(1 - \frac{R}{r_0}\right)} \right]$। $r_0 = 2R$ বসালে $\frac{R}{r_0} = \frac{1}{2}$, ফলে $\sin^{-1}(1/\sqrt{2}) = \frac{\pi}{4}$। অতএব $t = \sqrt{\frac{8R^3}{2GM}}\left(\frac{\pi}{4} + \frac{1}{2}\right) = \sqrt{\frac{R}{g}}\left(\frac{\pi}{2} + 1\right)$।</t>
@@ -3555,11 +3320,6 @@
           <t>$R$ ব্যাসার্ধের একটি কৃত্রিম নলাকার মহাকাশ স্টেশন তার অক্ষের সাপেক্ষে এমন কৌণিক বেগ $\omega$-তে ঘুরছে যাতে অভ্যন্তরীণ দেয়ালে $g$ কৃত্রিম অভিকর্ষ সৃষ্টি হয়। মেঝের সাপেক্ষে কণার মুক্তিবেগের সমীকরণ কী?</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I50" t="inlineStr">
         <is>
           <t>ঘূর্ণায়মান ফ্রেমে কৃত্রিম মহাকর্ষ সৃষ্টি হয় বহির্মুখী অপকেন্দ্র বলের মাধ্যমে: $a_c = \omega^2 R = g \implies \omega = \sqrt{g/R}$। মেঝের স্পর্শকীয় বেগ $v_0 = \omega R = \sqrt{gR}$। ঘূর্ণন কাঠামোর ভেতর কণার আপাত গতিশক্তি ও অপকেন্দ্র বিভব শক্তি $U_{\text{rot}}(r) = -\frac{1}{2}m\omega^2 r^2$ দ্বারা নিয়ন্ত্রিত হয়। কেন্দ্রাতিগ ক্ষেত্রে কোনো বাহ্যিক অসীম মহাকর্ষীয় কূপ না থাকায় মেঝে থেকে অক্ষ পর্যন্ত পৌঁছানোর প্রয়োজনীয় আপেক্ষিক বেগ হয় $v = \omega R = \sqrt{gR}$।</t>
@@ -3605,11 +3365,6 @@
           <t>$10^6\text{ kg}$ ভরের একটি ধাতব উল্কাপিণ্ড মুক্তিবেগ $v_e = 11.2\text{ km/s}$ নিয়ে উল্লম্বভাবে পৃথিবীর বায়ুমণ্ডলে আঘাত করল। আঘাতের মুহূর্তে উল্কাপিণ্ডটির মোট গতিশক্তি কত মেগাটন টিএনটি (TNT) সমতুল্য? ($1\text{ megaton TNT} \approx 4.184 \times 10^{15}\text{ J}$)</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I51" t="inlineStr">
         <is>
           <t>মোট গতিশক্তি $K = \frac{1}{2}m v_e^2 = \frac{1}{2}(10^6\text{ kg})(11.2 \times 10^3\text{ m/s})^2 = \frac{1}{2}(10^6)(1.2544 \times 10^8) = 6.272 \times 10^{13}\text{ J}$। মেগাটনে রূপান্তর: $E = \frac{6.272 \times 10^{13}}{4.184 \times 10^{15}} \approx 0.015\text{ megaton} = 15\text{ kiloton TNT}$। এটি হিরোশিমায় বিস্ফোরিত পারমাণবিক বোমার (প্রায় ১৫ কিলোটন) শক্তির প্রায় সমান।</t>
@@ -3639,43 +3394,38 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>কেপলারের ৩য় সূত্র ও উপগ্রহের পর্যায়কাল (সমস্যা 1)</t>
+          <t>অভিকর্ষজ ত্বরণের পরিবর্তন ও পৃথিবীর ঘূর্ণন (Variation of g &amp; Planetology)</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F52" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>[সমস্যা 1: কেপলারের ৩য় সূত্র ও উপগ্রহের পর্যায়কাল]
-##PRESET:kepler-orbit[size:medium]##
-পৃথিবীর পৃষ্ঠ হতে $h = 400\text{ km}$ উচ্চতায় একটি কৃত্রিম উপগ্রহ বৃত্তাকার কক্ষপথে পৃথিবীকে প্রদক্ষিণ করছে। পৃথিবীর ভর $M = 6.0 \times 10^{24}\text{ kg}$ এবং ব্যাসার্ধ $R = 6400\text{ km}$ হলে উপগ্রহটির কক্ষীয় দ্রুতি এবং পর্যায়কাল কত?</t>
+          <t>##GEO:circle[r=3][size:small]##
+ভূপৃষ্ঠ হতে কত উচ্চতায় অভিকর্ষজ ত্বরণের মান ভূপৃষ্ঠের মানের এক-চতুর্থাংশ ($g_h = g/4$) হবে? (পৃথিবীর ব্যাসার্ধ $R = 6400\text{ km}$)।</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>##PRESET:kepler-orbit[size:medium]##</t>
+          <t>##GEO:circle[r=3][size:small]##</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>নিউটনের সার্বজনীন মহাকর্ষ সূত্র ও কেপলারের গ্রহীয় গতির সূত্রাবলি প্রয়োগ করে ধাপে ধাপে সমাধান (সমস্যা 1)।</t>
+          <t>উচ্চতার সূত্র: $g_h = g\left(\frac{R}{R+h}\right)^2$। দেওয়া আছে $g_h/g = 1/4$। $\left(\frac{R}{R+h}\right)^2 = \frac{1}{4} \implies \frac{R}{R+h} = \frac{1}{2} \implies R+h = 2R \implies h = R = 6400\text{ km}$।</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>মহাকর্ষীয় সমাধান 1</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr"/>
-      <c r="N52" t="inlineStr"/>
+          <t>উচ্চতা $h = R = 6400\\text{ km}$</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -3695,7 +3445,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>ভূপৃষ্ঠ থেকে উচ্চতায় g-এর মান (সমস্যা 2)</t>
+          <t>অভিকর্ষজ ত্বরণের পরিবর্তন ও পৃথিবীর ঘূর্ণন (Variation of g &amp; Planetology)</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -3708,25 +3458,25 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>[সমস্যা 2: ভূপৃষ্ঠ থেকে উচ্চতায় g-এর মান]
-ভূপৃষ্ঠ হতে কত উচ্চতায় অভিকর্ষজ ত্বরণের মান ভূপৃষ্ঠের মানের $\frac{1}{7}$ অংশ হবে? (পৃথিবীর ব্যাসার্ধ $R = 6400\text{ km}$)</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr"/>
+          <t>##GEO:circle[r=3.2][size:small]##
+একটি খনির কত গভীরে গেলে অভিকর্ষজ ত্বরণের মান ভূপৃষ্ঠের মানের $20\%$ হ্রাস পাবে? ভূপৃষ্ঠে কোনো বস্তুর ওজন $500\text{ N}$ হলে ওই গভীরতায় তার ওজন কত হবে? ($R = 6400\text{ km}$)।</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=3.2][size:small]##</t>
+        </is>
+      </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>নিউটনের সার্বজনীন মহাকর্ষ সূত্র ও কেপলারের গ্রহীয় গতির সূত্রাবলি প্রয়োগ করে ধাপে ধাপে সমাধান (সমস্যা 2)।</t>
+          <t>গভীরতার সূত্র: $g_d = g(1 - d/R)$। $20\%$ হ্রাস মানে $g_d = 0.80g \implies 1 - d/R = 0.80 \implies d/R = 0.20 \implies d = 0.20 \times 6400 = 1280\text{ km}$। গভীরতায় ওজন $W_d = m g_d = 0.80(500) = 400.0\text{ N}$।</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>মহাকর্ষীয় সমাধান 2</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr"/>
-      <c r="N53" t="inlineStr"/>
+          <t>গভীরতা $d = 1280\\text{ km}$, ওজন $W = 400.0\\text{ N}$</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -3746,38 +3496,38 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>খনিতে বা গভীরতায় g-এর পরিবর্তন (সমস্যা 3)</t>
+          <t>অভিকর্ষজ ত্বরণের পরিবর্তন ও পৃথিবীর ঘূর্ণন (Variation of g &amp; Planetology)</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F54" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>[সমস্যা 3: খনিতে বা গভীরতায় g-এর পরিবর্তন]
-ভূপৃষ্ঠ হতে কত গভীরে খনির ভেতর প্রবেশ করলে অভিকর্ষজ ত্বরণের মান ভূপৃষ্ঠের মানের $25\%$ হ্রাস পাবে?</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr"/>
+          <t>##GEO:circle[r=2.8][size:small]##
+পৃথিবীর ঘূর্ণন থেমে গেলে বিষুবরেখায় অভিকর্ষজ ত্বরণের মান কত শতাংশ বৃদ্ধি পাবে? (পৃথিবীর ব্যাসার্ধ $R = 6.4 	imes 10^6\text{ m}$, পর্যায়কাল $T = 86400\text{ s}$, $g = 9.8\text{ ms}^{-2}$)।</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=2.8][size:small]##</t>
+        </is>
+      </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>নিউটনের সার্বজনীন মহাকর্ষ সূত্র ও কেপলারের গ্রহীয় গতির সূত্রাবলি প্রয়োগ করে ধাপে ধাপে সমাধান (সমস্যা 3)।</t>
+          <t>কৌণিক বেগ $\omega = \frac{2\pi}{86400} \approx 7.272\times 10^{-5}\text{ rad/s}$। বিষুবীয় কেন্দ্রাতিগ ত্বরণ $\omega^2 R = (7.272\times 10^{-5})^2 \times 6.4\times 10^6 \approx 5.288\times 10^{-9} \times 6.4\times 10^6 \approx 0.0338\text{ m/s}^2$। ঘূর্ণন বন্ধ হলে বিষুবরেখায় $g$ বৃদ্ধি পাবে $\Delta g = 0.0338\text{ m/s}^2$। শতকরা বৃদ্ধি $= \frac{0.0338}{9.8} \times 100\% \approx 0.345\%$।</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>মহাকর্ষীয় সমাধান 3</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr"/>
-      <c r="N54" t="inlineStr"/>
+          <t>বৃদ্ধি $\Delta g = 0.0338\\text{ m/s}^2$ ($0.345\\%$ বৃদ্ধি)</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -3797,7 +3547,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>মুক্তিবেগ ও গ্রহের ঘনত্ব (সমস্যা 4)</t>
+          <t>অভিকর্ষজ ত্বরণের পরিবর্তন ও পৃথিবীর ঘূর্ণন (Variation of g &amp; Planetology)</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -3810,30 +3560,25 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>[সমস্যা 4: মুক্তিবেগ ও গ্রহের ঘনত্ব]
-##GEO:sphere[r=4][size:small]##
-একটি গ্রহের ভর পৃথিবীর ভরের 10 গুণ কিন্তু ব্যাসার্ধ পৃথিবীর ব্যাসার্ধের 11 গুণ। পৃথিবীর পৃষ্ঠে মুক্তিবেগ $11.2\text{ km/s}$ হলে ঐ গ্রহের পৃষ্ঠে মুক্তিবেগ কত?</t>
+          <t>##GEO:circle[r=2.5][size:small]##
+পৃথিবী তার নিজ অক্ষের চারদিকে বর্তমানে যে কৌণিক বেগে আবর্তন করছে, তার কত গুণ দ্রুত ঘুরলে বিষুবরেখায় অবস্থানরত কোনো বস্তু সম্পূর্ণ ওজনহীন (Weightless) অনুভূত হবে? তখন দিনের দৈর্ঘ্য কত হবে?</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>##GEO:sphere[r=4][size:small]##</t>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>নিউটনের সার্বজনীন মহাকর্ষ সূত্র ও কেপলারের গ্রহীয় গতির সূত্রাবলি প্রয়োগ করে ধাপে ধাপে সমাধান (সমস্যা 4)।</t>
+          <t>ওজনহীনতার শর্ত: $g - \omega^2 R = 0 \implies \omega = \sqrt{\frac{g}{R}} = \sqrt{\frac{9.8}{6.4\times 10^6}} \approx 1.237\times 10^{-3}\text{ rad/s}$। বর্তমান বেগ $\omega_0 \approx 7.27\times 10^{-5}\text{ rad/s}$। অনুপাত $\frac{\omega}{\omega_0} = \frac{1.237\times 10^{-3}}{7.27\times 10^{-5}} \approx 17.06$ গুণ। নতুন পর্যায়কাল $T = \frac{2\pi}{\omega} = 2\pi\sqrt{\frac{R}{g}} \approx 5066\text{ s} \approx 84.4\text{ min} \approx 1.41\text{ h}$।</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>মহাকর্ষীয় সমাধান 4</t>
-        </is>
-      </c>
-      <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
+          <t>বর্তমান বেগের $\approx 17.06$ গুণ, দিনের দৈর্ঘ্য $\approx 1.41\text{ ঘণ্টা} = 84.4\text{ মিনিট}$</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -3853,38 +3598,38 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>ভূ-স্থির উপগ্রহের উচ্চতা ও কক্ষপথ (সমস্যা 5)</t>
+          <t>অভিকর্ষজ ত্বরণের পরিবর্তন ও পৃথিবীর ঘূর্ণন (Variation of g &amp; Planetology)</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F56" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>[সমস্যা 5: ভূ-স্থির উপগ্রহের উচ্চতা ও কক্ষপথ]
-একটি ভূ-স্থির উপগ্রহের পর্যায়কাল $T = 24\text{ ঘণ্টা}$। ভূপৃষ্ঠ হতে উপগ্রহটির উচ্চতা কত কিলোমিটার নির্ণয় কর। ($M = 6.0 \times 10^{24}\text{ kg}, R = 6400\text{ km}$)</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr"/>
+          <t>##GEO:circle[r=3][size:small]##
+ভূপৃষ্ঠ হতে $h$ উচ্চতায় এবং খনির $d$ গভীরতায় অভিকর্ষজ ত্বরণের মান সমান হলে প্রমাণ কর যে ক্ষুদ্র উচ্চতার জন্য ($h \ll R$) $d = 2h$।</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=3][size:small]##</t>
+        </is>
+      </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>নিউটনের সার্বজনীন মহাকর্ষ সূত্র ও কেপলারের গ্রহীয় গতির সূত্রাবলি প্রয়োগ করে ধাপে ধাপে সমাধান (সমস্যা 5)।</t>
+          <t>ক্ষুদ্র উচ্চতার জন্য দ্বিপদী উপপাদ্য: $g_h = g(1 + h/R)^{-2} \approx g(1 - 2h/R)$। গভীরতায়: $g_d = g(1 - d/R)$। সমান করে: $g(1 - 2h/R) = g(1 - d/R) \implies 2h/R = d/R \implies d = 2h$।</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>মহাকর্ষীয় সমাধান 5</t>
-        </is>
-      </c>
-      <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr"/>
-      <c r="N56" t="inlineStr"/>
+          <t>$d = 2h$</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -3904,7 +3649,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>মহাকর্ষীয় বিভব ও কৃতকাজ (সমস্যা 6)</t>
+          <t>অভিকর্ষজ ত্বরণের পরিবর্তন ও পৃথিবীর ঘূর্ণন (Variation of g &amp; Planetology)</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -3917,25 +3662,25 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>[সমস্যা 6: মহাকর্ষীয় বিভব ও কৃতকাজ]
-$m = 2\text{ kg}$ ভরের একটি বস্তুকে অসীম দূরত্ব হতে পৃথিবীর পৃষ্ঠে নিয়ে আসতে মহাকর্ষ বল দ্বারা সম্পাদিত কাজের মান কত?</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr"/>
+          <t>##GEO:circle[r=3][size:small]##
+ঢাকার অক্ষাংশ $\lambda = 23.8^\circ$। ঢাকার অবস্থান সাপেক্ষে পৃথিবীর আবর্তন গতির কারণে অভিকর্ষজ ত্বরণ $g$-এর কার্যকর মান কত হ্রাস পায়? ($R = 6400\text{ km}$)।</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=3][size:small]##</t>
+        </is>
+      </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>নিউটনের সার্বজনীন মহাকর্ষ সূত্র ও কেপলারের গ্রহীয় গতির সূত্রাবলি প্রয়োগ করে ধাপে ধাপে সমাধান (সমস্যা 6)।</t>
+          <t>অক্ষাংশের প্রভাব: $g' = g - \omega^2 R \cos^2\lambda$। হ্রাস $\Delta g = \omega^2 R \cos^2(23.8^\circ)$। $\omega^2 R \approx 0.0338\text{ m/s}^2$। $\cos 23.8^\circ \approx 0.915 \implies \cos^2(23.8^\circ) \approx 0.837$। $\Delta g = 0.0338 \times 0.837 \approx 0.0283\text{ m/s}^2$।</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>মহাকর্ষীয় সমাধান 6</t>
-        </is>
-      </c>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr"/>
-      <c r="N57" t="inlineStr"/>
+          <t>হ্রাস $\Delta g = 0.0284\\text{ m/s}^2$</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -3955,38 +3700,38 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>পৃথিবী ও চাঁদের মধ্যবর্তী নিরপেক্ষ বিন্দু (সমস্যা 7)</t>
+          <t>অভিকর্ষজ ত্বরণের পরিবর্তন ও পৃথিবীর ঘূর্ণন (Variation of g &amp; Planetology)</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F58" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>[সমস্যা 7: পৃথিবী ও চাঁদের মধ্যবর্তী নিরপেক্ষ বিন্দু]
-পৃথিবীর ভর চাঁদের ভরের 4 গুণ এবং এদের মধ্যবর্তী দূরত্ব $d = 3.84 \times 10^5\text{ km}$। পৃথিবী ও চাঁদের সংযোগকারী সরলরেখার কোন বিন্দুতে লব্ধি মহাকর্ষীয় প্রাবল্য শূন্য হবে?</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr"/>
+          <t>##GEO:pendulum[angle=15,length=4][size:small]##
+একটি সরল দোলক ভূপৃষ্ঠে সঠিক সময় দেয়। দোলকটিকে একটি কয়লা খনির তলদেশে নিয়ে গেলে তা প্রতিদিন $20\text{ সেকেন্ড}$ ধীরে চলে। খনিটির গভীরতা কত? ($R = 6400\text{ km}$)।</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>##GEO:pendulum[angle=15,length=4][size:small]##</t>
+        </is>
+      </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>নিউটনের সার্বজনীন মহাকর্ষ সূত্র ও কেপলারের গ্রহীয় গতির সূত্রাবলি প্রয়োগ করে ধাপে ধাপে সমাধান (সমস্যা 7)।</t>
+          <t>প্রতিদিনের হারানো সময় $\Delta T = 86400 \times \frac{1}{2}\frac{\Delta g}{g}$। গভীরতায় $\frac{\Delta g}{g} = \frac{d}{R}$। $\Delta T = 86400 \times \frac{d}{2R} \implies 20 = 43200 \times \frac{d}{6400} \implies d = \frac{20 \times 6400}{43200} = \frac{128000}{43200} \approx 2.96\text{ km}$।</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>মহাকর্ষীয় সমাধান 7</t>
-        </is>
-      </c>
-      <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr"/>
-      <c r="N58" t="inlineStr"/>
+          <t>খনির গভীরতা $d = 2.96\\text{ km}$</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -4006,7 +3751,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>আহ্নিক গতির কারণে g-এর হ্রাস (সমস্যা 8)</t>
+          <t>অভিকর্ষজ ত্বরণের পরিবর্তন ও পৃথিবীর ঘূর্ণন (Variation of g &amp; Planetology)</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -4019,25 +3764,25 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>[সমস্যা 8: আহ্নিক গতির কারণে g-এর হ্রাস]
-বিষুবরেখা অঞ্চলে পৃথিবীর আহ্নিক গতির জন্য কোনো বস্তুর ওজনে শতকরা কত আপাত হ্রাস ঘটে? ($R = 6400\text{ km}, T = 86400\text{ s}$)</t>
-        </is>
-      </c>
-      <c r="H59" t="inlineStr"/>
+          <t>##GEO:circle[r=3][size:small]##
+একটি কৃত্রিম উপগ্রহ ভূপৃষ্ঠের ঠিক ওপর দিয়ে পৃথিবীকে প্রদক্ষিণ করছে। উপগ্রহটির পর্যায়কাল এবং পৃথিবীর গড় ঘনত্বের মধ্যে সম্পর্ক প্রতিপাদন কর।</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=3][size:small]##</t>
+        </is>
+      </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>নিউটনের সার্বজনীন মহাকর্ষ সূত্র ও কেপলারের গ্রহীয় গতির সূত্রাবলি প্রয়োগ করে ধাপে ধাপে সমাধান (সমস্যা 8)।</t>
+          <t>$T = \frac{2\pi R}{v} = 2\pi R \sqrt{\frac{R}{GM}} = 2\pi \sqrt{\frac{R^3}{G \cdot \frac{4}{3}\pi R^3 \rho}} = 2\pi\sqrt{\frac{3}{4\pi G\rho}} = \sqrt{\frac{3\pi}{G\rho}}$।</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>মহাকর্ষীয় সমাধান 8</t>
-        </is>
-      </c>
-      <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr"/>
-      <c r="N59" t="inlineStr"/>
+          <t>$T = \sqrt{\frac{3\pi}{G\rho}} \approx 84.4\text{ মিনিট}$</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -4057,38 +3802,38 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>কেপলারের ক্ষেত্রফলের সূত্র ও ক্ষেত্রীয় বেগ (সমস্যা 9)</t>
+          <t>অভিকর্ষজ ত্বরণের পরিবর্তন ও পৃথিবীর ঘূর্ণন (Variation of g &amp; Planetology)</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F60" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>[সমস্যা 9: কেপলারের ক্ষেত্রফলের সূত্র ও ক্ষেত্রীয় বেগ]
-একটি উপগ্রহ উপবৃত্তাকার কক্ষপথে আবর্তনের সময় নিকটতম দূরত্বে বেগ $v_1 = 8\text{ km/s}$ এবং দূরত্ব $r_1 = 11000\text{ km}$। দূরতম বিন্দুতে দূরত্ব $r_2 = 20000\text{ km}$ হলে সেখানে বেগ কত?</t>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr"/>
+          <t>##GEO:circle[r=2.5][size:small]##
+ভূপৃষ্ঠে কোনো বস্তুর মুক্তিবেগ $v_e = 11.2\text{ km/s}$। যদি পৃথিবীর ব্যাসার্ধ অপরিবর্তিত রেখে তার ভর দ্বিগুণ করা হয়, তবে নতুন মুক্তিবেগ কত হবে?</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>নিউটনের সার্বজনীন মহাকর্ষ সূত্র ও কেপলারের গ্রহীয় গতির সূত্রাবলি প্রয়োগ করে ধাপে ধাপে সমাধান (সমস্যা 9)।</t>
+          <t>মুক্তিবেগ $v_e = \sqrt{\frac{2GM}{R}}$। ভর দ্বিগুণ হলে $M' = 2M \implies v'_e = \sqrt{\frac{2G(2M)}{R}} = \sqrt{2}v_e = 1.414 \times 11.2 \approx 15.84\text{ km/s}$।</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>মহাকর্ষীয় সমাধান 9</t>
-        </is>
-      </c>
-      <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr"/>
-      <c r="N60" t="inlineStr"/>
+          <t>$v'_e = 15.84\\text{ km/s}$</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -4108,7 +3853,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>বাইনারি স্টার সিস্টেম ও অভিকর্ষ বল (সমস্যা 10)</t>
+          <t>অভিকর্ষজ ত্বরণের পরিবর্তন ও পৃথিবীর ঘূর্ণন (Variation of g &amp; Planetology)</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -4121,25 +3866,25 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>[সমস্যা 10: বাইনারি স্টার সিস্টেম ও অভিকর্ষ বল]
-মহাশূন্যে পরস্পর হতে $r = 10 \times 10^{11}\text{ m}$ দূরত্বে অবস্থিত দুটি নক্ষত্রের প্রতিটির ভর $M = 2.0 \times 10^{30}\text{ kg}$। এদের মধ্যকার মহাকর্ষীয় আকর্ষণ বলের মান নির্ণয় কর।</t>
-        </is>
-      </c>
-      <c r="H61" t="inlineStr"/>
+          <t>##GEO:circle[r=2.2][size:small]##
+মঙ্গল গ্রহের ভর পৃথিবীর ভরের $0.11$ গুণ এবং ব্যাসার্ধ পৃথিবীর ব্যাসার্ধের $0.53$ গুণ। মঙ্গল গ্রহের পৃষ্ঠে অভিকর্ষজ ত্বরণ এবং মুক্তিবেগ নির্ণয় কর ($g_{	ext{earth}} = 9.8\text{ ms}^{-2}, v_{e,	ext{earth}} = 11.2\text{ km/s}$)।</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=2.2][size:small]##</t>
+        </is>
+      </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>নিউটনের সার্বজনীন মহাকর্ষ সূত্র ও কেপলারের গ্রহীয় গতির সূত্রাবলি প্রয়োগ করে ধাপে ধাপে সমাধান (সমস্যা 10)।</t>
+          <t>$g_{\text{mars}} = g_{\text{earth}}\left(\frac{M_m}{M_e}\right)\left(\frac{R_e}{R_m}\right)^2 = 9.8(0.11)\left(\frac{1}{0.53}\right)^2 = 9.8(0.11)(3.56) \approx 3.84\text{ m/s}^2$। মুক্তিবেগ $v_{e,\text{mars}} = v_{e,\text{earth}}\sqrt{\frac{M_m/M_e}{R_m/R_e}} = 11.2\sqrt{\frac{0.11}{0.53}} = 11.2\sqrt{0.2075} = 11.2(0.4556) \approx 5.10\text{ km/s}$।</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>মহাকর্ষীয় সমাধান 10</t>
-        </is>
-      </c>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr"/>
-      <c r="N61" t="inlineStr"/>
+          <t>$g_{\text{mars}} = 3.84\\text{ m/s}^2, v_{e,\text{mars}} = 5.10\\text{ km/s}$</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -4159,43 +3904,38 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>কেপলারের ৩য় সূত্র ও উপগ্রহের পর্যায়কাল (সমস্যা 11)</t>
+          <t>মহাকর্ষীয় বিভব, প্রাবল্য ও কৃত্রিম উপগ্রহ (Gravitational Potential &amp; Orbits)</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F62" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>[সমস্যা 11: কেপলারের ৩য় সূত্র ও উপগ্রহের পর্যায়কাল]
-##PRESET:kepler-orbit[size:medium]##
-পৃথিবীর পৃষ্ঠ হতে $h = 1200\text{ km}$ উচ্চতায় একটি কৃত্রিম উপগ্রহ বৃত্তাকার কক্ষপথে পৃথিবীকে প্রদক্ষিণ করছে। পৃথিবীর ভর $M = 6.0 \times 10^{24}\text{ kg}$ এবং ব্যাসার্ধ $R = 6400\text{ km}$ হলে উপগ্রহটির কক্ষীয় দ্রুতি এবং পর্যায়কাল কত?</t>
+          <t>##GEO:circle[r=3.5][size:small]##
+পৃথিবী ও চাঁদের কেন্দ্রদ্বয়ের মধ্যবর্তী দূরত্ব $r = 3.84 	imes 10^8\text{ m}$। পৃথিবীর ভর চাঁদের ভরের ৮১ গুণ ($M_e = 81 M_m$)। পৃথিবী ও চাঁদের সংযোগকারী সরলরেখার কোন বিন্দুতে লব্ধি মহাকর্ষীয় প্রাবল্যের মান শূন্য হবে?</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>##PRESET:kepler-orbit[size:medium]##</t>
+          <t>##GEO:circle[r=3.5][size:small]##</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>নিউটনের সার্বজনীন মহাকর্ষ সূত্র ও কেপলারের গ্রহীয় গতির সূত্রাবলি প্রয়োগ করে ধাপে ধাপে সমাধান (সমস্যা 11)।</t>
+          <t>ধরি পৃথিবীর কেন্দ্র হতে $x$ দূরত্বে প্রাবল্য শূন্য: $\frac{G M_e}{x^2} = \frac{G M_m}{(r - x)^2} \implies \frac{81}{x^2} = \frac{1}{(r-x)^2}$। বর্গমূল নিয়ে: $\frac{9}{x} = \frac{1}{r - x} \implies 9r - 9x = x \implies 10x = 9r \implies x = 0.9r = 0.9(3.84 \times 10^8) = 3.456 \times 10^8\text{ m}$।</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>মহাকর্ষীয় সমাধান 11</t>
-        </is>
-      </c>
-      <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr"/>
-      <c r="N62" t="inlineStr"/>
+          <t>পৃথিবীর কেন্দ্র হতে $3.456 \times 10^8\\text{ m}$ দূরে</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -4215,7 +3955,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>ভূপৃষ্ঠ থেকে উচ্চতায় g-এর মান (সমস্যা 12)</t>
+          <t>মহাকর্ষীয় বিভব, প্রাবল্য ও কৃত্রিম উপগ্রহ (Gravitational Potential &amp; Orbits)</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -4228,25 +3968,25 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>[সমস্যা 12: ভূপৃষ্ঠ থেকে উচ্চতায় g-এর মান]
-ভূপৃষ্ঠ হতে কত উচ্চতায় অভিকর্ষজ ত্বরণের মান ভূপৃষ্ঠের মানের $\frac{1}{7}$ অংশ হবে? (পৃথিবীর ব্যাসার্ধ $R = 6400\text{ km}$)</t>
-        </is>
-      </c>
-      <c r="H63" t="inlineStr"/>
+          <t>##GEO:circle[r=3][size:small]##
+একটি ভূ-স্থির উপগ্রহের (Geostationary Satellite) উচ্চতা ভূপৃষ্ঠ হতে কত কিলোমিটার? ($M = 6.0 	imes 10^{24}\text{ kg}, R = 6400\text{ km}, G = 6.673 	imes 10^{-11}\text{ N m}^2/\text{kg}^2$)।</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=3][size:small]##</t>
+        </is>
+      </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>নিউটনের সার্বজনীন মহাকর্ষ সূত্র ও কেপলারের গ্রহীয় গতির সূত্রাবলি প্রয়োগ করে ধাপে ধাপে সমাধান (সমস্যা 12)।</t>
+          <t>ভূ-স্থির উপগ্রহের পর্যায়কাল $T = 24\text{ h} = 86400\text{ s}$। কক্ষীয় ব্যাসার্ধ $r^3 = \frac{G M T^2}{4\pi^2} = \frac{(6.673\times 10^{-11})(6.0\times 10^{24})(86400)^2}{4\pi^2} \approx \frac{4.0038\times 10^{14} \times 7.465\times 10^9}{39.478} \approx 7.57\times 10^{22}\text{ m}^3$। $r = \sqrt[3]{7.57\times 10^{22}} \approx 4.23 \times 10^7\text{ m} = 42300\text{ km}$। উচ্চতা $h = r - R = 42300 - 6400 = 35900\text{ km}$।</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>মহাকর্ষীয় সমাধান 12</t>
-        </is>
-      </c>
-      <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr"/>
-      <c r="N63" t="inlineStr"/>
+          <t>উচ্চতা $h \approx 35938\\text{ km} \approx 3.59 \times 10^4\\text{ km}$</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -4266,38 +4006,38 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>খনিতে বা গভীরতায় g-এর পরিবর্তন (সমস্যা 13)</t>
+          <t>মহাকর্ষীয় বিভব, প্রাবল্য ও কৃত্রিম উপগ্রহ (Gravitational Potential &amp; Orbits)</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F64" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>[সমস্যা 13: খনিতে বা গভীরতায় g-এর পরিবর্তন]
-ভূপৃষ্ঠ হতে কত গভীরে খনির ভেতর প্রবেশ করলে অভিকর্ষজ ত্বরণের মান ভূপৃষ্ঠের মানের $40\%$ হ্রাস পাবে?</t>
-        </is>
-      </c>
-      <c r="H64" t="inlineStr"/>
+          <t>##GEO:circle[r=3][size:small]##
+ভূপৃষ্ঠ হতে $h = 600\text{ km}$ উচ্চতায় একটি নজরদারি উপগ্রহ পৃথিবীকে বৃত্তাকার কক্ষপথে প্রদক্ষিণ করছে। উপগ্রহটির কক্ষীয় দ্রুতি $v_o$ এবং পর্যায়কাল $T$ নির্ণয় কর ($R = 6400\text{ km}, g = 9.8\text{ ms}^{-2}$)।</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=3][size:small]##</t>
+        </is>
+      </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>নিউটনের সার্বজনীন মহাকর্ষ সূত্র ও কেপলারের গ্রহীয় গতির সূত্রাবলি প্রয়োগ করে ধাপে ধাপে সমাধান (সমস্যা 13)।</t>
+          <t>কক্ষীয় ব্যাসার্ধ $r = R + h = 6400 + 600 = 7000\text{ km} = 7.0 \times 10^6\text{ m}$। কক্ষীয় দ্রুতি $v_o = \sqrt{\frac{GM}{r}} = R\sqrt{\frac{g}{r}} = 6.4\times 10^6 \sqrt{\frac{9.8}{7.0\times 10^6}} \approx 7560\text{ m/s} = 7.56\text{ km/s}$। পর্যায়কাল $T = \frac{2\pi r}{v_o} = \frac{2\pi(7.0\times 10^6)}{7560} \approx 5818\text{ s} \approx 96.97\text{ min}$।</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>মহাকর্ষীয় সমাধান 13</t>
-        </is>
-      </c>
-      <c r="K64" t="inlineStr"/>
-      <c r="L64" t="inlineStr"/>
-      <c r="M64" t="inlineStr"/>
-      <c r="N64" t="inlineStr"/>
+          <t>$v_o = 7.56\\text{ km/s}, T = 96.7\\text{ মিনিট}$</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -4317,7 +4057,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>মুক্তিবেগ ও গ্রহের ঘনত্ব (সমস্যা 14)</t>
+          <t>মহাকর্ষীয় বিভব, প্রাবল্য ও কৃত্রিম উপগ্রহ (Gravitational Potential &amp; Orbits)</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -4330,30 +4070,25 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>[সমস্যা 14: মুক্তিবেগ ও গ্রহের ঘনত্ব]
-##GEO:sphere[r=4][size:small]##
-একটি গ্রহের ভর পৃথিবীর ভরের 6 গুণ কিন্তু ব্যাসার্ধ পৃথিবীর ব্যাসার্ধের 11 গুণ। পৃথিবীর পৃষ্ঠে মুক্তিবেগ $11.2\text{ km/s}$ হলে ঐ গ্রহের পৃষ্ঠে মুক্তিবেগ কত?</t>
+          <t>##GEO:circle[r=3.5][size:small]##
+একটি $m = 1000\text{ kg}$ ভরের কৃত্রিম উপগ্রহকে $r_1 = 7000\text{ km}$ ব্যাসার্ধের কক্ষপথ হতে $r_2 = 14000\text{ km}$ ব্যাসার্ধের উচ্চতর কক্ষপথে স্থানান্তর করতে কত মেগাজুল শক্তি প্রয়োজন? ($M_e = 6.0 	imes 10^{24}\text{ kg}$)।</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>##GEO:sphere[r=4][size:small]##</t>
+          <t>##GEO:circle[r=3.5][size:small]##</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>নিউটনের সার্বজনীন মহাকর্ষ সূত্র ও কেপলারের গ্রহীয় গতির সূত্রাবলি প্রয়োগ করে ধাপে ধাপে সমাধান (সমস্যা 14)।</t>
+          <t>কক্ষপথে উপগ্রহের মোট যান্ত্রিক শক্তি $E = -\frac{GMm}{2r}$। শক্তি পরিবর্তন $\Delta E = E_2 - E_1 = -\frac{GMm}{2r_2} - \left(-\frac{GMm}{2r_1}\right) = \frac{GMm}{2}\left(\frac{1}{r_1} - \frac{1}{r_2}\right)$। $\Delta E = \frac{(6.673\times 10^{-11})(6.0\times 10^{24})(1000)}{2}\left(\frac{1}{7\times 10^6} - \frac{1}{14\times 10^6}\right) = 2.002\times 10^{17}\left(\frac{1}{14\times 10^6}\right) \approx 1.43\times 10^{10}\text{ J} = 14300\text{ MJ}$।</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>মহাকর্ষীয় সমাধান 14</t>
-        </is>
-      </c>
-      <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr"/>
-      <c r="M65" t="inlineStr"/>
-      <c r="N65" t="inlineStr"/>
+          <t>প্রয়োজনীয় শক্তি $\Delta E = 1.43 \times 10^4\\text{ MJ}$</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -4373,38 +4108,38 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>ভূ-স্থির উপগ্রহের উচ্চতা ও কক্ষপথ (সমস্যা 15)</t>
+          <t>মহাকর্ষীয় বিভব, প্রাবল্য ও কৃত্রিম উপগ্রহ (Gravitational Potential &amp; Orbits)</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F66" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>[সমস্যা 15: ভূ-স্থির উপগ্রহের উচ্চতা ও কক্ষপথ]
-একটি ভূ-স্থির উপগ্রহের পর্যায়কাল $T = 24\text{ ঘণ্টা}$। ভূপৃষ্ঠ হতে উপগ্রহটির উচ্চতা কত কিলোমিটার নির্ণয় কর। ($M = 6.0 \times 10^{24}\text{ kg}, R = 6400\text{ km}$)</t>
-        </is>
-      </c>
-      <c r="H66" t="inlineStr"/>
+          <t>##GEO:circle[r=2.5][size:small]##
+একটি $M$ ভর এবং $R$ ব্যাসার্ধের সুষম নিরেট গোলকের কেন্দ্রে মহাকর্ষীয় বিভব নির্ণয় কর এবং দেখাও যে কেন্দ্রের বিভব পৃষ্ঠের বিভবের $1.5$ গুণ ($V_c = rac{3}{2}V_s$)।</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>নিউটনের সার্বজনীন মহাকর্ষ সূত্র ও কেপলারের গ্রহীয় গতির সূত্রাবলি প্রয়োগ করে ধাপে ধাপে সমাধান (সমস্যা 15)।</t>
+          <t>পৃষ্ঠে বিভব $V_s = -\frac{GM}{R}$। গোলকের অভ্যন্তরে মহাকর্ষীয় প্রাবল্য $E(r) = \frac{GM r}{R^3}$। কেন্দ্রে বিভব: $V_c - V_s = -\int_R^0 E(r) dr = \int_0^R \frac{GM r}{R^3} dr = \frac{GM}{R^3}\left[\frac{r^2}{2}\right]_0^R = \frac{GM}{2R}$। অতএব $V_c = V_s - \frac{GM}{2R} = -\frac{GM}{R} - \frac{GM}{2R} = -\frac{3GM}{2R}$।</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>মহাকর্ষীয় সমাধান 15</t>
-        </is>
-      </c>
-      <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr"/>
-      <c r="M66" t="inlineStr"/>
-      <c r="N66" t="inlineStr"/>
+          <t>$V_c = -\frac{3GM}{2R} = 1.5 V_s$</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -4424,7 +4159,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>মহাকর্ষীয় বিভব ও কৃতকাজ (সমস্যা 16)</t>
+          <t>মহাকর্ষীয় বিভব, প্রাবল্য ও কৃত্রিম উপগ্রহ (Gravitational Potential &amp; Orbits)</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -4437,25 +4172,25 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>[সমস্যা 16: মহাকর্ষীয় বিভব ও কৃতকাজ]
-$m = 10\text{ kg}$ ভরের একটি বস্তুকে অসীম দূরত্ব হতে পৃথিবীর পৃষ্ঠে নিয়ে আসতে মহাকর্ষ বল দ্বারা সম্পাদিত কাজের মান কত?</t>
-        </is>
-      </c>
-      <c r="H67" t="inlineStr"/>
+          <t>##GEO:circle[r=3][size:small]##
+একটি গ্রহের ঘনত্ব পৃথিবীর ঘনত্বের সমান কিন্তু এর ব্যাসার্ধ পৃথিবীর ব্যাসার্ধের দ্বিগুণ। গ্রহটির পৃষ্ঠে মুক্তিবেগ পৃথিবীর মুক্তিবেগের কত গুণ হবে?</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=3][size:small]##</t>
+        </is>
+      </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>নিউটনের সার্বজনীন মহাকর্ষ সূত্র ও কেপলারের গ্রহীয় গতির সূত্রাবলি প্রয়োগ করে ধাপে ধাপে সমাধান (সমস্যা 16)।</t>
+          <t>ঘনত্ব $\rho$ দ্বারা মুক্তিবেগ: $v_e = \sqrt{\frac{2GM}{R}} = \sqrt{\frac{2G(\frac{4}{3}\pi R^3 \rho)}{R}} = R\sqrt{\frac{8\pi G\rho}{3}} \propto R\sqrt{\rho}$। যেহেতু ঘনত্ব সমান, তাই $v_e \propto R$। ব্যাসার্ধ দ্বিগুণ হলে মুক্তিবেগও দ্বিগুণ হবে: $v'_e = 2(11.2) = 22.4\text{ km/s}$।</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>মহাকর্ষীয় সমাধান 16</t>
-        </is>
-      </c>
-      <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr"/>
-      <c r="M67" t="inlineStr"/>
-      <c r="N67" t="inlineStr"/>
+          <t>$v'_{e} = 2 v_e = 22.4\\text{ km/s}$</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -4475,38 +4210,38 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>পৃথিবী ও চাঁদের মধ্যবর্তী নিরপেক্ষ বিন্দু (সমস্যা 17)</t>
+          <t>মহাকর্ষীয় বিভব, প্রাবল্য ও কৃত্রিম উপগ্রহ (Gravitational Potential &amp; Orbits)</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F68" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>[সমস্যা 17: পৃথিবী ও চাঁদের মধ্যবর্তী নিরপেক্ষ বিন্দু]
-পৃথিবীর ভর চাঁদের ভরের 12 গুণ এবং এদের মধ্যবর্তী দূরত্ব $d = 3.84 \times 10^5\text{ km}$। পৃথিবী ও চাঁদের সংযোগকারী সরলরেখার কোন বিন্দুতে লব্ধি মহাকর্ষীয় প্রাবল্য শূন্য হবে?</t>
-        </is>
-      </c>
-      <c r="H68" t="inlineStr"/>
+          <t>##GEO:circle[r=2.5][size:small]##
+একটি রকেটকে পৃথিবী হতে এমন বেগে নিক্ষেপ করা হলো যেন তা অসীমে গিয়ে $v_{\infty} = 2.0\text{ km/s}$ শেষবেগ বজায় রাখে। ভূপৃষ্ঠ হতে রকেটটিকে কত বেগে উৎক্ষেপণ করা হয়েছিল? ($v_e = 11.2\text{ km/s}$)।</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>নিউটনের সার্বজনীন মহাকর্ষ সূত্র ও কেপলারের গ্রহীয় গতির সূত্রাবলি প্রয়োগ করে ধাপে ধাপে সমাধান (সমস্যা 17)।</t>
+          <t>শক্তির নিত্যতা: $\frac{1}{2}m v_0^2 - \frac{GMm}{R} = \frac{1}{2}m v_{\infty}^2 \implies v_0^2 = v_{\infty}^2 + \frac{2GM}{R} = v_{\infty}^2 + v_e^2$। $v_0 = \sqrt{v_e^2 + v_{\infty}^2} = \sqrt{(11.2)^2 + (2.0)^2} = \sqrt{125.44 + 4} = \sqrt{129.44} \approx 11.38\text{ km/s}$।</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>মহাকর্ষীয় সমাধান 17</t>
-        </is>
-      </c>
-      <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr"/>
-      <c r="M68" t="inlineStr"/>
-      <c r="N68" t="inlineStr"/>
+          <t>$v_0 = 11.38\\text{ km/s}$</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -4526,7 +4261,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>আহ্নিক গতির কারণে g-এর হ্রাস (সমস্যা 18)</t>
+          <t>মহাকর্ষীয় বিভব, প্রাবল্য ও কৃত্রিম উপগ্রহ (Gravitational Potential &amp; Orbits)</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -4539,25 +4274,25 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>[সমস্যা 18: আহ্নিক গতির কারণে g-এর হ্রাস]
-বিষুবরেখা অঞ্চলে পৃথিবীর আহ্নিক গতির জন্য কোনো বস্তুর ওজনে শতকরা কত আপাত হ্রাস ঘটে? ($R = 6400\text{ km}, T = 86400\text{ s}$)</t>
-        </is>
-      </c>
-      <c r="H69" t="inlineStr"/>
+          <t>##GEO:circle[r=3.5][size:small]##
+দুটি কৃত্রিম উপগ্রহ $A$ ও $B$ যথাক্রমে $4R$ এবং $R$ ব্যাসার্ধের বৃত্তাকার কক্ষপথে পৃথিবীকে প্রদক্ষিণ করছে। উপগ্রহদ্বয়ের পর্যায়কালের অনুপাত $T_A / T_B$ এবং কক্ষীয় বেগের অনুপাত $v_A / v_B$ কত?</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=3.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>নিউটনের সার্বজনীন মহাকর্ষ সূত্র ও কেপলারের গ্রহীয় গতির সূত্রাবলি প্রয়োগ করে ধাপে ধাপে সমাধান (সমস্যা 18)।</t>
+          <t>কেপলারের ৩য় সূত্র: $\frac{T_A^2}{T_B^2} = \left(\frac{r_A}{r_B}\right)^3 = \left(\frac{4R}{R}\right)^3 = 4^3 = 64 \implies \frac{T_A}{T_B} = \sqrt{64} = 8$। কক্ষীয় বেগ $v \propto \frac{1}{\sqrt{r}} \implies \frac{v_A}{v_B} = \sqrt{\frac{r_B}{r_A}} = \sqrt{\frac{R}{4R}} = \frac{1}{2}$।</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>মহাকর্ষীয় সমাধান 18</t>
-        </is>
-      </c>
-      <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr"/>
-      <c r="N69" t="inlineStr"/>
+          <t>$T_A / T_B = 8, v_A / v_B = 1/2$</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -4577,38 +4312,38 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>কেপলারের ক্ষেত্রফলের সূত্র ও ক্ষেত্রীয় বেগ (সমস্যা 19)</t>
+          <t>মহাকর্ষীয় বিভব, প্রাবল্য ও কৃত্রিম উপগ্রহ (Gravitational Potential &amp; Orbits)</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F70" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>[সমস্যা 19: কেপলারের ক্ষেত্রফলের সূত্র ও ক্ষেত্রীয় বেগ]
-একটি উপগ্রহ উপবৃত্তাকার কক্ষপথে আবর্তনের সময় নিকটতম দূরত্বে বেগ $v_1 = 4\text{ km/s}$ এবং দূরত্ব $r_1 = 11000\text{ km}$। দূরতম বিন্দুতে দূরত্ব $r_2 = 35000\text{ km}$ হলে সেখানে বেগ কত?</t>
-        </is>
-      </c>
-      <c r="H70" t="inlineStr"/>
+          <t>##GEO:circle[r=3.8][size:small]##
+সূর্য হতে বৃহস্পতির গড় দূরত্ব পৃথিবী হতে সূর্যের দূরত্বের $5.2$ গুণ। সৌরজগতে বৃহস্পতির সূর্যকে একবার প্রদক্ষিণ করতে পৃথিবীর কত বছর সময় লাগে?</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=3.8][size:small]##</t>
+        </is>
+      </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>নিউটনের সার্বজনীন মহাকর্ষ সূত্র ও কেপলারের গ্রহীয় গতির সূত্রাবলি প্রয়োগ করে ধাপে ধাপে সমাধান (সমস্যা 19)।</t>
+          <t>কেপলারের ৩য় সূত্র: $\frac{T_J}{T_E} = \left(\frac{r_J}{r_E}\right)^{3/2} = (5.2)^{1.5} \approx 11.86$। পৃথিবী বছর $T_E = 1\text{ year}$ হওয়ায় $T_J \approx 11.86\text{ years}$।</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>মহাকর্ষীয় সমাধান 19</t>
-        </is>
-      </c>
-      <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr"/>
-      <c r="M70" t="inlineStr"/>
-      <c r="N70" t="inlineStr"/>
+          <t>$T_J = 11.86\\text{ পৃথিবী বছর}$</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -4628,7 +4363,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>বাইনারি স্টার সিস্টেম ও অভিকর্ষ বল (সমস্যা 20)</t>
+          <t>মহাকর্ষীয় বিভব, প্রাবল্য ও কৃত্রিম উপগ্রহ (Gravitational Potential &amp; Orbits)</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -4641,25 +4376,25 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>[সমস্যা 20: বাইনারি স্টার সিস্টেম ও অভিকর্ষ বল]
-মহাশূন্যে পরস্পর হতে $r = 6 \times 10^{11}\text{ m}$ দূরত্বে অবস্থিত দুটি নক্ষত্রের প্রতিটির ভর $M = 2.0 \times 10^{30}\text{ kg}$। এদের মধ্যকার মহাকর্ষীয় আকর্ষণ বলের মান নির্ণয় কর।</t>
-        </is>
-      </c>
-      <c r="H71" t="inlineStr"/>
+          <t>##GEO:circle[r=2.5][size:small]##
+একটি ব্ল্যাকহোলের ভর সূর্যের ভরের সমান ($M = 2.0 	imes 10^{30}\text{ kg}$)। এর শোয়ার্জশিল্ড ব্যাসার্ধ (Schwarzschild radius) অর্থাৎ ঘটনা দিগন্তের ব্যাসার্ধ কত মিটার? ($c = 3.0 	imes 10^8\text{ m/s}, G = 6.673 	imes 10^{-11}\text{ N m}^2/\text{kg}^2$)।</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>নিউটনের সার্বজনীন মহাকর্ষ সূত্র ও কেপলারের গ্রহীয় গতির সূত্রাবলি প্রয়োগ করে ধাপে ধাপে সমাধান (সমস্যা 20)।</t>
+          <t>শোয়ার্জশিল্ড ব্যাসার্ধে মুক্তিবেগ আলোর বেগের সমান ($v_e = c$): $c = \sqrt{\frac{2GM}{R_s}} \implies R_s = \frac{2GM}{c^2} = \frac{2(6.673\times 10^{-11})(2.0\times 10^{30})}{(3.0\times 10^8)^2} = \frac{2.6692\times 10^{20}}{9.0\times 10^{16}} \approx 2966\text{ m} \approx 2.97\text{ km}$।</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>মহাকর্ষীয় সমাধান 20</t>
-        </is>
-      </c>
-      <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr"/>
-      <c r="M71" t="inlineStr"/>
-      <c r="N71" t="inlineStr"/>
+          <t>$R_s = 2.97\\text{ km} \approx 2966\\text{ m}$</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -4679,43 +4414,38 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>কেপলারের ৩য় সূত্র ও উপগ্রহের পর্যায়কাল (সমস্যা 21)</t>
+          <t>উন্নত কক্ষপথ বলবিদ্যা, কেপলারের সূত্র ও মহাকর্ষীয় বিভব (Advanced Orbital Mechanics &amp; Potentials)</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F72" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>[সমস্যা 21: কেপলারের ৩য় সূত্র ও উপগ্রহের পর্যায়কাল]
-##PRESET:kepler-orbit[size:medium]##
-পৃথিবীর পৃষ্ঠ হতে $h = 800\text{ km}$ উচ্চতায় একটি কৃত্রিম উপগ্রহ বৃত্তাকার কক্ষপথে পৃথিবীকে প্রদক্ষিণ করছে। পৃথিবীর ভর $M = 6.0 \times 10^{24}\text{ kg}$ এবং ব্যাসার্ধ $R = 6400\text{ km}$ হলে উপগ্রহটির কক্ষীয় দ্রুতি এবং পর্যায়কাল কত?</t>
+          <t>##GEO:circle[r=3.5][size:small]##
+একটি বৃত্তাকার কক্ষপথে প্রদক্ষিণরত কোনো উপগ্রহের গতিশক্তি $K$, মহাকর্ষীয় বিভবশক্তি $U$ এবং মোট যান্ত্রিক শক্তি $E$-এর মধ্যকার অনুপাত এবং সম্পর্ক প্রমাণ কর।</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>##PRESET:kepler-orbit[size:medium]##</t>
+          <t>##GEO:circle[r=3.5][size:small]##</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>নিউটনের সার্বজনীন মহাকর্ষ সূত্র ও কেপলারের গ্রহীয় গতির সূত্রাবলি প্রয়োগ করে ধাপে ধাপে সমাধান (সমস্যা 21)।</t>
+          <t>কক্ষীয় দ্রুতি $v = \sqrt{\frac{GM}{r}}$। গতিশক্তি $K = \frac{1}{2}m v^2 = \frac{GMm}{2r}$। বিভবশক্তি $U = -\frac{GMm}{r}$। মোট শক্তি $E = K + U = \frac{GMm}{2r} - \frac{GMm}{r} = -\frac{GMm}{2r}$। অতএব $E = -K$ এবং $U = -2K \implies K : U : E = 1 : -2 : -1$।</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>মহাকর্ষীয় সমাধান 21</t>
-        </is>
-      </c>
-      <c r="K72" t="inlineStr"/>
-      <c r="L72" t="inlineStr"/>
-      <c r="M72" t="inlineStr"/>
-      <c r="N72" t="inlineStr"/>
+          <t>$K : U : E = 1 : -2 : -1$, $E = -K = \frac{1}{2}U$</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -4735,12 +4465,12 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>ভূপৃষ্ঠ থেকে উচ্চতায় g-এর মান (সমস্যা 22)</t>
+          <t>উন্নত কক্ষপথ বলবিদ্যা, কেপলারের সূত্র ও মহাকর্ষীয় বিভব (Advanced Orbital Mechanics &amp; Potentials)</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F73" t="n">
@@ -4748,25 +4478,25 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>[সমস্যা 22: ভূপৃষ্ঠ থেকে উচ্চতায় g-এর মান]
-ভূপৃষ্ঠ হতে কত উচ্চতায় অভিকর্ষজ ত্বরণের মান ভূপৃষ্ঠের মানের $\frac{1}{7}$ অংশ হবে? (পৃথিবীর ব্যাসার্ধ $R = 6400\text{ km}$)</t>
-        </is>
-      </c>
-      <c r="H73" t="inlineStr"/>
+          <t>##GEO:circle[r=3][size:small]##
+কেপলারের দ্বিতীয় সূত্র অনুসারে কোনো গ্রহের ক্ষেত্রীয় দ্রুতি (Areal velocity) $\frac{dA}{dt}$ কৌণিক ভরবেগ $L$-এর সাথে সম্পর্কিত। দেখাও যে কেন্দ্রীয় বলের ক্ষেত্রে $\frac{dA}{dt} = \frac{L}{2m} = \text{ধ্রুবক}$।</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=3][size:small]##</t>
+        </is>
+      </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>নিউটনের সার্বজনীন মহাকর্ষ সূত্র ও কেপলারের গ্রহীয় গতির সূত্রাবলি প্রয়োগ করে ধাপে ধাপে সমাধান (সমস্যা 22)।</t>
+          <t>$dt$ সময়ে ব্যাসার্ধ ভেক্টর দ্বারা উৎপন্ন ত্রিভুজের ক্ষেত্রফল $dA = \frac{1}{2}|\vec{r} \times d\vec{r}| = \frac{1}{2}|\vec{r} \times \vec{v}| dt$। ক্ষেত্রীয় বেগ $\frac{dA}{dt} = \frac{1}{2}|\vec{r} \times \vec{v}| = \frac{|\vec{r} \times m\vec{v}|}{2m} = \frac{L}{2m}$। মহাকর্ষ বল কেন্দ্রীয় বল হওয়ায় টর্ক $\vec{\tau} = \vec{r} \times \vec{F} = \vec{0}$, ফলে কৌণিক ভরবেগ $L$ সংরক্ষিত এবং ক্ষেত্রীয় বেগ ধ্রুব থাকে।</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>মহাকর্ষীয় সমাধান 22</t>
-        </is>
-      </c>
-      <c r="K73" t="inlineStr"/>
-      <c r="L73" t="inlineStr"/>
-      <c r="M73" t="inlineStr"/>
-      <c r="N73" t="inlineStr"/>
+          <t>$\frac{dA}{dt} = \frac{L}{2m} = \text{constant}$</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -4786,38 +4516,38 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>খনিতে বা গভীরতায় g-এর পরিবর্তন (সমস্যা 23)</t>
+          <t>উন্নত কক্ষপথ বলবিদ্যা, কেপলারের সূত্র ও মহাকর্ষীয় বিভব (Advanced Orbital Mechanics &amp; Potentials)</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F74" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>[সমস্যা 23: খনিতে বা গভীরতায় g-এর পরিবর্তন]
-ভূপৃষ্ঠ হতে কত গভীরে খনির ভেতর প্রবেশ করলে অভিকর্ষজ ত্বরণের মান ভূপৃষ্ঠের মানের $20\%$ হ্রাস পাবে?</t>
-        </is>
-      </c>
-      <c r="H74" t="inlineStr"/>
+          <t>##GEO:circle[r=3.8][size:small]##
+একটি ধূমকেতু উপবৃত্তাকার কক্ষপথে সূর্যকে প্রদক্ষিণ করছে। সূর্যের নিকটতম দূরত্বে (Perihelion) এর দ্রুতি $v_p = 60\text{ km/s}$ এবং দূরত্ব $r_p = 8.0 	imes 10^7\text{ km}$। সূর্য হতে এর দূরতম দূরত্বে (Aphelion) $r_a = 1.6 	imes 10^9\text{ km}$ হলে দূরতম বিন্দুতে দ্রুতি $v_a$ কত?</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=3.8][size:small]##</t>
+        </is>
+      </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>নিউটনের সার্বজনীন মহাকর্ষ সূত্র ও কেপলারের গ্রহীয় গতির সূত্রাবলি প্রয়োগ করে ধাপে ধাপে সমাধান (সমস্যা 23)।</t>
+          <t>কৌণিক ভরবেগের নিত্যতা: $m r_p v_p = m r_a v_a \implies v_a = v_p \left(\frac{r_p}{r_a}\right) = 60 \left(\frac{8.0\times 10^7}{1.6\times 10^9}\right) = 60 \times \frac{1}{20} = 3.0\text{ km/s}$।</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>মহাকর্ষীয় সমাধান 23</t>
-        </is>
-      </c>
-      <c r="K74" t="inlineStr"/>
-      <c r="L74" t="inlineStr"/>
-      <c r="M74" t="inlineStr"/>
-      <c r="N74" t="inlineStr"/>
+          <t>$v_a = 3.0\text{ km/s}$</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -4837,12 +4567,12 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>মুক্তিবেগ ও গ্রহের ঘনত্ব (সমস্যা 24)</t>
+          <t>উন্নত কক্ষপথ বলবিদ্যা, কেপলারের সূত্র ও মহাকর্ষীয় বিভব (Advanced Orbital Mechanics &amp; Potentials)</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F75" t="n">
@@ -4850,30 +4580,25 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>[সমস্যা 24: মুক্তিবেগ ও গ্রহের ঘনত্ব]
-##GEO:sphere[r=4][size:small]##
-একটি গ্রহের ভর পৃথিবীর ভরের 2 গুণ কিন্তু ব্যাসার্ধ পৃথিবীর ব্যাসার্ধের 11 গুণ। পৃথিবীর পৃষ্ঠে মুক্তিবেগ $11.2\text{ km/s}$ হলে ঐ গ্রহের পৃষ্ঠে মুক্তিবেগ কত?</t>
+          <t>##GEO:circle[r=3][size:small]##
+একটি সুরঙ্গ পৃথিবীর কেন্দ্র দিয়ে এক প্রান্ত হতে অপর প্রান্ত পর্যন্ত খনন করা হলো। সুরঙ্গে একটি বস্তুকে ছেড়ে দিলে এটি সরল ছন্দিত স্পন্দনে আন্দোলিত হতে থাকে। প্রমাণ কর যে এর দোলনকাল $T = 2\pi\sqrt{\frac{R}{g}}$ এবং বস্তুটি সুরঙ্গের একপ্রান্ত হতে অন্যপ্রান্তে পৌঁছাতে কত মিনিট সময় নিবে? ($R = 6400\text{ km}, g = 9.8\text{ ms}^{-2}$)।</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>##GEO:sphere[r=4][size:small]##</t>
+          <t>##GEO:circle[r=3][size:small]##</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>নিউটনের সার্বজনীন মহাকর্ষ সূত্র ও কেপলারের গ্রহীয় গতির সূত্রাবলি প্রয়োগ করে ধাপে ধাপে সমাধান (সমস্যা 24)।</t>
+          <t>কেন্দ্র হতে $x$ দূরত্বে ত্বরণ $a = -\frac{g}{R}x$। এটি একটি সরল ছন্দিত স্পন্দন যেখানে $\omega^2 = \frac{g}{R} \implies \omega = \sqrt{\frac{g}{R}}$। পর্যায়কাল $T = \frac{2\pi}{\omega} = 2\pi\sqrt{\frac{R}{g}} = 2\pi\sqrt{\frac{6.4\times 10^6}{9.8}} \approx 5066\text{ s} \approx 84.4\text{ min}$। সুরঙ্গ অতিক্রম করতে সময় $t = T/2 = 42.2\text{ min}$।</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>মহাকর্ষীয় সমাধান 24</t>
-        </is>
-      </c>
-      <c r="K75" t="inlineStr"/>
-      <c r="L75" t="inlineStr"/>
-      <c r="M75" t="inlineStr"/>
-      <c r="N75" t="inlineStr"/>
+          <t>পর্যায়কাল $T = 84.4\text{ মিনিট}$, একপ্রান্ত হতে অন্যপ্রান্তে যেতে সময় $42.2\text{ মিনিট}$</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -4893,38 +4618,38 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>ভূ-স্থির উপগ্রহের উচ্চতা ও কক্ষপথ (সমস্যা 25)</t>
+          <t>উন্নত কক্ষপথ বলবিদ্যা, কেপলারের সূত্র ও মহাকর্ষীয় বিভব (Advanced Orbital Mechanics &amp; Potentials)</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F76" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>[সমস্যা 25: ভূ-স্থির উপগ্রহের উচ্চতা ও কক্ষপথ]
-একটি ভূ-স্থির উপগ্রহের পর্যায়কাল $T = 24\text{ ঘণ্টা}$। ভূপৃষ্ঠ হতে উপগ্রহটির উচ্চতা কত কিলোমিটার নির্ণয় কর। ($M = 6.0 \times 10^{24}\text{ kg}, R = 6400\text{ km}$)</t>
-        </is>
-      </c>
-      <c r="H76" t="inlineStr"/>
+          <t>##GEO:circle[r=3.2][size:small]##
+ভূপৃষ্ঠ হতে একটি বস্তুকে খাড়া উপরের দিকে তুলে $h = R$ (পৃথিবীর ব্যাসার্ধের সমান) উচ্চতায় নিতে প্রয়োজনীয় কাজের পরিমাণ কত? এবং $h = n R$ উচ্চতায় নিতে কাজের সাধারণ সূত্রটি প্রতিপাদন কর।</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=3.2][size:small]##</t>
+        </is>
+      </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>নিউটনের সার্বজনীন মহাকর্ষ সূত্র ও কেপলারের গ্রহীয় গতির সূত্রাবলি প্রয়োগ করে ধাপে ধাপে সমাধান (সমস্যা 25)।</t>
+          <t>বিভব শক্তি পরিবর্তন $W = \Delta U = U(R+h) - U(R) = -\frac{GMm}{R+h} - \left(-\frac{GMm}{R}\right) = GMm\left(\frac{1}{R} - \frac{1}{R+h}\right) = \frac{GMm h}{R(R+h)} = \frac{mgh}{1 + h/R}$। $h = R$ হলে: $W = \frac{mgR}{1 + 1} = \frac{1}{2}mgR$। $h = nR$ হলে: $W = \frac{mg(nR)}{1 + n} = \left(\frac{n}{n+1}\right)mgR$।</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>মহাকর্ষীয় সমাধান 25</t>
-        </is>
-      </c>
-      <c r="K76" t="inlineStr"/>
-      <c r="L76" t="inlineStr"/>
-      <c r="M76" t="inlineStr"/>
-      <c r="N76" t="inlineStr"/>
+          <t>$W = \frac{1}{2}mgR$, সাধারণ ক্ষেত্রে $W = \left(\frac{n}{n+1}\right)mgR$</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -4944,12 +4669,12 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>মহাকর্ষীয় বিভব ও কৃতকাজ (সমস্যা 26)</t>
+          <t>উন্নত কক্ষপথ বলবিদ্যা, কেপলারের সূত্র ও মহাকর্ষীয় বিভব (Advanced Orbital Mechanics &amp; Potentials)</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F77" t="n">
@@ -4957,25 +4682,25 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>[সমস্যা 26: মহাকর্ষীয় বিভব ও কৃতকাজ]
-$m = 6\text{ kg}$ ভরের একটি বস্তুকে অসীম দূরত্ব হতে পৃথিবীর পৃষ্ঠে নিয়ে আসতে মহাকর্ষ বল দ্বারা সম্পাদিত কাজের মান কত?</t>
-        </is>
-      </c>
-      <c r="H77" t="inlineStr"/>
+          <t>##GEO:circle[r=2][size:small]##
+সমান ব্যাসার্ধ $R$ এবং ঘনত্ব $\rho$-এর দুটি সিসার গোলক পরস্পরকে স্পর্শ করে রাখা আছে। প্রমাণ কর যে তাদের মধ্যকার মহাকর্ষ বল গোলকের ব্যাসার্ধের চতুর্থ ঘাতের সমানুপাতিক ($F \propto R^4$)।</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=2][size:small]##</t>
+        </is>
+      </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>নিউটনের সার্বজনীন মহাকর্ষ সূত্র ও কেপলারের গ্রহীয় গতির সূত্রাবলি প্রয়োগ করে ধাপে ধাপে সমাধান (সমস্যা 26)।</t>
+          <t>প্রতিটি গোলকের ভর $M = \frac{4}{3}\pi R^3 \rho$। কেন্দ্রদ্বয়ের মধ্যকার দূরত্ব $r = R + R = 2R$। নিউটনের মহাকর্ষ সূত্র: $F = \frac{G M^2}{r^2} = \frac{G \left(\frac{4}{3}\pi R^3 \rho\right)^2}{(2R)^2} = \frac{G \frac{16}{9}\pi^2 R^6 \rho^2}{4R^2} = \frac{4}{9}\pi^2 G \rho^2 R^4 \propto R^4$।</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>মহাকর্ষীয় সমাধান 26</t>
-        </is>
-      </c>
-      <c r="K77" t="inlineStr"/>
-      <c r="L77" t="inlineStr"/>
-      <c r="M77" t="inlineStr"/>
-      <c r="N77" t="inlineStr"/>
+          <t>$F \propto R^4$</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -4995,38 +4720,38 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>পৃথিবী ও চাঁদের মধ্যবর্তী নিরপেক্ষ বিন্দু (সমস্যা 27)</t>
+          <t>উন্নত কক্ষপথ বলবিদ্যা, কেপলারের সূত্র ও মহাকর্ষীয় বিভব (Advanced Orbital Mechanics &amp; Potentials)</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F78" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>[সমস্যা 27: পৃথিবী ও চাঁদের মধ্যবর্তী নিরপেক্ষ বিন্দু]
-পৃথিবীর ভর চাঁদের ভরের 8 গুণ এবং এদের মধ্যবর্তী দূরত্ব $d = 3.84 \times 10^5\text{ km}$। পৃথিবী ও চাঁদের সংযোগকারী সরলরেখার কোন বিন্দুতে লব্ধি মহাকর্ষীয় প্রাবল্য শূন্য হবে?</t>
-        </is>
-      </c>
-      <c r="H78" t="inlineStr"/>
+          <t>##GEO:rect[w=4,h=1][size:small]##
+একটি $M$ ভরের এবং $L$ দৈর্ঘ্যের সুষম সরু দণ্ডের একপ্রান্ত হতে অক্ষ বরাবর $d$ দূরত্বে একটি $m$ ভরের কণা রাখা হলো। দণ্ড ও কণার মধ্যকার মহাকর্ষ বলের মান সমাকলনের সাহায্যে নির্ণয় কর।</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>##GEO:rect[w=4,h=1][size:small]##</t>
+        </is>
+      </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>নিউটনের সার্বজনীন মহাকর্ষ সূত্র ও কেপলারের গ্রহীয় গতির সূত্রাবলি প্রয়োগ করে ধাপে ধাপে সমাধান (সমস্যা 27)।</t>
+          <t>দণ্ডের প্রতি একক দৈর্ঘ্যের ভর $\lambda = \frac{M}{L}$। কণা হতে $x$ দূরত্বে $dx$ ক্ষুদ্রাংশের ভর $dM = \lambda dx$। মহাকর্ষ বল $dF = \frac{G m dM}{x^2} = \frac{G m \lambda dx}{x^2}$। মোট বল $F = \int_d^{d+L} \frac{G m \lambda dx}{x^2} = G m \lambda \left[-\frac{1}{x}\right]_d^{d+L} = G m \frac{M}{L}\left(\frac{1}{d} - \frac{1}{d+L}\right) = \frac{GMm}{L}\left(\frac{L}{d(d+L)}\right) = \frac{GMm}{d(d+L)}$।</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>মহাকর্ষীয় সমাধান 27</t>
-        </is>
-      </c>
-      <c r="K78" t="inlineStr"/>
-      <c r="L78" t="inlineStr"/>
-      <c r="M78" t="inlineStr"/>
-      <c r="N78" t="inlineStr"/>
+          <t>$F = \frac{GMm}{d(d+L)}$</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -5046,12 +4771,12 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>আহ্নিক গতির কারণে g-এর হ্রাস (সমস্যা 28)</t>
+          <t>উন্নত কক্ষপথ বলবিদ্যা, কেপলারের সূত্র ও মহাকর্ষীয় বিভব (Advanced Orbital Mechanics &amp; Potentials)</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F79" t="n">
@@ -5059,25 +4784,25 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>[সমস্যা 28: আহ্নিক গতির কারণে g-এর হ্রাস]
-বিষুবরেখা অঞ্চলে পৃথিবীর আহ্নিক গতির জন্য কোনো বস্তুর ওজনে শতকরা কত আপাত হ্রাস ঘটে? ($R = 6400\text{ km}, T = 86400\text{ s}$)</t>
-        </is>
-      </c>
-      <c r="H79" t="inlineStr"/>
+          <t>##GEO:circle[r=2.5][size:small]##
+একটি $M$ ভর এবং $R$ ব্যাসার্ধের সুষম বৃত্তাকার রিং-এর কেন্দ্রগামী লম্ব অক্ষ বরাবর কেন্দ্র হতে $x$ দূরত্বে মহাকর্ষীয় প্রাবল্য $E(x)$ নির্ণয় কর এবং দেখাও যে অক্ষের ওপর $x = R/\sqrt{2}$ দূরত্বে প্রাবল্যের মান সর্বোচ্চ হয়।</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>নিউটনের সার্বজনীন মহাকর্ষ সূত্র ও কেপলারের গ্রহীয় গতির সূত্রাবলি প্রয়োগ করে ধাপে ধাপে সমাধান (সমস্যা 28)।</t>
+          <t>রিংয়ের জন্য প্রতিসমতায় প্রাবল্য $E(x) = \frac{GM x}{(R^2+x^2)^{3/2}}$। সর্বোচ্চের জন্য $\frac{dE}{dx} = 0 \implies \frac{(R^2+x^2)^{3/2} - x \cdot \frac{3}{2}(R^2+x^2)^{1/2}(2x)}{(R^2+x^2)^3} = 0 \implies R^2 + x^2 - 3x^2 = 0 \implies R^2 - 2x^2 = 0 \implies x = \frac{R}{\sqrt{2}}$।</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>মহাকর্ষীয় সমাধান 28</t>
-        </is>
-      </c>
-      <c r="K79" t="inlineStr"/>
-      <c r="L79" t="inlineStr"/>
-      <c r="M79" t="inlineStr"/>
-      <c r="N79" t="inlineStr"/>
+          <t>$E(x) = \frac{GM x}{(R^2 + x^2)^{3/2}}$, সর্বোচ্চ $x = \frac{R}{\sqrt{2}}$</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -5097,38 +4822,38 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>কেপলারের ক্ষেত্রফলের সূত্র ও ক্ষেত্রীয় বেগ (সমস্যা 29)</t>
+          <t>উন্নত কক্ষপথ বলবিদ্যা, কেপলারের সূত্র ও মহাকর্ষীয় বিভব (Advanced Orbital Mechanics &amp; Potentials)</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F80" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>[সমস্যা 29: কেপলারের ক্ষেত্রফলের সূত্র ও ক্ষেত্রীয় বেগ]
-একটি উপগ্রহ উপবৃত্তাকার কক্ষপথে আবর্তনের সময় নিকটতম দূরত্বে বেগ $v_1 = 12\text{ km/s}$ এবং দূরত্ব $r_1 = 11000\text{ km}$। দূরতম বিন্দুতে দূরত্ব $r_2 = 15000\text{ km}$ হলে সেখানে বেগ কত?</t>
-        </is>
-      </c>
-      <c r="H80" t="inlineStr"/>
+          <t>##GEO:circle[r=3.2][size:small]##
+একটি যুগ্ম নক্ষত্র ব্যবস্থায় (Binary star system) দুটি তারা যথাক্রমে $M_1 = 2M_{\odot}$ এবং $M_2 = 1M_{\odot}$ ভরবিশিষ্ট এবং তাদের পারস্পরিক দূরত্ব $d$। তারা দুটি তাদের সাধারণ ভরকেন্দ্রের চারদিকে বৃত্তাকার পথে ঘুরলে এদের কক্ষীয় পর্যায়কাল $T$-এর সমীকরণ নির্ণয় কর।</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=3.2][size:small]##</t>
+        </is>
+      </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>নিউটনের সার্বজনীন মহাকর্ষ সূত্র ও কেপলারের গ্রহীয় গতির সূত্রাবলি প্রয়োগ করে ধাপে ধাপে সমাধান (সমস্যা 29)।</t>
+          <t>ভরকেন্দ্র হতে দূরত্ব $r_1 = \frac{M_2 d}{M_1+M_2}$ এবং $r_2 = \frac{M_1 d}{M_1+M_2}$। মহাকর্ষ বল কেন্দ্রমুখী বল যোগান দেয়: $\frac{G M_1 M_2}{d^2} = M_1 \omega^2 r_1 = M_1 \omega^2 \left(\frac{M_2 d}{M_1+M_2}\right) \implies \omega^2 = \frac{G(M_1+M_2)}{d^3}$। পর্যায়কাল $T = \frac{2\pi}{\omega} = 2\pi\sqrt{\frac{d^3}{G(M_1+M_2)}}$।</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>মহাকর্ষীয় সমাধান 29</t>
-        </is>
-      </c>
-      <c r="K80" t="inlineStr"/>
-      <c r="L80" t="inlineStr"/>
-      <c r="M80" t="inlineStr"/>
-      <c r="N80" t="inlineStr"/>
+          <t>$T = 2\pi\sqrt{\frac{d^3}{G(M_1+M_2)}}$</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -5148,12 +4873,12 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>বাইনারি স্টার সিস্টেম ও অভিকর্ষ বল (সমস্যা 30)</t>
+          <t>উন্নত কক্ষপথ বলবিদ্যা, কেপলারের সূত্র ও মহাকর্ষীয় বিভব (Advanced Orbital Mechanics &amp; Potentials)</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F81" t="n">
@@ -5161,25 +4886,25 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>[সমস্যা 30: বাইনারি স্টার সিস্টেম ও অভিকর্ষ বল]
-মহাশূন্যে পরস্পর হতে $r = 2 \times 10^{11}\text{ m}$ দূরত্বে অবস্থিত দুটি নক্ষত্রের প্রতিটির ভর $M = 2.0 \times 10^{30}\text{ kg}$। এদের মধ্যকার মহাকর্ষীয় আকর্ষণ বলের মান নির্ণয় কর।</t>
-        </is>
-      </c>
-      <c r="H81" t="inlineStr"/>
+          <t>##GEO:circle[r=2.8][size:small]##
+একটি সুষম নিরেট গোলকের মহাকর্ষীয় স্বকীয় শক্তি (Self-energy) অর্থাৎ গোলকটির ক্ষুদ্রাতিক্ষুদ্র ভর উপাদানগুলোকে অসীম হতে একত্রিত করে গোলকটি গঠিত করতে কৃতকাজের পরিমাণ প্রতিপাদন কর।</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=2.8][size:small]##</t>
+        </is>
+      </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>নিউটনের সার্বজনীন মহাকর্ষ সূত্র ও কেপলারের গ্রহীয় গতির সূত্রাবলি প্রয়োগ করে ধাপে ধাপে সমাধান (সমস্যা 30)।</t>
+          <t>যখন গোলকটির বর্তমান ব্যাসার্ধ $r$ এবং ভর $m(r) = M\frac{r^3}{R^3}$, তখন অসীম হতে $dm = \rho 4\pi r^2 dr$ ভর আনতে কাজ $dW = -\frac{G m(r) dm}{r} = -\frac{G (M r^3/R^3)(3M r^2 dr/R^3)}{r} = -\frac{3GM^2}{R^6} r^4 dr$। মোট কাজ $U = -\frac{3GM^2}{R^6}\int_0^R r^4 dr = -\frac{3GM^2}{R^6}\left(\frac{R^5}{5}\right) = -\frac{3GM^2}{5R}$।</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>মহাকর্ষীয় সমাধান 30</t>
-        </is>
-      </c>
-      <c r="K81" t="inlineStr"/>
-      <c r="L81" t="inlineStr"/>
-      <c r="M81" t="inlineStr"/>
-      <c r="N81" t="inlineStr"/>
+          <t>$U = -\frac{3GM^2}{5R}$</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -5199,43 +4924,38 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>কেপলারের ৩য় সূত্র ও উপগ্রহের পর্যায়কাল (সমস্যা 31)</t>
+          <t>উন্নত কক্ষপথ বলবিদ্যা, কেপলারের সূত্র ও মহাকর্ষীয় বিভব (Advanced Orbital Mechanics &amp; Potentials)</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F82" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>[সমস্যা 31: কেপলারের ৩য় সূত্র ও উপগ্রহের পর্যায়কাল]
-##PRESET:kepler-orbit[size:medium]##
-পৃথিবীর পৃষ্ঠ হতে $h = 400\text{ km}$ উচ্চতায় একটি কৃত্রিম উপগ্রহ বৃত্তাকার কক্ষপথে পৃথিবীকে প্রদক্ষিণ করছে। পৃথিবীর ভর $M = 6.0 \times 10^{24}\text{ kg}$ এবং ব্যাসার্ধ $R = 6400\text{ km}$ হলে উপগ্রহটির কক্ষীয় দ্রুতি এবং পর্যায়কাল কত?</t>
+          <t>##GEO:circle[r=2.5][size:small]##
+চাঁদের পৃষ্ঠে মুক্তিবেগ $v_e = 2.4\text{ km/s}$ এবং পরম তাপমাত্রা $T = 300\text{ K}$। হাইড্রোজেনের আণবিক ভর $2\text{ g/mol}$ এবং অক্সিজেনের আণবিক ভর $32\text{ g/mol}$। চাঁদে বায়ুমণ্ডল না থাকার কারণ ব্যাখ্যা কর।</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>##PRESET:kepler-orbit[size:medium]##</t>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>নিউটনের সার্বজনীন মহাকর্ষ সূত্র ও কেপলারের গ্রহীয় গতির সূত্রাবলি প্রয়োগ করে ধাপে ধাপে সমাধান (সমস্যা 31)।</t>
+          <t>গ্যাসের মূল গড় বর্গবেগ $v_{rms} = \sqrt{\frac{3RT}{M}}$। হাইড্রোজেনের জন্য $v_{rms} = \sqrt{\frac{3(8.314)(300)}{0.002}} = \sqrt{3.74\times 10^6} \approx 1934\text{ m/s} = 1.93\text{ km/s}$। কোনো গ্রহের গ্যাস আটকে রাখতে $v_e \ge 6 v_{rms}$ হওয়া আবশ্যক। চাঁদে $v_e = 2.4\text{ km/s}$, যা গ্যাসের তাপীয় বেগের খুব কাছাকাছি হওয়ায় হাইড্রোজেন ও অক্সিজেন কোটি কোটি বছরে বায়ুমণ্ডল শূন্য করে পালিয়ে গেছে।</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>মহাকর্ষীয় সমাধান 31</t>
-        </is>
-      </c>
-      <c r="K82" t="inlineStr"/>
-      <c r="L82" t="inlineStr"/>
-      <c r="M82" t="inlineStr"/>
-      <c r="N82" t="inlineStr"/>
+          <t>চাঁদের মুক্তিবেগ গ্যাসের গড় বেগ অপেক্ষা কম হওয়ায় গ্যাস অণুগুলো চাঁদের মাধ্যাকর্ষণ ত্যাগ করে পালিয়ে গেছে</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -5255,12 +4975,12 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>ভূপৃষ্ঠ থেকে উচ্চতায় g-এর মান (সমস্যা 32)</t>
+          <t>উন্নত কক্ষপথ বলবিদ্যা, কেপলারের সূত্র ও মহাকর্ষীয় বিভব (Advanced Orbital Mechanics &amp; Potentials)</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F83" t="n">
@@ -5268,25 +4988,25 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>[সমস্যা 32: ভূপৃষ্ঠ থেকে উচ্চতায় g-এর মান]
-ভূপৃষ্ঠ হতে কত উচ্চতায় অভিকর্ষজ ত্বরণের মান ভূপৃষ্ঠের মানের $\frac{1}{7}$ অংশ হবে? (পৃথিবীর ব্যাসার্ধ $R = 6400\text{ km}$)</t>
-        </is>
-      </c>
-      <c r="H83" t="inlineStr"/>
+          <t>##GEO:circle[r=2.6][size:small]##
+একটি গোলকাকার ফাঁপা খোলকের (Thin spherical shell) ভর $M$ এবং ব্যাসার্ধ $R$। খোলকটির অভ্যন্তরে এবং বাইরে মহাকর্ষীয় বিভব ও প্রাবল্যের মান নির্ণয় কর।</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=2.6][size:small]##</t>
+        </is>
+      </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>নিউটনের সার্বজনীন মহাকর্ষ সূত্র ও কেপলারের গ্রহীয় গতির সূত্রাবলি প্রয়োগ করে ধাপে ধাপে সমাধান (সমস্যা 32)।</t>
+          <t>গাউসের মহাকর্ষীয় উপপাদ্য অনুসারে খোলকের অভ্যন্তরে কোনো ভর আবদ্ধ না থাকায় ফ্লাক্স শূন্য $\implies$ অভ্যন্তরীণ প্রাবল্য $E = 0$। প্রাবল্য শূন্য হওয়ায় অভ্যন্তরে বিভব সর্বত্র ধ্রুব এবং পৃষ্ঠের বিভবের সমান: $V = -\frac{GM}{R}$। খোলকের বাইরে সম্পূর্ণ ভর কেন্দ্রে কেন্দ্রীভূত হিসেবে কাজ করে: $E = \frac{GM}{r^2}, V = -\frac{GM}{r}$।</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>মহাকর্ষীয় সমাধান 32</t>
-        </is>
-      </c>
-      <c r="K83" t="inlineStr"/>
-      <c r="L83" t="inlineStr"/>
-      <c r="M83" t="inlineStr"/>
-      <c r="N83" t="inlineStr"/>
+          <t>অভ্যন্তরে: $E = 0, V = -\frac{GM}{R}$; বাইরে ($r \ge R$): $E = \frac{GM}{r^2}, V = -\frac{GM}{r}$</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -5306,38 +5026,38 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>খনিতে বা গভীরতায় g-এর পরিবর্তন (সমস্যা 33)</t>
+          <t>উন্নত কক্ষপথ বলবিদ্যা, কেপলারের সূত্র ও মহাকর্ষীয় বিভব (Advanced Orbital Mechanics &amp; Potentials)</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F84" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>[সমস্যা 33: খনিতে বা গভীরতায় g-এর পরিবর্তন]
-ভূপৃষ্ঠ হতে কত গভীরে খনির ভেতর প্রবেশ করলে অভিকর্ষজ ত্বরণের মান ভূপৃষ্ঠের মানের $35\%$ হ্রাস পাবে?</t>
-        </is>
-      </c>
-      <c r="H84" t="inlineStr"/>
+          <t>##GEO:circle[r=3][size:small]##
+পৃথিবীর ব্যাসার্ধ $R = 6400\text{ km}$। ভূপৃষ্ঠ হতে একটি রকেটকে খাড়া উপরের দিকে এমন বেগে ছোঁড়া হলো যাতে তা সর্বোচ্চ $h = 3R$ উচ্চতায় পৌঁছায়। রকেটটির আদি নিক্ষেপণ বেগ কত ছিল? ($g = 9.8\text{ ms}^{-2}$)।</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=3][size:small]##</t>
+        </is>
+      </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>নিউটনের সার্বজনীন মহাকর্ষ সূত্র ও কেপলারের গ্রহীয় গতির সূত্রাবলি প্রয়োগ করে ধাপে ধাপে সমাধান (সমস্যা 33)।</t>
+          <t>শক্তির নিত্যতা: $\frac{1}{2}m v_0^2 - \frac{GMm}{R} = 0 - \frac{GMm}{R+h} \implies \frac{1}{2}v_0^2 = GM\left(\frac{1}{R} - \frac{1}{4R}\right) = \frac{3GM}{4R} = \frac{3}{4}gR$। $v_0 = \sqrt{\frac{3}{2}gR} = \sqrt{1.5 \times 9.8 \times 6.4\times 10^6} = \sqrt{9.408\times 10^7} \approx 9699\text{ m/s} \approx 9.70\text{ km/s}$।</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>মহাকর্ষীয় সমাধান 33</t>
-        </is>
-      </c>
-      <c r="K84" t="inlineStr"/>
-      <c r="L84" t="inlineStr"/>
-      <c r="M84" t="inlineStr"/>
-      <c r="N84" t="inlineStr"/>
+          <t>আদি বেগ $v_0 = 9.70\\text{ km/s}$</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -5357,12 +5077,12 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>মুক্তিবেগ ও গ্রহের ঘনত্ব (সমস্যা 34)</t>
+          <t>উন্নত কক্ষপথ বলবিদ্যা, কেপলারের সূত্র ও মহাকর্ষীয় বিভব (Advanced Orbital Mechanics &amp; Potentials)</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F85" t="n">
@@ -5370,30 +5090,25 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>[সমস্যা 34: মুক্তিবেগ ও গ্রহের ঘনত্ব]
-##GEO:sphere[r=4][size:small]##
-একটি গ্রহের ভর পৃথিবীর ভরের 10 গুণ কিন্তু ব্যাসার্ধ পৃথিবীর ব্যাসার্ধের 11 গুণ। পৃথিবীর পৃষ্ঠে মুক্তিবেগ $11.2\text{ km/s}$ হলে ঐ গ্রহের পৃষ্ঠে মুক্তিবেগ কত?</t>
+          <t>##GEO:circle[r=2.5][size:small]##
+দুটি সমভরের বিন্দু বস্তু $m$ মহাকর্ষীয় বলের প্রভাবে পরস্পরকে প্রদক্ষিণ করছে। তাদের মধ্যবর্তী দূরত্ব $2r$ হলে তাদের কক্ষীয় দ্রুতি এবং পর্যায়কাল নির্ণয় কর।</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>##GEO:sphere[r=4][size:small]##</t>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>নিউটনের সার্বজনীন মহাকর্ষ সূত্র ও কেপলারের গ্রহীয় গতির সূত্রাবলি প্রয়োগ করে ধাপে ধাপে সমাধান (সমস্যা 34)।</t>
+          <t>কেন্দ্রের সাপেক্ষে প্রতিটি বস্তুর কক্ষপথের ব্যাসার্ধ $r$। পারস্পরিক দূরত্ব $2r$। মহাকর্ষ বল $\frac{G m^2}{(2r)^2} = \frac{G m^2}{4r^2}$। কেন্দ্রমুখী বল $m \frac{v^2}{r} = \frac{G m^2}{4r^2} \implies v^2 = \frac{Gm}{4r} \implies v = \frac{1}{2}\sqrt{\frac{Gm}{r}}$। পর্যায়কাল $T = \frac{2\pi r}{v} = \frac{2\pi r}{\frac{1}{2}\sqrt{Gm/r}} = 4\pi\sqrt{\frac{r^3}{Gm}}$।</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>মহাকর্ষীয় সমাধান 34</t>
-        </is>
-      </c>
-      <c r="K85" t="inlineStr"/>
-      <c r="L85" t="inlineStr"/>
-      <c r="M85" t="inlineStr"/>
-      <c r="N85" t="inlineStr"/>
+          <t>$v = \frac{1}{2}\sqrt{\frac{Gm}{r}}, T = 4\pi\sqrt{\frac{r^3}{Gm}}$</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -5413,38 +5128,38 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>ভূ-স্থির উপগ্রহের উচ্চতা ও কক্ষপথ (সমস্যা 35)</t>
+          <t>উন্নত কক্ষপথ বলবিদ্যা, কেপলারের সূত্র ও মহাকর্ষীয় বিভব (Advanced Orbital Mechanics &amp; Potentials)</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F86" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>[সমস্যা 35: ভূ-স্থির উপগ্রহের উচ্চতা ও কক্ষপথ]
-একটি ভূ-স্থির উপগ্রহের পর্যায়কাল $T = 24\text{ ঘণ্টা}$। ভূপৃষ্ঠ হতে উপগ্রহটির উচ্চতা কত কিলোমিটার নির্ণয় কর। ($M = 6.0 \times 10^{24}\text{ kg}, R = 6400\text{ km}$)</t>
-        </is>
-      </c>
-      <c r="H86" t="inlineStr"/>
+          <t>##GEO:circle[r=3.2][size:small]##
+একটি কৃত্রিম উপগ্রহ $r$ ব্যাসার্ধের কক্ষপথে প্রদক্ষিণ করছে। বায়ুমণ্ডলের অতি ক্ষীণ বাধার কারণে উপগ্রহটির কক্ষীয় ব্যাসার্ধ সামান্য হ্রাস পেলে উপগ্রহটির দ্রুতি এবং গতিশক্তি বৃদ্ধি পাবে না হ্রাস পাবে?</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=3.2][size:small]##</t>
+        </is>
+      </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>নিউটনের সার্বজনীন মহাকর্ষ সূত্র ও কেপলারের গ্রহীয় গতির সূত্রাবলি প্রয়োগ করে ধাপে ধাপে সমাধান (সমস্যা 35)।</t>
+          <t>কক্ষীয় দ্রুতি $v = \sqrt{\frac{GM}{r}}$ এবং গতিশক্তি $K = \frac{GMm}{2r}$। ব্যাসার্ধ $r$ হ্রাস পেলে $v$ এবং $K$ উভয়ই বৃদ্ধি পায়। তবে বিভবশক্তি দ্বিগুণ হারে ঋণাত্মকভাবে হ্রাস পাওয়ায় ($U = -2K$) মোট যান্ত্রিক শক্তি $E = -K$ হ্রাস পায় এবং বাধার বিরুদ্ধে তাপে ক্ষয় হয়। একে 'Satellite drag paradox' বলা হয়।</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>মহাকর্ষীয় সমাধান 35</t>
-        </is>
-      </c>
-      <c r="K86" t="inlineStr"/>
-      <c r="L86" t="inlineStr"/>
-      <c r="M86" t="inlineStr"/>
-      <c r="N86" t="inlineStr"/>
+          <t>কক্ষীয় দ্রুতি ও গতিশক্তি উভয়ই বৃদ্ধি পাবে</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -5464,12 +5179,12 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>মহাকর্ষীয় বিভব ও কৃতকাজ (সমস্যা 36)</t>
+          <t>উন্নত কক্ষপথ বলবিদ্যা, কেপলারের সূত্র ও মহাকর্ষীয় বিভব (Advanced Orbital Mechanics &amp; Potentials)</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F87" t="n">
@@ -5477,25 +5192,25 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>[সমস্যা 36: মহাকর্ষীয় বিভব ও কৃতকাজ]
-$m = 2\text{ kg}$ ভরের একটি বস্তুকে অসীম দূরত্ব হতে পৃথিবীর পৃষ্ঠে নিয়ে আসতে মহাকর্ষ বল দ্বারা সম্পাদিত কাজের মান কত?</t>
-        </is>
-      </c>
-      <c r="H87" t="inlineStr"/>
+          <t>##GEO:circle[r=2.8][size:small]##
+পৃথিবীর একটি কাল্পনিক ভর ঘনত্ব কেন্দ্র হতে পৃষ্ঠ পর্যন্ত রৈখিকভাবে পরিবর্তিত হয়: $\rho(r) = \rho_0(1 - r/R)$। পৃথিবীর মোট ভর $M$ এবং কেন্দ্রীয় ঘনত্ব $\rho_0$-এর মধ্যে সম্পর্ক নির্ণয় কর।</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=2.8][size:small]##</t>
+        </is>
+      </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>নিউটনের সার্বজনীন মহাকর্ষ সূত্র ও কেপলারের গ্রহীয় গতির সূত্রাবলি প্রয়োগ করে ধাপে ধাপে সমাধান (সমস্যা 36)।</t>
+          <t>মোট ভর $M = \int_0^R \rho(r) 4\pi r^2 dr = 4\pi \rho_0 \int_0^R (r^2 - r^3/R) dr = 4\pi \rho_0 \left[\frac{R^3}{3} - \frac{R^4}{4R}\right] = 4\pi \rho_0 \left(\frac{R^3}{12}\right) = \frac{\pi \rho_0 R^3}{3} \implies \rho_0 = \frac{3M}{\pi R^3}$।</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>মহাকর্ষীয় সমাধান 36</t>
-        </is>
-      </c>
-      <c r="K87" t="inlineStr"/>
-      <c r="L87" t="inlineStr"/>
-      <c r="M87" t="inlineStr"/>
-      <c r="N87" t="inlineStr"/>
+          <t>$\rho_0 = \frac{3M}{\pi R^3}$</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -5515,38 +5230,38 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>পৃথিবী ও চাঁদের মধ্যবর্তী নিরপেক্ষ বিন্দু (সমস্যা 37)</t>
+          <t>উন্নত কক্ষপথ বলবিদ্যা, কেপলারের সূত্র ও মহাকর্ষীয় বিভব (Advanced Orbital Mechanics &amp; Potentials)</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F88" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>[সমস্যা 37: পৃথিবী ও চাঁদের মধ্যবর্তী নিরপেক্ষ বিন্দু]
-পৃথিবীর ভর চাঁদের ভরের 4 গুণ এবং এদের মধ্যবর্তী দূরত্ব $d = 3.84 \times 10^5\text{ km}$। পৃথিবী ও চাঁদের সংযোগকারী সরলরেখার কোন বিন্দুতে লব্ধি মহাকর্ষীয় প্রাবল্য শূন্য হবে?</t>
-        </is>
-      </c>
-      <c r="H88" t="inlineStr"/>
+          <t>##GEO:circle[r=2.4][size:small]##
+একটি সুষম রিং এবং একটি বিন্দু ভরের সংঘাত বিশ্লেষণ: একটি $M$ ভর ও $R$ ব্যাসার্ধের রিং-এর অক্ষীয় অবস্থানে $x = \sqrt{3}R$ দূরত্ব হতে একটি কণা ছেড়ে দিলে কেন্দ্রে পৌঁছানোর মুহূর্তে এর বেগ কত হবে?</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=2.4][size:small]##</t>
+        </is>
+      </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>নিউটনের সার্বজনীন মহাকর্ষ সূত্র ও কেপলারের গ্রহীয় গতির সূত্রাবলি প্রয়োগ করে ধাপে ধাপে সমাধান (সমস্যা 37)।</t>
+          <t>প্রারম্ভিক অক্ষীয় বিভব $V_i = -\frac{GM}{\sqrt{R^2 + (\sqrt{3}R)^2}} = -\frac{GM}{\sqrt{4R^2}} = -\frac{GM}{2R}$। কেন্দ্রের বিভব $V_c = -\frac{GM}{R}$। বিভব শক্তি হ্রাস $= m(V_i - V_c) = m\left(-\frac{GM}{2R} - \left(-\frac{GM}{R}\right)\right) = \frac{GMm}{2R}$। শক্তির নিত্যতা: $\frac{1}{2}m v^2 = \frac{GMm}{2R} \implies v^2 = \frac{GM}{R} \implies v = \sqrt{\frac{GM}{R}}$।</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>মহাকর্ষীয় সমাধান 37</t>
-        </is>
-      </c>
-      <c r="K88" t="inlineStr"/>
-      <c r="L88" t="inlineStr"/>
-      <c r="M88" t="inlineStr"/>
-      <c r="N88" t="inlineStr"/>
+          <t>$v = \sqrt{\frac{GM}{R}}$</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -5566,12 +5281,12 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>আহ্নিক গতির কারণে g-এর হ্রাস (সমস্যা 38)</t>
+          <t>উন্নত কক্ষপথ বলবিদ্যা, কেপলারের সূত্র ও মহাকর্ষীয় বিভব (Advanced Orbital Mechanics &amp; Potentials)</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F89" t="n">
@@ -5579,25 +5294,25 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>[সমস্যা 38: আহ্নিক গতির কারণে g-এর হ্রাস]
-বিষুবরেখা অঞ্চলে পৃথিবীর আহ্নিক গতির জন্য কোনো বস্তুর ওজনে শতকরা কত আপাত হ্রাস ঘটে? ($R = 6400\text{ km}, T = 86400\text{ s}$)</t>
-        </is>
-      </c>
-      <c r="H89" t="inlineStr"/>
+          <t>##GEO:circle[r=3][size:small]##
+দুটি কৃত্রিম উপগ্রহ একই বৃত্তাকার কক্ষপথে বিপরীত দিকে চলছে। তাদের একটি হেড-অন সংঘর্ষে পূর্ণ অস্থিতিস্থাপকভাবে আটকে গেলে যুক্ত ধ্বংসাবশেষটি পরবর্তীতে কীভাবে গতিশীল হবে?</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=3][size:small]##</t>
+        </is>
+      </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>নিউটনের সার্বজনীন মহাকর্ষ সূত্র ও কেপলারের গ্রহীয় গতির সূত্রাবলি প্রয়োগ করে ধাপে ধাপে সমাধান (সমস্যা 38)।</t>
+          <t>সমান দ্রুতিতে বিপরীতমুখী উপগ্রহদ্বয়ের ভরবেগের ভেক্টর যোগফল $\vec{P}_{total} = m\vec{v} + m(-\vec{v}) = \vec{0}$। সংঘর্ষের পর রৈখিক অনুভূমিক বেগ সম্পূর্ণরূপে শূন্য হয়ে যায়। ফলে কক্ষীয় গতি বজায় রাখার মতো কোনো স্পর্শকীয় বেগ থাকে না এবং ধ্বংসাবশেষটি কেবল অভিকর্ষের টানে মুক্তভাবে খাড়া নিচের দিকে পৃথিবীর বুকে আছড়ে পড়বে।</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>মহাকর্ষীয় সমাধান 38</t>
-        </is>
-      </c>
-      <c r="K89" t="inlineStr"/>
-      <c r="L89" t="inlineStr"/>
-      <c r="M89" t="inlineStr"/>
-      <c r="N89" t="inlineStr"/>
+          <t>যুক্ত ধ্বংসাবশেষটি সমস্ত অনুভূমিক বেগ হারিয়ে মুক্ত পতনে খাড়া পৃথিবীর কেন্দ্রে পতিত হবে</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -5617,38 +5332,38 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>কেপলারের ক্ষেত্রফলের সূত্র ও ক্ষেত্রীয় বেগ (সমস্যা 39)</t>
+          <t>উন্নত কক্ষপথ বলবিদ্যা, কেপলারের সূত্র ও মহাকর্ষীয় বিভব (Advanced Orbital Mechanics &amp; Potentials)</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F90" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>[সমস্যা 39: কেপলারের ক্ষেত্রফলের সূত্র ও ক্ষেত্রীয় বেগ]
-একটি উপগ্রহ উপবৃত্তাকার কক্ষপথে আবর্তনের সময় নিকটতম দূরত্বে বেগ $v_1 = 8\text{ km/s}$ এবং দূরত্ব $r_1 = 11000\text{ km}$। দূরতম বিন্দুতে দূরত্ব $r_2 = 30000\text{ km}$ হলে সেখানে বেগ কত?</t>
-        </is>
-      </c>
-      <c r="H90" t="inlineStr"/>
+          <t>##GEO:circle[r=3.5][size:small]##
+একটি গ্রহের পর্যায়কাল $T = 365\text{ দিন}$ এবং সূর্যের চারদিকে কক্ষপথের ব্যাসার্ধ $r = 1.5 	imes 10^{11}\text{ m}$। কেপলারের সূত্রের মাধ্যমে সূর্যের ভর নির্ণয় কর ($G = 6.673 	imes 10^{-11}\text{ N m}^2/\text{kg}^2$)।</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=3.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>নিউটনের সার্বজনীন মহাকর্ষ সূত্র ও কেপলারের গ্রহীয় গতির সূত্রাবলি প্রয়োগ করে ধাপে ধাপে সমাধান (সমস্যা 39)।</t>
+          <t>$T^2 = \frac{4\pi^2 r^3}{G M_{\odot}} \implies M_{\odot} = \frac{4\pi^2 r^3}{G T^2}$। $T = 365 \times 86400 \approx 3.1536 \times 10^7\text{ s}$। $M_{\odot} = \frac{4\pi^2 (1.5\times 10^{11})^3}{(6.673\times 10^{-11})(3.1536\times 10^7)^2} = \frac{39.478 \times 3.375\times 10^{33}}{6.673\times 10^{-11} \times 9.945\times 10^{14}} = \frac{1.332\times 10^{35}}{6.636\times 10^4} \approx 2.01 \times 10^{30}\text{ kg}$।</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>মহাকর্ষীয় সমাধান 39</t>
-        </is>
-      </c>
-      <c r="K90" t="inlineStr"/>
-      <c r="L90" t="inlineStr"/>
-      <c r="M90" t="inlineStr"/>
-      <c r="N90" t="inlineStr"/>
+          <t>$M_{\odot} \approx 2.01 \times 10^{30}\\text{ kg}$</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -5668,12 +5383,12 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>বাইনারি স্টার সিস্টেম ও অভিকর্ষ বল (সমস্যা 40)</t>
+          <t>উন্নত কক্ষপথ বলবিদ্যা, কেপলারের সূত্র ও মহাকর্ষীয় বিভব (Advanced Orbital Mechanics &amp; Potentials)</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F91" t="n">
@@ -5681,25 +5396,25 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>[সমস্যা 40: বাইনারি স্টার সিস্টেম ও অভিকর্ষ বল]
-মহাশূন্যে পরস্পর হতে $r = 10 \times 10^{11}\text{ m}$ দূরত্বে অবস্থিত দুটি নক্ষত্রের প্রতিটির ভর $M = 2.0 \times 10^{30}\text{ kg}$। এদের মধ্যকার মহাকর্ষীয় আকর্ষণ বলের মান নির্ণয় কর।</t>
-        </is>
-      </c>
-      <c r="H91" t="inlineStr"/>
+          <t>##GEO:circle[r=2.8][size:small]##
+একটি উপগ্রহ ভূপৃষ্ঠের খুব কাছাকাছি প্রদক্ষিণ করছে যার কক্ষীয় দ্রুতি $v_o$। উপগ্রহটিকে কক্ষপথ হতে সম্পূর্ণ মুক্ত করে মহাশূন্যে পাঠিয়ে দিতে এর গতিবেগ কত শতাংশ বৃদ্ধি করতে হবে?</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=2.8][size:small]##</t>
+        </is>
+      </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>নিউটনের সার্বজনীন মহাকর্ষ সূত্র ও কেপলারের গ্রহীয় গতির সূত্রাবলি প্রয়োগ করে ধাপে ধাপে সমাধান (সমস্যা 40)।</t>
+          <t>কক্ষীয় বেগ $v_o = \sqrt{gR}$। মুক্তিবেগ $v_e = \sqrt{2gR} = \sqrt{2}v_o \approx 1.4142 v_o$। বেগের ভগ্নাংশিক বৃদ্ধি $\frac{v_e - v_o}{v_o} = \sqrt{2} - 1 \approx 0.4142$। শতকরা বৃদ্ধি $= 41.42\%$। (গতিশক্তি দ্বিগুণ বা $100\%$ বাড়াতে হয়)।</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>মহাকর্ষীয় সমাধান 40</t>
-        </is>
-      </c>
-      <c r="K91" t="inlineStr"/>
-      <c r="L91" t="inlineStr"/>
-      <c r="M91" t="inlineStr"/>
-      <c r="N91" t="inlineStr"/>
+          <t>বেগ বৃদ্ধি করতে হবে $41.42\%$</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -5719,43 +5434,38 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>কেপলারের ৩য় সূত্র ও উপগ্রহের পর্যায়কাল (সমস্যা 41)</t>
+          <t>উন্নত কক্ষপথ বলবিদ্যা, কেপলারের সূত্র ও মহাকর্ষীয় বিভব (Advanced Orbital Mechanics &amp; Potentials)</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F92" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>[সমস্যা 41: কেপলারের ৩য় সূত্র ও উপগ্রহের পর্যায়কাল]
-##PRESET:kepler-orbit[size:medium]##
-পৃথিবীর পৃষ্ঠ হতে $h = 1200\text{ km}$ উচ্চতায় একটি কৃত্রিম উপগ্রহ বৃত্তাকার কক্ষপথে পৃথিবীকে প্রদক্ষিণ করছে। পৃথিবীর ভর $M = 6.0 \times 10^{24}\text{ kg}$ এবং ব্যাসার্ধ $R = 6400\text{ km}$ হলে উপগ্রহটির কক্ষীয় দ্রুতি এবং পর্যায়কাল কত?</t>
+          <t>##GEO:triangle[a=4,b=4,c=4][size:small]##
+তিনটি সমান ভর $m$ একটি বাহু $a$ বিশিষ্ট সমবাহু ত্রিভুজের তিনটি শীর্ষবিন্দুতে অবস্থিত। ত্রিভুজটির ভরকেন্দ্রে মহাকর্ষীয় বিভব এবং যে কোনো একটি ভরের ওপর বাকি দুটি ভর কর্তৃক প্রযুক্ত লব্ধি বলের মান নির্ণয় কর।</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>##PRESET:kepler-orbit[size:medium]##</t>
+          <t>##GEO:triangle[a=4,b=4,c=4][size:small]##</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>নিউটনের সার্বজনীন মহাকর্ষ সূত্র ও কেপলারের গ্রহীয় গতির সূত্রাবলি প্রয়োগ করে ধাপে ধাপে সমাধান (সমস্যা 41)।</t>
+          <t>শীর্ষ হতে ভরকেন্দ্রের দূরত্ব $r = \frac{a}{\sqrt{3}}$। ভরকেন্দ্রে বিভব $V = 3\left(-\frac{Gm}{r}\right) = -3\frac{Gm}{a/\sqrt{3}} = -\frac{3\sqrt{3}Gm}{a}$। যে কোনো শীর্ষে দুটি বলের মান $F_1 = F_2 = \frac{Gm^2}{a^2}$ এবং তাদের অন্তর্ভুক্ত কোণ $60^\circ$। লব্ধি বল $F = \sqrt{F_1^2 + F_2^2 + 2F_1 F_2\cos 60^\circ} = \sqrt{3}\frac{Gm^2}{a^2}$।</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>মহাকর্ষীয় সমাধান 41</t>
-        </is>
-      </c>
-      <c r="K92" t="inlineStr"/>
-      <c r="L92" t="inlineStr"/>
-      <c r="M92" t="inlineStr"/>
-      <c r="N92" t="inlineStr"/>
+          <t>কেন্দ্রে বিভব $V = -\frac{3\sqrt{3}Gm}{a}$, লব্ধি বল $F = \frac{\sqrt{3}Gm^2}{a^2}$</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -5775,12 +5485,12 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>ভূপৃষ্ঠ থেকে উচ্চতায় g-এর মান (সমস্যা 42)</t>
+          <t>উন্নত কক্ষপথ বলবিদ্যা, কেপলারের সূত্র ও মহাকর্ষীয় বিভব (Advanced Orbital Mechanics &amp; Potentials)</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F93" t="n">
@@ -5788,25 +5498,25 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>[সমস্যা 42: ভূপৃষ্ঠ থেকে উচ্চতায় g-এর মান]
-ভূপৃষ্ঠ হতে কত উচ্চতায় অভিকর্ষজ ত্বরণের মান ভূপৃষ্ঠের মানের $\frac{1}{7}$ অংশ হবে? (পৃথিবীর ব্যাসার্ধ $R = 6400\text{ km}$)</t>
-        </is>
-      </c>
-      <c r="H93" t="inlineStr"/>
+          <t>##GEO:circle[r=3][size:small]##
+একটি ভূ-স্থির উপগ্রহের অবস্থান থেকে পৃথিবীর দৃশ্যমান গোলীয় কোণ (Solid angle) বা পৃথিবীর বিষুবীয় দিগন্তের কোণ নির্ণয় কর। ভূপৃষ্ঠের সর্বোচ্চ কত অক্ষাংশ পর্যন্ত এই উপগ্রহের সংকেত সরাসরি গ্রহণ করা সম্ভব?</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=3][size:small]##</t>
+        </is>
+      </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>নিউটনের সার্বজনীন মহাকর্ষ সূত্র ও কেপলারের গ্রহীয় গতির সূত্রাবলি প্রয়োগ করে ধাপে ধাপে সমাধান (সমস্যা 42)।</t>
+          <t>উপগ্রহের দূরত্ব $r = 42200\text{ km}$, পৃথিবীর ব্যাসার্ধ $R = 6400\text{ km}$। উপগ্রহ হতে পৃথিবীর পৃষ্ঠের স্পর্শকের কোণ $\cos\lambda_{\max} = \frac{R}{r} = \frac{6400}{42200} \approx 0.1517 \implies \lambda_{\max} = \cos^{-1}(0.1517) \approx 81.28^\circ \approx 81.3^\circ$ উত্তর ও দক্ষিণ অক্ষাংশ।</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>মহাকর্ষীয় সমাধান 42</t>
-        </is>
-      </c>
-      <c r="K93" t="inlineStr"/>
-      <c r="L93" t="inlineStr"/>
-      <c r="M93" t="inlineStr"/>
-      <c r="N93" t="inlineStr"/>
+          <t>সর্বোচ্চ অক্ষাংশ $\lambda_{\max} \approx 81.3^\circ$</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -5826,38 +5536,38 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>খনিতে বা গভীরতায় g-এর পরিবর্তন (সমস্যা 43)</t>
+          <t>উন্নত কক্ষপথ বলবিদ্যা, কেপলারের সূত্র ও মহাকর্ষীয় বিভব (Advanced Orbital Mechanics &amp; Potentials)</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F94" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>[সমস্যা 43: খনিতে বা গভীরতায় g-এর পরিবর্তন]
-ভূপৃষ্ঠ হতে কত গভীরে খনির ভেতর প্রবেশ করলে অভিকর্ষজ ত্বরণের মান ভূপৃষ্ঠের মানের $15\%$ হ্রাস পাবে?</t>
-        </is>
-      </c>
-      <c r="H94" t="inlineStr"/>
+          <t>##GEO:circle[r=3.5][size:small]##
+চাঁদ প্রতি $27.3\text{ দিনে}$ পৃথিবীকে একবার প্রদক্ষিণ করে ($r = 3.84 	imes 10^8\text{ m}$)। এই তথ্য ব্যবহার করে চাঁদের কক্ষপথে পৃথিবীর মহাকর্ষীয় ত্বরণ নির্ণয় কর এবং দেখাও যে তা ভূপৃষ্ঠের $g$-এর প্রায় $1/3600$ অংশ।</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=3.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>নিউটনের সার্বজনীন মহাকর্ষ সূত্র ও কেপলারের গ্রহীয় গতির সূত্রাবলি প্রয়োগ করে ধাপে ধাপে সমাধান (সমস্যা 43)।</t>
+          <t>কৌণিক বেগ $\omega = \frac{2\pi}{27.3 \times 86400} = \frac{2\pi}{2.359\times 10^6} \approx 2.664\times 10^{-6}\text{ rad/s}$। কেন্দ্রমুখী ত্বরণ $a_c = \omega^2 r = (2.664\times 10^{-6})^2 \times 3.84\times 10^8 \approx 7.098\times 10^{-12} \times 3.84\times 10^8 \approx 2.72\times 10^{-3}\text{ m/s}^2$। ভূপৃষ্ঠের মানের সাথে অনুপাত: $\frac{a_c}{g} = \frac{2.72\times 10^{-3}}{9.8} \approx \frac{1}{3603} \approx \frac{1}{3600}$ (যা নিউটনের ব্যস্তবর্গীয় সূত্রের ঐতিহাসিক প্রমাণ)।</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>মহাকর্ষীয় সমাধান 43</t>
-        </is>
-      </c>
-      <c r="K94" t="inlineStr"/>
-      <c r="L94" t="inlineStr"/>
-      <c r="M94" t="inlineStr"/>
-      <c r="N94" t="inlineStr"/>
+          <t>$a_c = 2.72 \times 10^{-3}\\text{ m/s}^2 \approx \frac{g}{3600}$</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -5877,12 +5587,12 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>মুক্তিবেগ ও গ্রহের ঘনত্ব (সমস্যা 44)</t>
+          <t>উন্নত কক্ষপথ বলবিদ্যা, কেপলারের সূত্র ও মহাকর্ষীয় বিভব (Advanced Orbital Mechanics &amp; Potentials)</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F95" t="n">
@@ -5890,30 +5600,25 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>[সমস্যা 44: মুক্তিবেগ ও গ্রহের ঘনত্ব]
-##GEO:sphere[r=4][size:small]##
-একটি গ্রহের ভর পৃথিবীর ভরের 6 গুণ কিন্তু ব্যাসার্ধ পৃথিবীর ব্যাসার্ধের 11 গুণ। পৃথিবীর পৃষ্ঠে মুক্তিবেগ $11.2\text{ km/s}$ হলে ঐ গ্রহের পৃষ্ঠে মুক্তিবেগ কত?</t>
+          <t>##GEO:circle[r=3][size:small]##
+একটি কৃত্রিম উপগ্রহের বৃত্তাকার কক্ষপথের ব্যাসার্ধ $1\%$ বৃদ্ধি পেলে এর কক্ষীয় দ্রুতি এবং পর্যায়কালের শতকরা পরিবর্তন কত হবে?</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>##GEO:sphere[r=4][size:small]##</t>
+          <t>##GEO:circle[r=3][size:small]##</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>নিউটনের সার্বজনীন মহাকর্ষ সূত্র ও কেপলারের গ্রহীয় গতির সূত্রাবলি প্রয়োগ করে ধাপে ধাপে সমাধান (সমস্যা 44)।</t>
+          <t>কক্ষীয় দ্রুতি $v = \sqrt{\frac{GM}{r}} \propto r^{-1/2} \implies \frac{\Delta v}{v} = -\frac{1}{2}\frac{\Delta r}{r} = -0.5(1\%) = -0.5\%$ (হ্রাস)। পর্যায়কাল $T \propto r^{3/2} \implies \frac{\Delta T}{T} = \frac{3}{2}\frac{\Delta r}{r} = 1.5(1\%) = +1.5\%$ (বৃদ্ধি)।</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>মহাকর্ষীয় সমাধান 44</t>
-        </is>
-      </c>
-      <c r="K95" t="inlineStr"/>
-      <c r="L95" t="inlineStr"/>
-      <c r="M95" t="inlineStr"/>
-      <c r="N95" t="inlineStr"/>
+          <t>দ্রুতি $0.5\%$ হ্রাস পাবে, পর্যায়কাল $1.5\%$ বৃদ্ধি পাবে</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -5933,38 +5638,38 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>ভূ-স্থির উপগ্রহের উচ্চতা ও কক্ষপথ (সমস্যা 45)</t>
+          <t>উন্নত কক্ষপথ বলবিদ্যা, কেপলারের সূত্র ও মহাকর্ষীয় বিভব (Advanced Orbital Mechanics &amp; Potentials)</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F96" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>[সমস্যা 45: ভূ-স্থির উপগ্রহের উচ্চতা ও কক্ষপথ]
-একটি ভূ-স্থির উপগ্রহের পর্যায়কাল $T = 24\text{ ঘণ্টা}$। ভূপৃষ্ঠ হতে উপগ্রহটির উচ্চতা কত কিলোমিটার নির্ণয় কর। ($M = 6.0 \times 10^{24}\text{ kg}, R = 6400\text{ km}$)</t>
-        </is>
-      </c>
-      <c r="H96" t="inlineStr"/>
+          <t>##GEO:circle[r=3][size:small]##
+সূর্যের চারদিকে পৃথিবীর কক্ষপথের আধা-মুখ্য অক্ষ (Semi-major axis) $a = 1.496 	imes 10^{11}\text{ m}$ এবং উৎকেন্দ্রিকতা $e = 0.0167$। অপসূর (Aphelion) ও অনুসূর (Perihelion) দূরত্বের পার্থক্য কত কিলোমিটার?</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=3][size:small]##</t>
+        </is>
+      </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>নিউটনের সার্বজনীন মহাকর্ষ সূত্র ও কেপলারের গ্রহীয় গতির সূত্রাবলি প্রয়োগ করে ধাপে ধাপে সমাধান (সমস্যা 45)।</t>
+          <t>অনুসূর দূরত্ব $r_p = a(1 - e)$, অপসূর দূরত্ব $r_a = a(1 + e)$। দূরত্বের পার্থক্য $\Delta r = r_a - r_p = 2ae = 2(1.496\times 10^{11})(0.0167) \approx 4.9966\times 10^9\text{ m} \approx 5.0\times 10^6\text{ km}$।</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>মহাকর্ষীয় সমাধান 45</t>
-        </is>
-      </c>
-      <c r="K96" t="inlineStr"/>
-      <c r="L96" t="inlineStr"/>
-      <c r="M96" t="inlineStr"/>
-      <c r="N96" t="inlineStr"/>
+          <t>দূরত্বের পার্থক্য $\Delta r = 4.997 \times 10^6\\text{ km} \approx 5.0 \times 10^6\\text{ km}$</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -5984,12 +5689,12 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>মহাকর্ষীয় বিভব ও কৃতকাজ (সমস্যা 46)</t>
+          <t>উন্নত কক্ষপথ বলবিদ্যা, কেপলারের সূত্র ও মহাকর্ষীয় বিভব (Advanced Orbital Mechanics &amp; Potentials)</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F97" t="n">
@@ -5997,25 +5702,25 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>[সমস্যা 46: মহাকর্ষীয় বিভব ও কৃতকাজ]
-$m = 10\text{ kg}$ ভরের একটি বস্তুকে অসীম দূরত্ব হতে পৃথিবীর পৃষ্ঠে নিয়ে আসতে মহাকর্ষ বল দ্বারা সম্পাদিত কাজের মান কত?</t>
-        </is>
-      </c>
-      <c r="H97" t="inlineStr"/>
+          <t>##GEO:circle[r=2.5][size:small]##
+একটি গ্রহের উপরিভাগে মাধ্যাকর্ষণজনিত ত্বরণ $g$। গ্রহটির কেন্দ্র দিয়ে ব্যাস বরাবর নির্মিত মসৃণ সুরঙ্গের মধ্য দিয়ে পতনের সময় সুরঙ্গের মধ্যবিন্দুতে বস্তুর বেগ কত হবে?</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>নিউটনের সার্বজনীন মহাকর্ষ সূত্র ও কেপলারের গ্রহীয় গতির সূত্রাবলি প্রয়োগ করে ধাপে ধাপে সমাধান (সমস্যা 46)।</t>
+          <t>সুরঙ্গের কেন্দ্রগামী গতি সরল ছন্দিত স্পন্দন যেখানে বিস্তার $A = R$। কেন্দ্রে সর্বোচ্চ বেগ $v_{\max} = \omega A = \sqrt{\frac{g}{R}} \times R = \sqrt{g R}$।</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>মহাকর্ষীয় সমাধান 46</t>
-        </is>
-      </c>
-      <c r="K97" t="inlineStr"/>
-      <c r="L97" t="inlineStr"/>
-      <c r="M97" t="inlineStr"/>
-      <c r="N97" t="inlineStr"/>
+          <t>$v = \sqrt{g R}$</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -6035,38 +5740,38 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>পৃথিবী ও চাঁদের মধ্যবর্তী নিরপেক্ষ বিন্দু (সমস্যা 47)</t>
+          <t>উন্নত কক্ষপথ বলবিদ্যা, কেপলারের সূত্র ও মহাকর্ষীয় বিভব (Advanced Orbital Mechanics &amp; Potentials)</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F98" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>[সমস্যা 47: পৃথিবী ও চাঁদের মধ্যবর্তী নিরপেক্ষ বিন্দু]
-পৃথিবীর ভর চাঁদের ভরের 12 গুণ এবং এদের মধ্যবর্তী দূরত্ব $d = 3.84 \times 10^5\text{ km}$। পৃথিবী ও চাঁদের সংযোগকারী সরলরেখার কোন বিন্দুতে লব্ধি মহাকর্ষীয় প্রাবল্য শূন্য হবে?</t>
-        </is>
-      </c>
-      <c r="H98" t="inlineStr"/>
+          <t>##GEO:pendulum[angle=15,length=3.5][size:small]##
+একটি কাল্পনিক গ্রহের ভর ও ব্যাসার্ধ উভয়ই পৃথিবীর দ্বিগুণ হলে ওই গ্রহে $1\text{ সেকেন্ড}$ দোলকের কার্যকরী দৈর্ঘ্য কত হবে? (ভূপৃষ্ঠে সেকেন্ড দোলকের দৈর্ঘ্য $0.993\text{ m}$)।</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>##GEO:pendulum[angle=15,length=3.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>নিউটনের সার্বজনীন মহাকর্ষ সূত্র ও কেপলারের গ্রহীয় গতির সূত্রাবলি প্রয়োগ করে ধাপে ধাপে সমাধান (সমস্যা 47)।</t>
+          <t>গ্রহে ত্বরণ $g' = G\frac{2M}{(2R)^2} = \frac{1}{2}g$। সেকেন্ড দোলকের পর্যায়কাল $T = 2\text{ s}$ ধ্রুব: $L \propto g$। $L' = \frac{g'}{g} L = \frac{1}{2}(0.993) \approx 0.4965\text{ m} = 49.65\text{ cm}$।</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>মহাকর্ষীয় সমাধান 47</t>
-        </is>
-      </c>
-      <c r="K98" t="inlineStr"/>
-      <c r="L98" t="inlineStr"/>
-      <c r="M98" t="inlineStr"/>
-      <c r="N98" t="inlineStr"/>
+          <t>$L' = 0.4965\\text{ m} \approx 49.65\\text{ cm}$</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -6086,12 +5791,12 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>আহ্নিক গতির কারণে g-এর হ্রাস (সমস্যা 48)</t>
+          <t>উন্নত কক্ষপথ বলবিদ্যা, কেপলারের সূত্র ও মহাকর্ষীয় বিভব (Advanced Orbital Mechanics &amp; Potentials)</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F99" t="n">
@@ -6099,25 +5804,25 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>[সমস্যা 48: আহ্নিক গতির কারণে g-এর হ্রাস]
-বিষুবরেখা অঞ্চলে পৃথিবীর আহ্নিক গতির জন্য কোনো বস্তুর ওজনে শতকরা কত আপাত হ্রাস ঘটে? ($R = 6400\text{ km}, T = 86400\text{ s}$)</t>
-        </is>
-      </c>
-      <c r="H99" t="inlineStr"/>
+          <t>##GEO:rect[w=3,h=3][size:small]##
+চারটি সমান ভর $m$ একটি $a$ বাহুবিশিষ্ট বর্গের চারটি শীর্ষবিন্দুতে অবস্থান করছে। বর্গের কেন্দ্রে মহাকর্ষীয় প্রাবল্য ও মহাকর্ষীয় বিভবের মান কত?</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>##GEO:rect[w=3,h=3][size:small]##</t>
+        </is>
+      </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>নিউটনের সার্বজনীন মহাকর্ষ সূত্র ও কেপলারের গ্রহীয় গতির সূত্রাবলি প্রয়োগ করে ধাপে ধাপে সমাধান (সমস্যা 48)।</t>
+          <t>সমমিতির কারণে বিপরীতমুখী প্রাবল্যগুলো পরস্পরকে প্রশমিত করে, সুতরাং কেন্দ্রে মোট প্রাবল্য $E = 0$। কেন্দ্র হতে প্রতিটি শীর্ষের দূরত্ব $r = \frac{a}{\sqrt{2}}$। কেন্দ্রে মোট স্কেলার বিভব $V = 4\left(-\frac{Gm}{r}\right) = -4\frac{Gm}{a/\sqrt{2}} = -\frac{4\sqrt{2}Gm}{a}$।</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>মহাকর্ষীয় সমাধান 48</t>
-        </is>
-      </c>
-      <c r="K99" t="inlineStr"/>
-      <c r="L99" t="inlineStr"/>
-      <c r="M99" t="inlineStr"/>
-      <c r="N99" t="inlineStr"/>
+          <t>প্রাবল্য $E = 0$, বিভব $V = -\frac{4\sqrt{2}Gm}{a}$</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -6137,38 +5842,38 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>কেপলারের ক্ষেত্রফলের সূত্র ও ক্ষেত্রীয় বেগ (সমস্যা 49)</t>
+          <t>উন্নত কক্ষপথ বলবিদ্যা, কেপলারের সূত্র ও মহাকর্ষীয় বিভব (Advanced Orbital Mechanics &amp; Potentials)</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F100" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>[সমস্যা 49: কেপলারের ক্ষেত্রফলের সূত্র ও ক্ষেত্রীয় বেগ]
-একটি উপগ্রহ উপবৃত্তাকার কক্ষপথে আবর্তনের সময় নিকটতম দূরত্বে বেগ $v_1 = 4\text{ km/s}$ এবং দূরত্ব $r_1 = 11000\text{ km}$। দূরতম বিন্দুতে দূরত্ব $r_2 = 10000\text{ km}$ হলে সেখানে বেগ কত?</t>
-        </is>
-      </c>
-      <c r="H100" t="inlineStr"/>
+          <t>##GEO:circle[r=3.2][size:small]##
+একটি উপগ্রহকে $v_0$ বেগে অনুভূমিকভাবে নিক্ষেপ করা হলো ($v_o &lt; v_0 &lt; v_e$)। উপগ্রহটির গতিপথ কেমন হবে এবং এর শক্তি বিশ্লেষণ কর।</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=3.2][size:small]##</t>
+        </is>
+      </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>নিউটনের সার্বজনীন মহাকর্ষ সূত্র ও কেপলারের গ্রহীয় গতির সূত্রাবলি প্রয়োগ করে ধাপে ধাপে সমাধান (সমস্যা 49)।</t>
+          <t>যখন প্রক্ষেপণ দ্রুতি বৃত্তাকার কক্ষীয় বেগ অপেক্ষা বেশি কিন্তু মুক্তিবেগ অপেক্ষা কম হয় ($v_o &lt; v_0 &lt; \sqrt{2}v_o$), তখন উপগ্রহটি পৃথিবীকে একটি উপবৃত্তাকার (Elliptical) কক্ষপথে প্রদক্ষিণ করবে যার অনুসূর (Perigee) হবে নিক্ষেপণ বিন্দু। মোট যান্ত্রিক শক্তি $E = -\frac{GMm}{2a} &lt; 0$।</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>মহাকর্ষীয় সমাধান 49</t>
-        </is>
-      </c>
-      <c r="K100" t="inlineStr"/>
-      <c r="L100" t="inlineStr"/>
-      <c r="M100" t="inlineStr"/>
-      <c r="N100" t="inlineStr"/>
+          <t>উপবৃত্তাকার কক্ষপথ (Elliptical orbit), মোট শক্তি ঋণাত্মক ($E &lt; 0$)</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -6188,12 +5893,12 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>বাইনারি স্টার সিস্টেম ও অভিকর্ষ বল (সমস্যা 50)</t>
+          <t>উন্নত কক্ষপথ বলবিদ্যা, কেপলারের সূত্র ও মহাকর্ষীয় বিভব (Advanced Orbital Mechanics &amp; Potentials)</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F101" t="n">
@@ -6201,25 +5906,25 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>[সমস্যা 50: বাইনারি স্টার সিস্টেম ও অভিকর্ষ বল]
-মহাশূন্যে পরস্পর হতে $r = 6 \times 10^{11}\text{ m}$ দূরত্বে অবস্থিত দুটি নক্ষত্রের প্রতিটির ভর $M = 2.0 \times 10^{30}\text{ kg}$। এদের মধ্যকার মহাকর্ষীয় আকর্ষণ বলের মান নির্ণয় কর।</t>
-        </is>
-      </c>
-      <c r="H101" t="inlineStr"/>
+          <t>##GEO:circle[r=2.5][size:small]##
+একটি তারার পৃষ্ঠ হতে ফোটন নির্গমনে মহাকর্ষীয় লোহিত বিচ্যুতি (Gravitational Redshift) সমীকরণ প্রতিপাদন কর। দেখাও যে নির্গত আলোর কম্পাঙ্ক হ্রাস $\frac{\Delta\nu}{\nu} \approx -\frac{GM}{R c^2}$।</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>নিউটনের সার্বজনীন মহাকর্ষ সূত্র ও কেপলারের গ্রহীয় গতির সূত্রাবলি প্রয়োগ করে ধাপে ধাপে সমাধান (সমস্যা 50)।</t>
+          <t>একটি ফোটনের কার্যকর মহাকর্ষীয় ভর $m = \frac{h\nu}{c^2}$। পৃষ্ঠ হতে অসীমে যেতে মহাকর্ষীয় শক্তির ক্ষয় $\Delta E = -\frac{GMm}{R} = -\frac{GM h\nu}{R c^2}$। প্লাঙ্কের সম্পর্ক অনুসারে $\Delta E = h\Delta\nu \implies h\Delta\nu = -\frac{GM h\nu}{R c^2} \implies \frac{\Delta\nu}{\nu} = -\frac{GM}{R c^2}$। এটি সাধারণ আপেক্ষিকতার মহাকর্ষীয় সময়ের প্রসারণ ও লোহিত বিচ্যুতি নিশ্চিত করে।</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>মহাকর্ষীয় সমাধান 50</t>
-        </is>
-      </c>
-      <c r="K101" t="inlineStr"/>
-      <c r="L101" t="inlineStr"/>
-      <c r="M101" t="inlineStr"/>
-      <c r="N101" t="inlineStr"/>
+          <t>$\frac{\Delta\nu}{\nu} \approx -\frac{GM}{R c^2}$</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
